--- a/Data/2020_F013B4_CO_PIT/2020_F013B4_CO_PIT_CropCanopy.xlsx
+++ b/Data/2020_F013B4_CO_PIT/2020_F013B4_CO_PIT_CropCanopy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mnt\Data1\USDA-ALARC\GIS\PDI project\cottondata\Data\2020_F013B4_CO_PIT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2604DA9F-4398-480B-B59F-293587EC9719}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99487B70-A549-4E0A-BC22-6644E384922A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7890" yWindow="-555" windowWidth="20175" windowHeight="16230" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1620" yWindow="-26850" windowWidth="17955" windowHeight="22395" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Height" sheetId="10" r:id="rId1"/>
@@ -1773,21 +1773,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1841,9 +1826,6 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
@@ -1926,17 +1908,11 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="15" fontId="10" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
@@ -2064,12 +2040,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="26" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2128,6 +2098,36 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="26" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6003,1614 +6003,1614 @@
   <dimension ref="A1:J64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17" style="143" customWidth="1"/>
-    <col min="2" max="2" width="7.7109375" style="119" customWidth="1"/>
-    <col min="3" max="4" width="5.28515625" style="89" customWidth="1"/>
-    <col min="5" max="6" width="9.140625" style="89"/>
-    <col min="7" max="7" width="11.140625" style="89" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="89"/>
+    <col min="1" max="1" width="17" style="135" customWidth="1"/>
+    <col min="2" max="2" width="7.7109375" style="113" customWidth="1"/>
+    <col min="3" max="4" width="5.28515625" style="84" customWidth="1"/>
+    <col min="5" max="6" width="9.140625" style="84"/>
+    <col min="7" max="7" width="11.140625" style="84" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="84"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="185">
+      <c r="A1" s="177">
         <v>2020</v>
       </c>
-      <c r="B1" s="185" t="s">
+      <c r="B1" s="177" t="s">
         <v>231</v>
       </c>
-      <c r="C1" s="184" t="s">
+      <c r="C1" s="176" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B2" s="89"/>
+      <c r="B2" s="84"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B3" s="183" t="s">
+      <c r="B3" s="175" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="116" t="s">
+      <c r="A4" s="110" t="s">
         <v>229</v>
       </c>
-      <c r="B4" s="183"/>
+      <c r="B4" s="175"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="116"/>
-      <c r="B5" s="183"/>
+      <c r="A5" s="110"/>
+      <c r="B5" s="175"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="116"/>
-      <c r="B6" s="183"/>
+      <c r="A6" s="110"/>
+      <c r="B6" s="175"/>
     </row>
     <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C7" s="183"/>
+      <c r="C7" s="175"/>
     </row>
     <row r="8" spans="1:10" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C8" s="89" t="s">
+      <c r="C8" s="84" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="182" t="s">
+      <c r="B9" s="174" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="181">
+      <c r="C9" s="173">
         <v>43950</v>
       </c>
-      <c r="D9" s="180"/>
-      <c r="E9" s="179">
+      <c r="D9" s="172"/>
+      <c r="E9" s="171">
         <v>43951</v>
       </c>
-      <c r="F9" s="179">
+      <c r="F9" s="171">
         <v>43952</v>
       </c>
-      <c r="G9" s="179">
+      <c r="G9" s="171">
         <v>43957</v>
       </c>
-      <c r="H9" s="179">
+      <c r="H9" s="171">
         <v>43960</v>
       </c>
-      <c r="I9" s="179">
+      <c r="I9" s="171">
         <v>43962</v>
       </c>
-      <c r="J9" s="179"/>
+      <c r="J9" s="171"/>
     </row>
     <row r="10" spans="1:10" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="174"/>
-      <c r="B10" s="178" t="s">
+      <c r="A10" s="166"/>
+      <c r="B10" s="170" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="177">
+      <c r="C10" s="169">
         <v>120</v>
       </c>
-      <c r="D10" s="176"/>
-      <c r="E10" s="175">
+      <c r="D10" s="168"/>
+      <c r="E10" s="167">
         <v>121</v>
       </c>
-      <c r="F10" s="175">
+      <c r="F10" s="167">
         <v>122</v>
       </c>
-      <c r="G10" s="175">
+      <c r="G10" s="167">
         <v>127</v>
       </c>
-      <c r="H10" s="175">
+      <c r="H10" s="167">
         <v>130</v>
       </c>
-      <c r="I10" s="175">
+      <c r="I10" s="167">
         <v>132</v>
       </c>
-      <c r="J10" s="175"/>
-    </row>
-    <row r="11" spans="1:10" s="169" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="174"/>
-      <c r="B11" s="173" t="s">
+      <c r="J10" s="167"/>
+    </row>
+    <row r="11" spans="1:10" s="161" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="166"/>
+      <c r="B11" s="165" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="172" t="s">
+      <c r="C11" s="164" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="171"/>
-      <c r="E11" s="170" t="s">
+      <c r="D11" s="163"/>
+      <c r="E11" s="162" t="s">
         <v>44</v>
       </c>
-      <c r="F11" s="170" t="s">
+      <c r="F11" s="162" t="s">
         <v>44</v>
       </c>
-      <c r="G11" s="170" t="s">
+      <c r="G11" s="162" t="s">
         <v>44</v>
       </c>
-      <c r="H11" s="170" t="s">
+      <c r="H11" s="162" t="s">
         <v>44</v>
       </c>
-      <c r="I11" s="170" t="s">
+      <c r="I11" s="162" t="s">
         <v>44</v>
       </c>
-      <c r="J11" s="170"/>
-    </row>
-    <row r="12" spans="1:10" s="119" customFormat="1" ht="37.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="165"/>
-      <c r="B12" s="164" t="s">
+      <c r="J11" s="162"/>
+    </row>
+    <row r="12" spans="1:10" s="113" customFormat="1" ht="37.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="157"/>
+      <c r="B12" s="156" t="s">
         <v>227</v>
       </c>
-      <c r="C12" s="168" t="s">
+      <c r="C12" s="160" t="s">
         <v>226</v>
       </c>
-      <c r="D12" s="167"/>
-      <c r="E12" s="166" t="s">
+      <c r="D12" s="159"/>
+      <c r="E12" s="158" t="s">
         <v>225</v>
       </c>
-      <c r="F12" s="166" t="s">
+      <c r="F12" s="158" t="s">
         <v>224</v>
       </c>
-      <c r="G12" s="166" t="s">
+      <c r="G12" s="158" t="s">
         <v>223</v>
       </c>
-      <c r="H12" s="166" t="s">
+      <c r="H12" s="158" t="s">
         <v>222</v>
       </c>
-      <c r="I12" s="166" t="s">
+      <c r="I12" s="158" t="s">
         <v>221</v>
       </c>
-      <c r="J12" s="166"/>
-    </row>
-    <row r="13" spans="1:10" s="119" customFormat="1" ht="37.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="165"/>
-      <c r="B13" s="164"/>
-      <c r="C13" s="162" t="s">
+      <c r="J12" s="158"/>
+    </row>
+    <row r="13" spans="1:10" s="113" customFormat="1" ht="37.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="157"/>
+      <c r="B13" s="156"/>
+      <c r="C13" s="154" t="s">
         <v>219</v>
       </c>
-      <c r="D13" s="163" t="s">
+      <c r="D13" s="155" t="s">
         <v>220</v>
       </c>
-      <c r="E13" s="162" t="s">
+      <c r="E13" s="154" t="s">
         <v>219</v>
       </c>
-      <c r="F13" s="162" t="s">
+      <c r="F13" s="154" t="s">
         <v>219</v>
       </c>
-      <c r="G13" s="162" t="s">
+      <c r="G13" s="154" t="s">
         <v>219</v>
       </c>
-      <c r="H13" s="162" t="s">
+      <c r="H13" s="154" t="s">
         <v>219</v>
       </c>
-      <c r="I13" s="162" t="s">
+      <c r="I13" s="154" t="s">
         <v>219</v>
       </c>
-      <c r="J13" s="162"/>
+      <c r="J13" s="154"/>
     </row>
     <row r="14" spans="1:10" ht="37.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="161" t="s">
+      <c r="A14" s="153" t="s">
         <v>218</v>
       </c>
-      <c r="B14" s="155" t="s">
+      <c r="B14" s="147" t="s">
         <v>216</v>
       </c>
-      <c r="C14" s="97">
+      <c r="C14" s="92">
         <v>5</v>
       </c>
-      <c r="D14" s="154">
-        <v>2</v>
-      </c>
-      <c r="E14" s="157">
+      <c r="D14" s="146">
+        <v>2</v>
+      </c>
+      <c r="E14" s="149">
         <v>9</v>
       </c>
-      <c r="F14" s="97">
+      <c r="F14" s="92">
         <v>9</v>
       </c>
-      <c r="G14" s="97">
+      <c r="G14" s="92">
         <v>10</v>
       </c>
-      <c r="H14" s="97">
+      <c r="H14" s="92">
         <v>11</v>
       </c>
-      <c r="I14" s="97">
+      <c r="I14" s="92">
         <v>11</v>
       </c>
-      <c r="J14" s="97"/>
+      <c r="J14" s="92"/>
     </row>
     <row r="15" spans="1:10" ht="37.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="156"/>
-      <c r="B15" s="153" t="s">
+      <c r="A15" s="148"/>
+      <c r="B15" s="145" t="s">
         <v>215</v>
       </c>
-      <c r="C15" s="150">
+      <c r="C15" s="142">
         <v>6</v>
       </c>
-      <c r="D15" s="152">
-        <v>2</v>
-      </c>
-      <c r="E15" s="150">
+      <c r="D15" s="144">
+        <v>2</v>
+      </c>
+      <c r="E15" s="142">
         <v>9</v>
       </c>
-      <c r="F15" s="150">
+      <c r="F15" s="142">
         <v>9</v>
       </c>
-      <c r="G15" s="150">
+      <c r="G15" s="142">
         <v>10</v>
       </c>
-      <c r="H15" s="150">
+      <c r="H15" s="142">
         <v>11</v>
       </c>
-      <c r="I15" s="150">
+      <c r="I15" s="142">
         <v>11</v>
       </c>
-      <c r="J15" s="150"/>
+      <c r="J15" s="142"/>
     </row>
     <row r="16" spans="1:10" ht="37.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="153" t="s">
+      <c r="B16" s="145" t="s">
         <v>214</v>
       </c>
-      <c r="C16" s="150">
+      <c r="C16" s="142">
         <v>5</v>
       </c>
-      <c r="D16" s="152">
+      <c r="D16" s="144">
         <v>1</v>
       </c>
-      <c r="E16" s="150">
+      <c r="E16" s="142">
         <v>7</v>
       </c>
-      <c r="F16" s="150">
+      <c r="F16" s="142">
         <v>9</v>
       </c>
-      <c r="G16" s="150">
+      <c r="G16" s="142">
         <v>10</v>
       </c>
-      <c r="H16" s="150">
+      <c r="H16" s="142">
         <v>10</v>
       </c>
-      <c r="I16" s="150">
+      <c r="I16" s="142">
         <v>10</v>
       </c>
-      <c r="J16" s="150"/>
+      <c r="J16" s="142"/>
     </row>
     <row r="17" spans="1:10" ht="37.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="148" t="s">
+      <c r="B17" s="140" t="s">
         <v>213</v>
       </c>
-      <c r="C17" s="91">
-        <v>3</v>
-      </c>
-      <c r="D17" s="147">
+      <c r="C17" s="86">
+        <v>3</v>
+      </c>
+      <c r="D17" s="139">
         <v>0</v>
       </c>
-      <c r="E17" s="91">
+      <c r="E17" s="86">
         <v>6</v>
       </c>
-      <c r="F17" s="91">
+      <c r="F17" s="86">
         <v>6</v>
       </c>
-      <c r="G17" s="91">
+      <c r="G17" s="86">
         <v>7</v>
       </c>
-      <c r="H17" s="91">
+      <c r="H17" s="86">
         <v>7</v>
       </c>
-      <c r="I17" s="91">
+      <c r="I17" s="86">
         <v>7</v>
       </c>
-      <c r="J17" s="91"/>
+      <c r="J17" s="86"/>
     </row>
     <row r="18" spans="1:10" ht="37.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="155" t="s">
+      <c r="B18" s="147" t="s">
         <v>212</v>
       </c>
-      <c r="C18" s="97">
-        <v>3</v>
-      </c>
-      <c r="D18" s="154">
+      <c r="C18" s="92">
+        <v>3</v>
+      </c>
+      <c r="D18" s="146">
         <v>0</v>
       </c>
-      <c r="E18" s="97">
+      <c r="E18" s="92">
         <v>6</v>
       </c>
-      <c r="F18" s="97">
+      <c r="F18" s="92">
         <v>8</v>
       </c>
-      <c r="G18" s="97">
+      <c r="G18" s="92">
         <v>10</v>
       </c>
-      <c r="H18" s="97">
+      <c r="H18" s="92">
         <v>10</v>
       </c>
-      <c r="I18" s="97">
+      <c r="I18" s="92">
         <v>10</v>
       </c>
-      <c r="J18" s="97"/>
+      <c r="J18" s="92"/>
     </row>
     <row r="19" spans="1:10" ht="37.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="153" t="s">
+      <c r="B19" s="145" t="s">
         <v>211</v>
       </c>
-      <c r="C19" s="150">
-        <v>4</v>
-      </c>
-      <c r="D19" s="152">
+      <c r="C19" s="142">
+        <v>4</v>
+      </c>
+      <c r="D19" s="144">
         <v>0</v>
       </c>
-      <c r="E19" s="151">
+      <c r="E19" s="143">
         <v>8</v>
       </c>
-      <c r="F19" s="150">
+      <c r="F19" s="142">
         <v>9</v>
       </c>
-      <c r="G19" s="150">
+      <c r="G19" s="142">
         <v>11</v>
       </c>
-      <c r="H19" s="150">
+      <c r="H19" s="142">
         <v>13</v>
       </c>
-      <c r="I19" s="150">
+      <c r="I19" s="142">
         <v>12</v>
       </c>
-      <c r="J19" s="150"/>
+      <c r="J19" s="142"/>
     </row>
     <row r="20" spans="1:10" ht="37.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="153" t="s">
+      <c r="B20" s="145" t="s">
         <v>210</v>
       </c>
-      <c r="C20" s="150">
-        <v>3</v>
-      </c>
-      <c r="D20" s="152">
+      <c r="C20" s="142">
+        <v>3</v>
+      </c>
+      <c r="D20" s="144">
         <v>0</v>
       </c>
-      <c r="E20" s="151">
+      <c r="E20" s="143">
         <v>10</v>
       </c>
-      <c r="F20" s="150">
+      <c r="F20" s="142">
         <v>11</v>
       </c>
-      <c r="G20" s="150">
+      <c r="G20" s="142">
         <v>12</v>
       </c>
-      <c r="H20" s="150">
+      <c r="H20" s="142">
         <v>13</v>
       </c>
-      <c r="I20" s="150">
+      <c r="I20" s="142">
         <v>13</v>
       </c>
-      <c r="J20" s="150"/>
+      <c r="J20" s="142"/>
     </row>
     <row r="21" spans="1:10" ht="37.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="148" t="s">
+      <c r="B21" s="140" t="s">
         <v>209</v>
       </c>
-      <c r="C21" s="91">
+      <c r="C21" s="86">
         <v>5</v>
       </c>
-      <c r="D21" s="147">
-        <v>2</v>
-      </c>
-      <c r="E21" s="91">
+      <c r="D21" s="139">
+        <v>2</v>
+      </c>
+      <c r="E21" s="86">
         <v>10</v>
       </c>
-      <c r="F21" s="91">
+      <c r="F21" s="86">
         <v>12</v>
       </c>
-      <c r="G21" s="91">
+      <c r="G21" s="86">
         <v>13</v>
       </c>
-      <c r="H21" s="91">
+      <c r="H21" s="86">
         <v>14</v>
       </c>
-      <c r="I21" s="91">
+      <c r="I21" s="86">
         <v>14</v>
       </c>
-      <c r="J21" s="91"/>
+      <c r="J21" s="86"/>
     </row>
     <row r="22" spans="1:10" ht="37.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="155" t="s">
+      <c r="B22" s="147" t="s">
         <v>208</v>
       </c>
-      <c r="C22" s="97">
-        <v>3</v>
-      </c>
-      <c r="D22" s="154">
+      <c r="C22" s="92">
+        <v>3</v>
+      </c>
+      <c r="D22" s="146">
         <v>0</v>
       </c>
-      <c r="E22" s="97">
+      <c r="E22" s="92">
         <v>9</v>
       </c>
-      <c r="F22" s="160">
+      <c r="F22" s="152">
         <v>10</v>
       </c>
-      <c r="G22" s="160">
+      <c r="G22" s="152">
         <v>10</v>
       </c>
-      <c r="H22" s="160">
+      <c r="H22" s="152">
         <v>10</v>
       </c>
-      <c r="I22" s="160">
+      <c r="I22" s="152">
         <v>11</v>
       </c>
-      <c r="J22" s="160"/>
+      <c r="J22" s="152"/>
     </row>
     <row r="23" spans="1:10" ht="37.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="153" t="s">
+      <c r="B23" s="145" t="s">
         <v>207</v>
       </c>
-      <c r="C23" s="150">
+      <c r="C23" s="142">
         <v>5</v>
       </c>
-      <c r="D23" s="152">
+      <c r="D23" s="144">
         <v>1</v>
       </c>
-      <c r="E23" s="150">
+      <c r="E23" s="142">
         <v>11</v>
       </c>
-      <c r="F23" s="150">
+      <c r="F23" s="142">
         <v>14</v>
       </c>
-      <c r="G23" s="150">
+      <c r="G23" s="142">
         <v>16</v>
       </c>
-      <c r="H23" s="150">
+      <c r="H23" s="142">
         <v>16</v>
       </c>
-      <c r="I23" s="150">
+      <c r="I23" s="142">
         <v>16</v>
       </c>
-      <c r="J23" s="150"/>
+      <c r="J23" s="142"/>
     </row>
     <row r="24" spans="1:10" ht="37.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="153" t="s">
+      <c r="B24" s="145" t="s">
         <v>206</v>
       </c>
-      <c r="C24" s="150">
-        <v>2</v>
-      </c>
-      <c r="D24" s="152">
+      <c r="C24" s="142">
+        <v>2</v>
+      </c>
+      <c r="D24" s="144">
         <v>0</v>
       </c>
-      <c r="E24" s="150">
+      <c r="E24" s="142">
         <v>7</v>
       </c>
-      <c r="F24" s="150">
+      <c r="F24" s="142">
         <v>7</v>
       </c>
-      <c r="G24" s="150">
+      <c r="G24" s="142">
         <v>8</v>
       </c>
-      <c r="H24" s="150">
+      <c r="H24" s="142">
         <v>8</v>
       </c>
-      <c r="I24" s="150">
+      <c r="I24" s="142">
         <v>8</v>
       </c>
-      <c r="J24" s="150"/>
+      <c r="J24" s="142"/>
     </row>
     <row r="25" spans="1:10" ht="37.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="148" t="s">
+      <c r="B25" s="140" t="s">
         <v>205</v>
       </c>
-      <c r="C25" s="91">
+      <c r="C25" s="86">
         <v>1</v>
       </c>
-      <c r="D25" s="147">
+      <c r="D25" s="139">
         <v>0</v>
       </c>
-      <c r="E25" s="159">
-        <v>3</v>
-      </c>
-      <c r="F25" s="91">
-        <v>3</v>
-      </c>
-      <c r="G25" s="91">
+      <c r="E25" s="151">
+        <v>3</v>
+      </c>
+      <c r="F25" s="86">
+        <v>3</v>
+      </c>
+      <c r="G25" s="86">
         <v>8</v>
       </c>
-      <c r="H25" s="91">
+      <c r="H25" s="86">
         <v>8</v>
       </c>
-      <c r="I25" s="91">
+      <c r="I25" s="86">
         <v>8</v>
       </c>
-      <c r="J25" s="91"/>
+      <c r="J25" s="86"/>
     </row>
     <row r="26" spans="1:10" ht="37.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="155" t="s">
+      <c r="B26" s="147" t="s">
         <v>204</v>
       </c>
-      <c r="C26" s="97">
+      <c r="C26" s="92">
         <v>7</v>
       </c>
-      <c r="D26" s="154">
-        <v>4</v>
-      </c>
-      <c r="E26" s="157">
+      <c r="D26" s="146">
+        <v>4</v>
+      </c>
+      <c r="E26" s="149">
         <v>13</v>
       </c>
-      <c r="F26" s="97">
+      <c r="F26" s="92">
         <v>15</v>
       </c>
-      <c r="G26" s="97">
+      <c r="G26" s="92">
         <v>15</v>
       </c>
-      <c r="H26" s="97">
+      <c r="H26" s="92">
         <v>15</v>
       </c>
-      <c r="I26" s="97">
+      <c r="I26" s="92">
         <v>15</v>
       </c>
-      <c r="J26" s="97"/>
+      <c r="J26" s="92"/>
     </row>
     <row r="27" spans="1:10" ht="37.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="153" t="s">
+      <c r="B27" s="145" t="s">
         <v>203</v>
       </c>
-      <c r="C27" s="150">
+      <c r="C27" s="142">
         <v>9</v>
       </c>
-      <c r="D27" s="152">
-        <v>3</v>
-      </c>
-      <c r="E27" s="150">
+      <c r="D27" s="144">
+        <v>3</v>
+      </c>
+      <c r="E27" s="142">
         <v>14</v>
       </c>
-      <c r="F27" s="150">
+      <c r="F27" s="142">
         <v>17</v>
       </c>
-      <c r="G27" s="150">
+      <c r="G27" s="142">
         <v>17</v>
       </c>
-      <c r="H27" s="150">
+      <c r="H27" s="142">
         <v>18</v>
       </c>
-      <c r="I27" s="150">
+      <c r="I27" s="142">
         <v>18</v>
       </c>
-      <c r="J27" s="150"/>
+      <c r="J27" s="142"/>
     </row>
     <row r="28" spans="1:10" ht="37.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="153" t="s">
+      <c r="B28" s="145" t="s">
         <v>202</v>
       </c>
-      <c r="C28" s="150">
+      <c r="C28" s="142">
         <v>6</v>
       </c>
-      <c r="D28" s="152">
-        <v>2</v>
-      </c>
-      <c r="E28" s="150">
+      <c r="D28" s="144">
+        <v>2</v>
+      </c>
+      <c r="E28" s="142">
         <v>9</v>
       </c>
-      <c r="F28" s="150">
+      <c r="F28" s="142">
         <v>10</v>
       </c>
-      <c r="G28" s="150">
+      <c r="G28" s="142">
         <v>10</v>
       </c>
-      <c r="H28" s="150">
+      <c r="H28" s="142">
         <v>10</v>
       </c>
-      <c r="I28" s="150">
+      <c r="I28" s="142">
         <v>10</v>
       </c>
-      <c r="J28" s="150"/>
+      <c r="J28" s="142"/>
     </row>
     <row r="29" spans="1:10" ht="37.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="148" t="s">
+      <c r="B29" s="140" t="s">
         <v>201</v>
       </c>
-      <c r="C29" s="91">
+      <c r="C29" s="86">
         <v>6</v>
       </c>
-      <c r="D29" s="147">
+      <c r="D29" s="139">
         <v>1</v>
       </c>
-      <c r="E29" s="91">
+      <c r="E29" s="86">
         <v>8</v>
       </c>
-      <c r="F29" s="91">
+      <c r="F29" s="86">
         <v>8</v>
       </c>
-      <c r="G29" s="91">
+      <c r="G29" s="86">
         <v>9</v>
       </c>
-      <c r="H29" s="91">
+      <c r="H29" s="86">
         <v>9</v>
       </c>
-      <c r="I29" s="91">
+      <c r="I29" s="86">
         <v>9</v>
       </c>
-      <c r="J29" s="91"/>
+      <c r="J29" s="86"/>
     </row>
     <row r="30" spans="1:10" ht="37.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="158"/>
-      <c r="B30" s="155" t="s">
+      <c r="A30" s="150"/>
+      <c r="B30" s="147" t="s">
         <v>200</v>
       </c>
-      <c r="C30" s="97">
+      <c r="C30" s="92">
         <v>6</v>
       </c>
-      <c r="D30" s="154">
-        <v>2</v>
-      </c>
-      <c r="E30" s="157">
+      <c r="D30" s="146">
+        <v>2</v>
+      </c>
+      <c r="E30" s="149">
         <v>7</v>
       </c>
-      <c r="F30" s="97">
+      <c r="F30" s="92">
         <v>12</v>
       </c>
-      <c r="G30" s="97">
+      <c r="G30" s="92">
         <v>12</v>
       </c>
-      <c r="H30" s="97">
+      <c r="H30" s="92">
         <v>13</v>
       </c>
-      <c r="I30" s="97">
+      <c r="I30" s="92">
         <v>13</v>
       </c>
-      <c r="J30" s="97"/>
+      <c r="J30" s="92"/>
     </row>
     <row r="31" spans="1:10" ht="37.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="156"/>
-      <c r="B31" s="153" t="s">
+      <c r="A31" s="148"/>
+      <c r="B31" s="145" t="s">
         <v>199</v>
       </c>
-      <c r="C31" s="150">
+      <c r="C31" s="142">
         <v>9</v>
       </c>
-      <c r="D31" s="152">
-        <v>4</v>
-      </c>
-      <c r="E31" s="150">
+      <c r="D31" s="144">
+        <v>4</v>
+      </c>
+      <c r="E31" s="142">
         <v>11</v>
       </c>
-      <c r="F31" s="150">
+      <c r="F31" s="142">
         <v>14</v>
       </c>
-      <c r="G31" s="150">
+      <c r="G31" s="142">
         <v>14</v>
       </c>
-      <c r="H31" s="150">
+      <c r="H31" s="142">
         <v>14</v>
       </c>
-      <c r="I31" s="150">
+      <c r="I31" s="142">
         <v>14</v>
       </c>
-      <c r="J31" s="150"/>
+      <c r="J31" s="142"/>
     </row>
     <row r="32" spans="1:10" ht="37.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="153" t="s">
+      <c r="B32" s="145" t="s">
         <v>198</v>
       </c>
-      <c r="C32" s="150">
+      <c r="C32" s="142">
         <v>6</v>
       </c>
-      <c r="D32" s="152">
+      <c r="D32" s="144">
         <v>1</v>
       </c>
-      <c r="E32" s="150">
+      <c r="E32" s="142">
         <v>12</v>
       </c>
-      <c r="F32" s="150">
+      <c r="F32" s="142">
         <v>11</v>
       </c>
-      <c r="G32" s="150">
+      <c r="G32" s="142">
         <v>11</v>
       </c>
-      <c r="H32" s="150">
+      <c r="H32" s="142">
         <v>11</v>
       </c>
-      <c r="I32" s="150">
+      <c r="I32" s="142">
         <v>11</v>
       </c>
-      <c r="J32" s="150"/>
+      <c r="J32" s="142"/>
     </row>
     <row r="33" spans="1:10" ht="37.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="148" t="s">
+      <c r="B33" s="140" t="s">
         <v>197</v>
       </c>
-      <c r="C33" s="91">
+      <c r="C33" s="86">
         <v>8</v>
       </c>
-      <c r="D33" s="147">
-        <v>2</v>
-      </c>
-      <c r="E33" s="91">
+      <c r="D33" s="139">
+        <v>2</v>
+      </c>
+      <c r="E33" s="86">
         <v>11</v>
       </c>
-      <c r="F33" s="91">
+      <c r="F33" s="86">
         <v>11</v>
       </c>
-      <c r="G33" s="91">
+      <c r="G33" s="86">
         <v>11</v>
       </c>
-      <c r="H33" s="91">
+      <c r="H33" s="86">
         <v>11</v>
       </c>
-      <c r="I33" s="91">
+      <c r="I33" s="86">
         <v>11</v>
       </c>
-      <c r="J33" s="91"/>
+      <c r="J33" s="86"/>
     </row>
     <row r="34" spans="1:10" ht="37.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="155" t="s">
+      <c r="B34" s="147" t="s">
         <v>196</v>
       </c>
-      <c r="C34" s="97">
+      <c r="C34" s="92">
         <v>5</v>
       </c>
-      <c r="D34" s="154">
-        <v>2</v>
-      </c>
-      <c r="E34" s="97">
+      <c r="D34" s="146">
+        <v>2</v>
+      </c>
+      <c r="E34" s="92">
         <v>11</v>
       </c>
-      <c r="F34" s="97">
+      <c r="F34" s="92">
         <v>10</v>
       </c>
-      <c r="G34" s="97">
+      <c r="G34" s="92">
         <v>13</v>
       </c>
-      <c r="H34" s="97">
+      <c r="H34" s="92">
         <v>13</v>
       </c>
-      <c r="I34" s="97">
+      <c r="I34" s="92">
         <v>13</v>
       </c>
-      <c r="J34" s="97"/>
+      <c r="J34" s="92"/>
     </row>
     <row r="35" spans="1:10" ht="37.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="153" t="s">
+      <c r="B35" s="145" t="s">
         <v>195</v>
       </c>
-      <c r="C35" s="150">
+      <c r="C35" s="142">
         <v>5</v>
       </c>
-      <c r="D35" s="152">
+      <c r="D35" s="144">
         <v>1</v>
       </c>
-      <c r="E35" s="151">
+      <c r="E35" s="143">
         <v>9</v>
       </c>
-      <c r="F35" s="150">
+      <c r="F35" s="142">
         <v>10</v>
       </c>
-      <c r="G35" s="150">
+      <c r="G35" s="142">
         <v>12</v>
       </c>
-      <c r="H35" s="150">
+      <c r="H35" s="142">
         <v>12</v>
       </c>
-      <c r="I35" s="150">
+      <c r="I35" s="142">
         <v>12</v>
       </c>
-      <c r="J35" s="150"/>
+      <c r="J35" s="142"/>
     </row>
     <row r="36" spans="1:10" ht="37.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="153" t="s">
+      <c r="B36" s="145" t="s">
         <v>194</v>
       </c>
-      <c r="C36" s="150">
-        <v>4</v>
-      </c>
-      <c r="D36" s="152">
+      <c r="C36" s="142">
+        <v>4</v>
+      </c>
+      <c r="D36" s="144">
         <v>0</v>
       </c>
-      <c r="E36" s="151">
+      <c r="E36" s="143">
         <v>8</v>
       </c>
-      <c r="F36" s="150">
+      <c r="F36" s="142">
         <v>9</v>
       </c>
-      <c r="G36" s="150">
+      <c r="G36" s="142">
         <v>12</v>
       </c>
-      <c r="H36" s="150">
+      <c r="H36" s="142">
         <v>12</v>
       </c>
-      <c r="I36" s="150">
+      <c r="I36" s="142">
         <v>12</v>
       </c>
-      <c r="J36" s="150"/>
+      <c r="J36" s="142"/>
     </row>
     <row r="37" spans="1:10" ht="37.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="149" t="s">
+      <c r="A37" s="141" t="s">
         <v>217</v>
       </c>
-      <c r="B37" s="148" t="s">
+      <c r="B37" s="140" t="s">
         <v>193</v>
       </c>
-      <c r="C37" s="91">
+      <c r="C37" s="86">
         <v>7</v>
       </c>
-      <c r="D37" s="147">
-        <v>4</v>
-      </c>
-      <c r="E37" s="91">
+      <c r="D37" s="139">
+        <v>4</v>
+      </c>
+      <c r="E37" s="86">
         <v>10</v>
       </c>
-      <c r="F37" s="91">
+      <c r="F37" s="86">
         <v>12</v>
       </c>
-      <c r="G37" s="91">
+      <c r="G37" s="86">
         <v>11</v>
       </c>
-      <c r="H37" s="91">
+      <c r="H37" s="86">
         <v>11</v>
       </c>
-      <c r="I37" s="91">
+      <c r="I37" s="86">
         <v>11</v>
       </c>
-      <c r="J37" s="91"/>
+      <c r="J37" s="86"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E38" s="146"/>
+      <c r="E38" s="138"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B40" s="119" t="s">
+      <c r="B40" s="113" t="s">
         <v>7</v>
       </c>
-      <c r="C40" s="112">
+      <c r="C40" s="106">
         <v>120</v>
       </c>
-      <c r="D40" s="89">
+      <c r="D40" s="84">
         <v>121</v>
       </c>
-      <c r="E40" s="89">
+      <c r="E40" s="84">
         <v>122</v>
       </c>
-      <c r="F40" s="89">
+      <c r="F40" s="84">
         <v>127</v>
       </c>
-      <c r="G40" s="89">
+      <c r="G40" s="84">
         <v>130</v>
       </c>
-      <c r="H40" s="89">
+      <c r="H40" s="84">
         <v>132</v>
       </c>
-      <c r="I40" s="145">
+      <c r="I40" s="137">
         <v>0.5</v>
       </c>
-      <c r="J40" s="89" t="s">
+      <c r="J40" s="84" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B41" s="119" t="s">
+      <c r="B41" s="113" t="s">
         <v>216</v>
       </c>
-      <c r="C41" s="89">
+      <c r="C41" s="84">
         <v>5</v>
       </c>
-      <c r="D41" s="89">
+      <c r="D41" s="84">
         <v>9</v>
       </c>
-      <c r="E41" s="89">
+      <c r="E41" s="84">
         <v>9</v>
       </c>
-      <c r="F41" s="89">
+      <c r="F41" s="84">
         <v>10</v>
       </c>
-      <c r="G41" s="89">
+      <c r="G41" s="84">
         <v>11</v>
       </c>
-      <c r="H41" s="89">
+      <c r="H41" s="84">
         <v>11</v>
       </c>
-      <c r="I41" s="89">
-        <f>H41/2</f>
+      <c r="I41" s="84">
+        <f t="shared" ref="I41:I64" si="0">H41/2</f>
         <v>5.5</v>
       </c>
-      <c r="J41" s="144">
+      <c r="J41" s="136">
         <f>C$40+(I41-C41)/(D41-C41)*(D$40-C$40)</f>
         <v>120.125</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B42" s="119" t="s">
+      <c r="B42" s="113" t="s">
         <v>215</v>
       </c>
-      <c r="C42" s="89">
+      <c r="C42" s="84">
         <v>6</v>
       </c>
-      <c r="D42" s="89">
+      <c r="D42" s="84">
         <v>9</v>
       </c>
-      <c r="E42" s="89">
+      <c r="E42" s="84">
         <v>9</v>
       </c>
-      <c r="F42" s="89">
+      <c r="F42" s="84">
         <v>10</v>
       </c>
-      <c r="G42" s="89">
+      <c r="G42" s="84">
         <v>11</v>
       </c>
-      <c r="H42" s="89">
+      <c r="H42" s="84">
         <v>11</v>
       </c>
-      <c r="I42" s="89">
-        <f>H42/2</f>
+      <c r="I42" s="84">
+        <f t="shared" si="0"/>
         <v>5.5</v>
       </c>
-      <c r="J42" s="144">
-        <f>C$40+(I42-C42)/(D42-C42)*(D$40-C$40)</f>
+      <c r="J42" s="136">
+        <f t="shared" ref="J42:J51" si="1">C$40+(I42-C42)/(D42-C42)*(D$40-C$40)</f>
         <v>119.83333333333333</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B43" s="119" t="s">
+      <c r="B43" s="113" t="s">
         <v>214</v>
       </c>
-      <c r="C43" s="89">
+      <c r="C43" s="84">
         <v>5</v>
       </c>
-      <c r="D43" s="89">
+      <c r="D43" s="84">
         <v>7</v>
       </c>
-      <c r="E43" s="89">
+      <c r="E43" s="84">
         <v>9</v>
       </c>
-      <c r="F43" s="89">
+      <c r="F43" s="84">
         <v>10</v>
       </c>
-      <c r="G43" s="89">
+      <c r="G43" s="84">
         <v>10</v>
       </c>
-      <c r="H43" s="89">
+      <c r="H43" s="84">
         <v>10</v>
       </c>
-      <c r="I43" s="89">
-        <f>H43/2</f>
+      <c r="I43" s="84">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="J43" s="144">
-        <f>C$40+(I43-C43)/(D43-C43)*(D$40-C$40)</f>
+      <c r="J43" s="136">
+        <f t="shared" si="1"/>
         <v>120</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B44" s="119" t="s">
+      <c r="B44" s="113" t="s">
         <v>213</v>
       </c>
-      <c r="C44" s="89">
-        <v>3</v>
-      </c>
-      <c r="D44" s="89">
+      <c r="C44" s="84">
+        <v>3</v>
+      </c>
+      <c r="D44" s="84">
         <v>6</v>
       </c>
-      <c r="E44" s="89">
+      <c r="E44" s="84">
         <v>6</v>
       </c>
-      <c r="F44" s="89">
+      <c r="F44" s="84">
         <v>7</v>
       </c>
-      <c r="G44" s="89">
+      <c r="G44" s="84">
         <v>7</v>
       </c>
-      <c r="H44" s="89">
+      <c r="H44" s="84">
         <v>7</v>
       </c>
-      <c r="I44" s="89">
-        <f>H44/2</f>
+      <c r="I44" s="84">
+        <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="J44" s="144">
-        <f>C$40+(I44-C44)/(D44-C44)*(D$40-C$40)</f>
+      <c r="J44" s="136">
+        <f t="shared" si="1"/>
         <v>120.16666666666667</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B45" s="119" t="s">
+      <c r="B45" s="113" t="s">
         <v>212</v>
       </c>
-      <c r="C45" s="89">
-        <v>3</v>
-      </c>
-      <c r="D45" s="89">
+      <c r="C45" s="84">
+        <v>3</v>
+      </c>
+      <c r="D45" s="84">
         <v>6</v>
       </c>
-      <c r="E45" s="89">
+      <c r="E45" s="84">
         <v>8</v>
       </c>
-      <c r="F45" s="89">
+      <c r="F45" s="84">
         <v>10</v>
       </c>
-      <c r="G45" s="89">
+      <c r="G45" s="84">
         <v>10</v>
       </c>
-      <c r="H45" s="89">
+      <c r="H45" s="84">
         <v>10</v>
       </c>
-      <c r="I45" s="89">
-        <f>H45/2</f>
+      <c r="I45" s="84">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="J45" s="144">
-        <f>C$40+(I45-C45)/(D45-C45)*(D$40-C$40)</f>
+      <c r="J45" s="136">
+        <f t="shared" si="1"/>
         <v>120.66666666666667</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B46" s="119" t="s">
+      <c r="B46" s="113" t="s">
         <v>211</v>
       </c>
-      <c r="C46" s="89">
-        <v>4</v>
-      </c>
-      <c r="D46" s="89">
+      <c r="C46" s="84">
+        <v>4</v>
+      </c>
+      <c r="D46" s="84">
         <v>8</v>
       </c>
-      <c r="E46" s="89">
+      <c r="E46" s="84">
         <v>9</v>
       </c>
-      <c r="F46" s="89">
+      <c r="F46" s="84">
         <v>11</v>
       </c>
-      <c r="G46" s="89">
+      <c r="G46" s="84">
         <v>13</v>
       </c>
-      <c r="H46" s="89">
+      <c r="H46" s="84">
         <v>12</v>
       </c>
-      <c r="I46" s="89">
-        <f>H46/2</f>
+      <c r="I46" s="84">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="J46" s="144">
-        <f>C$40+(I46-C46)/(D46-C46)*(D$40-C$40)</f>
+      <c r="J46" s="136">
+        <f t="shared" si="1"/>
         <v>120.5</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B47" s="119" t="s">
+      <c r="B47" s="113" t="s">
         <v>210</v>
       </c>
-      <c r="C47" s="89">
-        <v>3</v>
-      </c>
-      <c r="D47" s="89">
+      <c r="C47" s="84">
+        <v>3</v>
+      </c>
+      <c r="D47" s="84">
         <v>10</v>
       </c>
-      <c r="E47" s="89">
+      <c r="E47" s="84">
         <v>11</v>
       </c>
-      <c r="F47" s="89">
+      <c r="F47" s="84">
         <v>12</v>
       </c>
-      <c r="G47" s="89">
+      <c r="G47" s="84">
         <v>13</v>
       </c>
-      <c r="H47" s="89">
+      <c r="H47" s="84">
         <v>13</v>
       </c>
-      <c r="I47" s="89">
-        <f>H47/2</f>
+      <c r="I47" s="84">
+        <f t="shared" si="0"/>
         <v>6.5</v>
       </c>
-      <c r="J47" s="144">
-        <f>C$40+(I47-C47)/(D47-C47)*(D$40-C$40)</f>
+      <c r="J47" s="136">
+        <f t="shared" si="1"/>
         <v>120.5</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B48" s="119" t="s">
+      <c r="B48" s="113" t="s">
         <v>209</v>
       </c>
-      <c r="C48" s="89">
+      <c r="C48" s="84">
         <v>5</v>
       </c>
-      <c r="D48" s="89">
+      <c r="D48" s="84">
         <v>10</v>
       </c>
-      <c r="E48" s="89">
+      <c r="E48" s="84">
         <v>12</v>
       </c>
-      <c r="F48" s="89">
+      <c r="F48" s="84">
         <v>13</v>
       </c>
-      <c r="G48" s="89">
+      <c r="G48" s="84">
         <v>14</v>
       </c>
-      <c r="H48" s="89">
+      <c r="H48" s="84">
         <v>14</v>
       </c>
-      <c r="I48" s="89">
-        <f>H48/2</f>
+      <c r="I48" s="84">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="J48" s="144">
-        <f>C$40+(I48-C48)/(D48-C48)*(D$40-C$40)</f>
+      <c r="J48" s="136">
+        <f t="shared" si="1"/>
         <v>120.4</v>
       </c>
     </row>
     <row r="49" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B49" s="119" t="s">
+      <c r="B49" s="113" t="s">
         <v>208</v>
       </c>
-      <c r="C49" s="89">
-        <v>3</v>
-      </c>
-      <c r="D49" s="89">
+      <c r="C49" s="84">
+        <v>3</v>
+      </c>
+      <c r="D49" s="84">
         <v>9</v>
       </c>
-      <c r="E49" s="89">
+      <c r="E49" s="84">
         <v>10</v>
       </c>
-      <c r="F49" s="89">
+      <c r="F49" s="84">
         <v>10</v>
       </c>
-      <c r="G49" s="89">
+      <c r="G49" s="84">
         <v>10</v>
       </c>
-      <c r="H49" s="89">
+      <c r="H49" s="84">
         <v>11</v>
       </c>
-      <c r="I49" s="89">
-        <f>H49/2</f>
+      <c r="I49" s="84">
+        <f t="shared" si="0"/>
         <v>5.5</v>
       </c>
-      <c r="J49" s="144">
-        <f>C$40+(I49-C49)/(D49-C49)*(D$40-C$40)</f>
+      <c r="J49" s="136">
+        <f t="shared" si="1"/>
         <v>120.41666666666667</v>
       </c>
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B50" s="119" t="s">
+      <c r="B50" s="113" t="s">
         <v>207</v>
       </c>
-      <c r="C50" s="89">
+      <c r="C50" s="84">
         <v>5</v>
       </c>
-      <c r="D50" s="89">
+      <c r="D50" s="84">
         <v>11</v>
       </c>
-      <c r="E50" s="89">
+      <c r="E50" s="84">
         <v>14</v>
       </c>
-      <c r="F50" s="89">
+      <c r="F50" s="84">
         <v>16</v>
       </c>
-      <c r="G50" s="89">
+      <c r="G50" s="84">
         <v>16</v>
       </c>
-      <c r="H50" s="89">
+      <c r="H50" s="84">
         <v>16</v>
       </c>
-      <c r="I50" s="89">
-        <f>H50/2</f>
+      <c r="I50" s="84">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="J50" s="144">
-        <f>C$40+(I50-C50)/(D50-C50)*(D$40-C$40)</f>
+      <c r="J50" s="136">
+        <f t="shared" si="1"/>
         <v>120.5</v>
       </c>
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B51" s="119" t="s">
+      <c r="B51" s="113" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="89">
-        <v>2</v>
-      </c>
-      <c r="D51" s="89">
+      <c r="C51" s="84">
+        <v>2</v>
+      </c>
+      <c r="D51" s="84">
         <v>7</v>
       </c>
-      <c r="E51" s="89">
+      <c r="E51" s="84">
         <v>7</v>
       </c>
-      <c r="F51" s="89">
+      <c r="F51" s="84">
         <v>8</v>
       </c>
-      <c r="G51" s="89">
+      <c r="G51" s="84">
         <v>8</v>
       </c>
-      <c r="H51" s="89">
+      <c r="H51" s="84">
         <v>8</v>
       </c>
-      <c r="I51" s="89">
-        <f>H51/2</f>
-        <v>4</v>
-      </c>
-      <c r="J51" s="144">
-        <f>C$40+(I51-C51)/(D51-C51)*(D$40-C$40)</f>
+      <c r="I51" s="84">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="J51" s="136">
+        <f t="shared" si="1"/>
         <v>120.4</v>
       </c>
     </row>
     <row r="52" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B52" s="119" t="s">
+      <c r="B52" s="113" t="s">
         <v>205</v>
       </c>
-      <c r="C52" s="89">
+      <c r="C52" s="84">
         <v>1</v>
       </c>
-      <c r="D52" s="89">
-        <v>3</v>
-      </c>
-      <c r="E52" s="89">
-        <v>3</v>
-      </c>
-      <c r="F52" s="89">
+      <c r="D52" s="84">
+        <v>3</v>
+      </c>
+      <c r="E52" s="84">
+        <v>3</v>
+      </c>
+      <c r="F52" s="84">
         <v>8</v>
       </c>
-      <c r="G52" s="89">
+      <c r="G52" s="84">
         <v>8</v>
       </c>
-      <c r="H52" s="89">
+      <c r="H52" s="84">
         <v>8</v>
       </c>
-      <c r="I52" s="89">
-        <f>H52/2</f>
-        <v>4</v>
-      </c>
-      <c r="J52" s="144">
+      <c r="I52" s="84">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="J52" s="136">
         <f>E$40+(I52-E52)/(F52-E52)*(F$40-E$40)</f>
         <v>123</v>
       </c>
     </row>
     <row r="53" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B53" s="119" t="s">
+      <c r="B53" s="113" t="s">
         <v>204</v>
       </c>
-      <c r="C53" s="89">
+      <c r="C53" s="84">
         <v>7</v>
       </c>
-      <c r="D53" s="89">
+      <c r="D53" s="84">
         <v>13</v>
       </c>
-      <c r="E53" s="89">
+      <c r="E53" s="84">
         <v>15</v>
       </c>
-      <c r="F53" s="89">
+      <c r="F53" s="84">
         <v>15</v>
       </c>
-      <c r="G53" s="89">
+      <c r="G53" s="84">
         <v>15</v>
       </c>
-      <c r="H53" s="89">
+      <c r="H53" s="84">
         <v>15</v>
       </c>
-      <c r="I53" s="89">
-        <f>H53/2</f>
+      <c r="I53" s="84">
+        <f t="shared" si="0"/>
         <v>7.5</v>
       </c>
-      <c r="J53" s="144">
-        <f>C$40+(I53-C53)/(D53-C53)*(D$40-C$40)</f>
+      <c r="J53" s="136">
+        <f t="shared" ref="J53:J64" si="2">C$40+(I53-C53)/(D53-C53)*(D$40-C$40)</f>
         <v>120.08333333333333</v>
       </c>
     </row>
     <row r="54" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B54" s="119" t="s">
+      <c r="B54" s="113" t="s">
         <v>203</v>
       </c>
-      <c r="C54" s="89">
+      <c r="C54" s="84">
         <v>9</v>
       </c>
-      <c r="D54" s="89">
+      <c r="D54" s="84">
         <v>14</v>
       </c>
-      <c r="E54" s="89">
+      <c r="E54" s="84">
         <v>17</v>
       </c>
-      <c r="F54" s="89">
+      <c r="F54" s="84">
         <v>17</v>
       </c>
-      <c r="G54" s="89">
+      <c r="G54" s="84">
         <v>18</v>
       </c>
-      <c r="H54" s="89">
+      <c r="H54" s="84">
         <v>18</v>
       </c>
-      <c r="I54" s="89">
-        <f>H54/2</f>
+      <c r="I54" s="84">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="J54" s="144">
-        <f>C$40+(I54-C54)/(D54-C54)*(D$40-C$40)</f>
+      <c r="J54" s="136">
+        <f t="shared" si="2"/>
         <v>120</v>
       </c>
     </row>
     <row r="55" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B55" s="119" t="s">
+      <c r="B55" s="113" t="s">
         <v>202</v>
       </c>
-      <c r="C55" s="89">
+      <c r="C55" s="84">
         <v>6</v>
       </c>
-      <c r="D55" s="89">
+      <c r="D55" s="84">
         <v>9</v>
       </c>
-      <c r="E55" s="89">
+      <c r="E55" s="84">
         <v>10</v>
       </c>
-      <c r="F55" s="89">
+      <c r="F55" s="84">
         <v>10</v>
       </c>
-      <c r="G55" s="89">
+      <c r="G55" s="84">
         <v>10</v>
       </c>
-      <c r="H55" s="89">
+      <c r="H55" s="84">
         <v>10</v>
       </c>
-      <c r="I55" s="89">
-        <f>H55/2</f>
+      <c r="I55" s="84">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="J55" s="144">
-        <f>C$40+(I55-C55)/(D55-C55)*(D$40-C$40)</f>
+      <c r="J55" s="136">
+        <f t="shared" si="2"/>
         <v>119.66666666666667</v>
       </c>
     </row>
     <row r="56" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B56" s="119" t="s">
+      <c r="B56" s="113" t="s">
         <v>201</v>
       </c>
-      <c r="C56" s="89">
+      <c r="C56" s="84">
         <v>6</v>
       </c>
-      <c r="D56" s="89">
+      <c r="D56" s="84">
         <v>8</v>
       </c>
-      <c r="E56" s="89">
+      <c r="E56" s="84">
         <v>8</v>
       </c>
-      <c r="F56" s="89">
+      <c r="F56" s="84">
         <v>9</v>
       </c>
-      <c r="G56" s="89">
+      <c r="G56" s="84">
         <v>9</v>
       </c>
-      <c r="H56" s="89">
+      <c r="H56" s="84">
         <v>9</v>
       </c>
-      <c r="I56" s="89">
-        <f>H56/2</f>
+      <c r="I56" s="84">
+        <f t="shared" si="0"/>
         <v>4.5</v>
       </c>
-      <c r="J56" s="144">
-        <f>C$40+(I56-C56)/(D56-C56)*(D$40-C$40)</f>
+      <c r="J56" s="136">
+        <f t="shared" si="2"/>
         <v>119.25</v>
       </c>
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B57" s="119" t="s">
+      <c r="B57" s="113" t="s">
         <v>200</v>
       </c>
-      <c r="C57" s="89">
+      <c r="C57" s="84">
         <v>6</v>
       </c>
-      <c r="D57" s="89">
+      <c r="D57" s="84">
         <v>7</v>
       </c>
-      <c r="E57" s="89">
+      <c r="E57" s="84">
         <v>12</v>
       </c>
-      <c r="F57" s="89">
+      <c r="F57" s="84">
         <v>12</v>
       </c>
-      <c r="G57" s="89">
+      <c r="G57" s="84">
         <v>13</v>
       </c>
-      <c r="H57" s="89">
+      <c r="H57" s="84">
         <v>13</v>
       </c>
-      <c r="I57" s="89">
-        <f>H57/2</f>
+      <c r="I57" s="84">
+        <f t="shared" si="0"/>
         <v>6.5</v>
       </c>
-      <c r="J57" s="144">
-        <f>C$40+(I57-C57)/(D57-C57)*(D$40-C$40)</f>
+      <c r="J57" s="136">
+        <f t="shared" si="2"/>
         <v>120.5</v>
       </c>
     </row>
     <row r="58" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B58" s="119" t="s">
+      <c r="B58" s="113" t="s">
         <v>199</v>
       </c>
-      <c r="C58" s="89">
+      <c r="C58" s="84">
         <v>9</v>
       </c>
-      <c r="D58" s="89">
+      <c r="D58" s="84">
         <v>11</v>
       </c>
-      <c r="E58" s="89">
+      <c r="E58" s="84">
         <v>14</v>
       </c>
-      <c r="F58" s="89">
+      <c r="F58" s="84">
         <v>14</v>
       </c>
-      <c r="G58" s="89">
+      <c r="G58" s="84">
         <v>14</v>
       </c>
-      <c r="H58" s="89">
+      <c r="H58" s="84">
         <v>14</v>
       </c>
-      <c r="I58" s="89">
-        <f>H58/2</f>
+      <c r="I58" s="84">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="J58" s="144">
-        <f>C$40+(I58-C58)/(D58-C58)*(D$40-C$40)</f>
+      <c r="J58" s="136">
+        <f t="shared" si="2"/>
         <v>119</v>
       </c>
     </row>
     <row r="59" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B59" s="119" t="s">
+      <c r="B59" s="113" t="s">
         <v>198</v>
       </c>
-      <c r="C59" s="89">
+      <c r="C59" s="84">
         <v>6</v>
       </c>
-      <c r="D59" s="89">
+      <c r="D59" s="84">
         <v>12</v>
       </c>
-      <c r="E59" s="89">
+      <c r="E59" s="84">
         <v>11</v>
       </c>
-      <c r="F59" s="89">
+      <c r="F59" s="84">
         <v>11</v>
       </c>
-      <c r="G59" s="89">
+      <c r="G59" s="84">
         <v>11</v>
       </c>
-      <c r="H59" s="89">
+      <c r="H59" s="84">
         <v>11</v>
       </c>
-      <c r="I59" s="89">
-        <f>H59/2</f>
+      <c r="I59" s="84">
+        <f t="shared" si="0"/>
         <v>5.5</v>
       </c>
-      <c r="J59" s="144">
-        <f>C$40+(I59-C59)/(D59-C59)*(D$40-C$40)</f>
+      <c r="J59" s="136">
+        <f t="shared" si="2"/>
         <v>119.91666666666667</v>
       </c>
     </row>
     <row r="60" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B60" s="119" t="s">
+      <c r="B60" s="113" t="s">
         <v>197</v>
       </c>
-      <c r="C60" s="89">
+      <c r="C60" s="84">
         <v>8</v>
       </c>
-      <c r="D60" s="89">
+      <c r="D60" s="84">
         <v>11</v>
       </c>
-      <c r="E60" s="89">
+      <c r="E60" s="84">
         <v>11</v>
       </c>
-      <c r="F60" s="89">
+      <c r="F60" s="84">
         <v>11</v>
       </c>
-      <c r="G60" s="89">
+      <c r="G60" s="84">
         <v>11</v>
       </c>
-      <c r="H60" s="89">
+      <c r="H60" s="84">
         <v>11</v>
       </c>
-      <c r="I60" s="89">
-        <f>H60/2</f>
+      <c r="I60" s="84">
+        <f t="shared" si="0"/>
         <v>5.5</v>
       </c>
-      <c r="J60" s="144">
-        <f>C$40+(I60-C60)/(D60-C60)*(D$40-C$40)</f>
+      <c r="J60" s="136">
+        <f t="shared" si="2"/>
         <v>119.16666666666667</v>
       </c>
     </row>
     <row r="61" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B61" s="119" t="s">
+      <c r="B61" s="113" t="s">
         <v>196</v>
       </c>
-      <c r="C61" s="89">
+      <c r="C61" s="84">
         <v>5</v>
       </c>
-      <c r="D61" s="89">
+      <c r="D61" s="84">
         <v>11</v>
       </c>
-      <c r="E61" s="89">
+      <c r="E61" s="84">
         <v>10</v>
       </c>
-      <c r="F61" s="89">
+      <c r="F61" s="84">
         <v>13</v>
       </c>
-      <c r="G61" s="89">
+      <c r="G61" s="84">
         <v>13</v>
       </c>
-      <c r="H61" s="89">
+      <c r="H61" s="84">
         <v>13</v>
       </c>
-      <c r="I61" s="89">
-        <f>H61/2</f>
+      <c r="I61" s="84">
+        <f t="shared" si="0"/>
         <v>6.5</v>
       </c>
-      <c r="J61" s="144">
-        <f>C$40+(I61-C61)/(D61-C61)*(D$40-C$40)</f>
+      <c r="J61" s="136">
+        <f t="shared" si="2"/>
         <v>120.25</v>
       </c>
     </row>
     <row r="62" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B62" s="119" t="s">
+      <c r="B62" s="113" t="s">
         <v>195</v>
       </c>
-      <c r="C62" s="89">
+      <c r="C62" s="84">
         <v>5</v>
       </c>
-      <c r="D62" s="89">
+      <c r="D62" s="84">
         <v>9</v>
       </c>
-      <c r="E62" s="89">
+      <c r="E62" s="84">
         <v>10</v>
       </c>
-      <c r="F62" s="89">
+      <c r="F62" s="84">
         <v>12</v>
       </c>
-      <c r="G62" s="89">
+      <c r="G62" s="84">
         <v>12</v>
       </c>
-      <c r="H62" s="89">
+      <c r="H62" s="84">
         <v>12</v>
       </c>
-      <c r="I62" s="89">
-        <f>H62/2</f>
+      <c r="I62" s="84">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="J62" s="144">
-        <f>C$40+(I62-C62)/(D62-C62)*(D$40-C$40)</f>
+      <c r="J62" s="136">
+        <f t="shared" si="2"/>
         <v>120.25</v>
       </c>
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B63" s="119" t="s">
+      <c r="B63" s="113" t="s">
         <v>194</v>
       </c>
-      <c r="C63" s="89">
-        <v>4</v>
-      </c>
-      <c r="D63" s="89">
+      <c r="C63" s="84">
+        <v>4</v>
+      </c>
+      <c r="D63" s="84">
         <v>8</v>
       </c>
-      <c r="E63" s="89">
+      <c r="E63" s="84">
         <v>9</v>
       </c>
-      <c r="F63" s="89">
+      <c r="F63" s="84">
         <v>12</v>
       </c>
-      <c r="G63" s="89">
+      <c r="G63" s="84">
         <v>12</v>
       </c>
-      <c r="H63" s="89">
+      <c r="H63" s="84">
         <v>12</v>
       </c>
-      <c r="I63" s="89">
-        <f>H63/2</f>
+      <c r="I63" s="84">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="J63" s="144">
-        <f>C$40+(I63-C63)/(D63-C63)*(D$40-C$40)</f>
+      <c r="J63" s="136">
+        <f t="shared" si="2"/>
         <v>120.5</v>
       </c>
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B64" s="119" t="s">
+      <c r="B64" s="113" t="s">
         <v>193</v>
       </c>
-      <c r="C64" s="89">
+      <c r="C64" s="84">
         <v>7</v>
       </c>
-      <c r="D64" s="89">
+      <c r="D64" s="84">
         <v>10</v>
       </c>
-      <c r="E64" s="89">
+      <c r="E64" s="84">
         <v>12</v>
       </c>
-      <c r="F64" s="89">
+      <c r="F64" s="84">
         <v>11</v>
       </c>
-      <c r="G64" s="89">
+      <c r="G64" s="84">
         <v>11</v>
       </c>
-      <c r="H64" s="89">
+      <c r="H64" s="84">
         <v>11</v>
       </c>
-      <c r="I64" s="89">
-        <f>H64/2</f>
+      <c r="I64" s="84">
+        <f t="shared" si="0"/>
         <v>5.5</v>
       </c>
-      <c r="J64" s="144">
-        <f>C$40+(I64-C64)/(D64-C64)*(D$40-C$40)</f>
+      <c r="J64" s="136">
+        <f t="shared" si="2"/>
         <v>119.5</v>
       </c>
     </row>
@@ -7633,953 +7633,953 @@
   <dimension ref="A1:M42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="89"/>
-    <col min="2" max="2" width="7.7109375" style="119" customWidth="1"/>
-    <col min="3" max="3" width="6.7109375" style="119" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" style="119" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="89"/>
+    <col min="1" max="1" width="9.140625" style="84"/>
+    <col min="2" max="2" width="7.7109375" style="113" customWidth="1"/>
+    <col min="3" max="3" width="6.7109375" style="113" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" style="113" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="84"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="22.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="184">
+      <c r="A1" s="176">
         <v>2020</v>
       </c>
-      <c r="B1" s="185" t="s">
+      <c r="B1" s="177" t="s">
         <v>231</v>
       </c>
-      <c r="C1" s="185"/>
-      <c r="D1" s="184" t="s">
+      <c r="C1" s="177"/>
+      <c r="D1" s="176" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="119"/>
-      <c r="B2" s="89"/>
-      <c r="C2" s="89"/>
+      <c r="A2" s="113"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="84"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="119"/>
-      <c r="B3" s="183" t="s">
+      <c r="A3" s="113"/>
+      <c r="B3" s="175" t="s">
         <v>265</v>
       </c>
-      <c r="C3" s="183"/>
+      <c r="C3" s="175"/>
     </row>
     <row r="4" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="116" t="s">
+      <c r="A4" s="110" t="s">
         <v>264</v>
       </c>
-      <c r="B4" s="183"/>
-      <c r="C4" s="183"/>
+      <c r="B4" s="175"/>
+      <c r="C4" s="175"/>
     </row>
     <row r="5" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="116" t="s">
+      <c r="A5" s="110" t="s">
         <v>263</v>
       </c>
-      <c r="B5" s="183"/>
-      <c r="C5" s="183"/>
+      <c r="B5" s="175"/>
+      <c r="C5" s="175"/>
     </row>
     <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="89" t="s">
+      <c r="A6" s="84" t="s">
         <v>262</v>
       </c>
-      <c r="B6" s="116"/>
-      <c r="C6" s="116"/>
-      <c r="D6" s="207"/>
+      <c r="B6" s="110"/>
+      <c r="C6" s="110"/>
+      <c r="D6" s="197"/>
     </row>
     <row r="7" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D7" s="207"/>
+      <c r="D7" s="197"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B9" s="182" t="s">
+      <c r="B9" s="174" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="206"/>
-      <c r="D9" s="181">
+      <c r="C9" s="196"/>
+      <c r="D9" s="173">
         <v>43957</v>
       </c>
-      <c r="E9" s="205"/>
-      <c r="F9" s="179">
+      <c r="E9" s="195"/>
+      <c r="F9" s="171">
         <v>43960</v>
       </c>
-      <c r="G9" s="179">
+      <c r="G9" s="171">
         <v>43962</v>
       </c>
-      <c r="H9" s="179"/>
-      <c r="I9" s="179"/>
+      <c r="H9" s="171"/>
+      <c r="I9" s="171"/>
     </row>
     <row r="10" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="178" t="s">
+      <c r="B10" s="170" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="178"/>
-      <c r="D10" s="177">
+      <c r="C10" s="170"/>
+      <c r="D10" s="169">
         <v>127</v>
       </c>
-      <c r="E10" s="204"/>
-      <c r="F10" s="175">
+      <c r="E10" s="194"/>
+      <c r="F10" s="167">
         <v>130</v>
       </c>
-      <c r="G10" s="175">
+      <c r="G10" s="167">
         <v>132</v>
       </c>
-      <c r="H10" s="175"/>
-      <c r="I10" s="175"/>
-    </row>
-    <row r="11" spans="1:13" s="169" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="B11" s="173" t="s">
+      <c r="H10" s="167"/>
+      <c r="I10" s="167"/>
+    </row>
+    <row r="11" spans="1:13" s="161" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="B11" s="165" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="173"/>
-      <c r="D11" s="172" t="s">
+      <c r="C11" s="165"/>
+      <c r="D11" s="164" t="s">
         <v>44</v>
       </c>
-      <c r="E11" s="203"/>
-      <c r="F11" s="170" t="s">
+      <c r="E11" s="193"/>
+      <c r="F11" s="162" t="s">
         <v>44</v>
       </c>
-      <c r="G11" s="170" t="s">
+      <c r="G11" s="162" t="s">
         <v>44</v>
       </c>
-      <c r="H11" s="170"/>
-      <c r="I11" s="170"/>
-    </row>
-    <row r="12" spans="1:13" s="119" customFormat="1" ht="37.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="164" t="s">
+      <c r="H11" s="162"/>
+      <c r="I11" s="162"/>
+    </row>
+    <row r="12" spans="1:13" s="113" customFormat="1" ht="37.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="156" t="s">
         <v>227</v>
       </c>
-      <c r="C12" s="202" t="s">
+      <c r="C12" s="192" t="s">
         <v>261</v>
       </c>
-      <c r="D12" s="201" t="s">
+      <c r="D12" s="191" t="s">
         <v>259</v>
       </c>
-      <c r="E12" s="200" t="s">
+      <c r="E12" s="190" t="s">
         <v>260</v>
       </c>
-      <c r="F12" s="199" t="s">
+      <c r="F12" s="189" t="s">
         <v>259</v>
       </c>
-      <c r="G12" s="199" t="s">
+      <c r="G12" s="189" t="s">
         <v>259</v>
       </c>
-      <c r="H12" s="198"/>
-      <c r="I12" s="198"/>
-      <c r="K12" s="197">
+      <c r="H12" s="188"/>
+      <c r="I12" s="188"/>
+      <c r="K12" s="187">
         <v>0.5</v>
       </c>
-      <c r="L12" s="119" t="s">
+      <c r="L12" s="113" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="190" t="s">
+      <c r="B13" s="180" t="s">
         <v>216</v>
       </c>
-      <c r="C13" s="97">
+      <c r="C13" s="92">
         <v>11</v>
       </c>
-      <c r="D13" s="189">
-        <v>2</v>
-      </c>
-      <c r="E13" s="152">
-        <v>3</v>
-      </c>
-      <c r="F13" s="150">
+      <c r="D13" s="179">
+        <v>2</v>
+      </c>
+      <c r="E13" s="144">
+        <v>3</v>
+      </c>
+      <c r="F13" s="142">
         <v>8</v>
       </c>
-      <c r="G13" s="150">
+      <c r="G13" s="142">
         <v>9</v>
       </c>
-      <c r="H13" s="150"/>
-      <c r="I13" s="150"/>
-      <c r="K13" s="89">
-        <f>C13/2</f>
+      <c r="H13" s="142"/>
+      <c r="I13" s="142"/>
+      <c r="K13" s="84">
+        <f t="shared" ref="K13:K36" si="0">C13/2</f>
         <v>5.5</v>
       </c>
-      <c r="L13" s="144">
+      <c r="L13" s="136">
         <f>D$10+(K13-D13)/(F13-D13)*(F$10-D$10)</f>
         <v>128.75</v>
       </c>
-      <c r="M13" s="89" t="s">
+      <c r="M13" s="84" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="190" t="s">
+      <c r="B14" s="180" t="s">
         <v>215</v>
       </c>
-      <c r="C14" s="150">
+      <c r="C14" s="142">
         <v>11</v>
       </c>
-      <c r="D14" s="189">
+      <c r="D14" s="179">
         <v>1</v>
       </c>
-      <c r="E14" s="152">
-        <v>2</v>
-      </c>
-      <c r="F14" s="150">
+      <c r="E14" s="144">
+        <v>2</v>
+      </c>
+      <c r="F14" s="142">
         <v>8</v>
       </c>
-      <c r="G14" s="150">
+      <c r="G14" s="142">
         <v>10</v>
       </c>
-      <c r="H14" s="150"/>
-      <c r="I14" s="150"/>
-      <c r="K14" s="89">
-        <f>C14/2</f>
+      <c r="H14" s="142"/>
+      <c r="I14" s="142"/>
+      <c r="K14" s="84">
+        <f t="shared" si="0"/>
         <v>5.5</v>
       </c>
-      <c r="L14" s="144">
+      <c r="L14" s="136">
         <f>D$10+(K14-D14)/(F14-D14)*(F$10-D$10)</f>
         <v>128.92857142857142</v>
       </c>
-      <c r="M14" s="89" t="s">
+      <c r="M14" s="84" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="190" t="s">
+      <c r="B15" s="180" t="s">
         <v>214</v>
       </c>
-      <c r="C15" s="150">
+      <c r="C15" s="142">
         <v>10</v>
       </c>
-      <c r="D15" s="189">
+      <c r="D15" s="179">
         <v>1</v>
       </c>
-      <c r="E15" s="152">
-        <v>2</v>
-      </c>
-      <c r="F15" s="150">
+      <c r="E15" s="144">
+        <v>2</v>
+      </c>
+      <c r="F15" s="142">
         <v>7</v>
       </c>
-      <c r="G15" s="150">
+      <c r="G15" s="142">
         <v>10</v>
       </c>
-      <c r="H15" s="150"/>
-      <c r="I15" s="150"/>
-      <c r="K15" s="89">
-        <f>C15/2</f>
+      <c r="H15" s="142"/>
+      <c r="I15" s="142"/>
+      <c r="K15" s="84">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L15" s="144">
+      <c r="L15" s="136">
         <f>D$10+(K15-D15)/(F15-D15)*(F$10-D$10)</f>
         <v>129</v>
       </c>
-      <c r="M15" s="89" t="s">
+      <c r="M15" s="84" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="196" t="s">
+      <c r="B16" s="186" t="s">
         <v>213</v>
       </c>
-      <c r="C16" s="91">
+      <c r="C16" s="86">
         <v>7</v>
       </c>
-      <c r="D16" s="195">
+      <c r="D16" s="185">
         <v>0</v>
       </c>
-      <c r="E16" s="147">
-        <v>3</v>
-      </c>
-      <c r="F16" s="91">
+      <c r="E16" s="139">
+        <v>3</v>
+      </c>
+      <c r="F16" s="86">
         <v>6</v>
       </c>
-      <c r="G16" s="91">
+      <c r="G16" s="86">
         <v>7</v>
       </c>
-      <c r="H16" s="91"/>
-      <c r="I16" s="91"/>
-      <c r="K16" s="89">
-        <f>C16/2</f>
+      <c r="H16" s="86"/>
+      <c r="I16" s="86"/>
+      <c r="K16" s="84">
+        <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="L16" s="144">
+      <c r="L16" s="136">
         <f>D$10+(K16-D16)/(F16-D16)*(F$10-D$10)</f>
         <v>128.75</v>
       </c>
-      <c r="M16" s="89" t="s">
+      <c r="M16" s="84" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="17" spans="2:13" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="194" t="s">
+      <c r="B17" s="184" t="s">
         <v>212</v>
       </c>
-      <c r="C17" s="97">
+      <c r="C17" s="92">
         <v>10</v>
       </c>
-      <c r="D17" s="193">
+      <c r="D17" s="183">
         <v>0</v>
       </c>
-      <c r="E17" s="192">
+      <c r="E17" s="182">
         <v>1</v>
       </c>
-      <c r="F17" s="191">
-        <v>4</v>
-      </c>
-      <c r="G17" s="191">
+      <c r="F17" s="181">
+        <v>4</v>
+      </c>
+      <c r="G17" s="181">
         <v>7</v>
       </c>
-      <c r="H17" s="191"/>
-      <c r="I17" s="191"/>
-      <c r="K17" s="89">
-        <f>C17/2</f>
+      <c r="H17" s="181"/>
+      <c r="I17" s="181"/>
+      <c r="K17" s="84">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L17" s="144">
+      <c r="L17" s="136">
         <f>F$10+(K17-F17)/(G17-F17)*(G$10-F$10)</f>
         <v>130.66666666666666</v>
       </c>
-      <c r="M17" s="89" t="s">
+      <c r="M17" s="84" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="18" spans="2:13" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="190" t="s">
+      <c r="B18" s="180" t="s">
         <v>211</v>
       </c>
-      <c r="C18" s="150">
+      <c r="C18" s="142">
         <v>12</v>
       </c>
-      <c r="D18" s="189">
+      <c r="D18" s="179">
         <v>1</v>
       </c>
-      <c r="E18" s="152">
+      <c r="E18" s="144">
         <v>1</v>
       </c>
-      <c r="F18" s="150">
+      <c r="F18" s="142">
         <v>5</v>
       </c>
-      <c r="G18" s="150">
+      <c r="G18" s="142">
         <v>10</v>
       </c>
-      <c r="H18" s="150"/>
-      <c r="I18" s="150"/>
-      <c r="K18" s="89">
-        <f>C18/2</f>
+      <c r="H18" s="142"/>
+      <c r="I18" s="142"/>
+      <c r="K18" s="84">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="L18" s="144">
+      <c r="L18" s="136">
         <f>F$10+(K18-F18)/(G18-F18)*(G$10-F$10)</f>
         <v>130.4</v>
       </c>
-      <c r="M18" s="89" t="s">
+      <c r="M18" s="84" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="19" spans="2:13" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="190" t="s">
+      <c r="B19" s="180" t="s">
         <v>210</v>
       </c>
-      <c r="C19" s="150">
+      <c r="C19" s="142">
         <v>13</v>
       </c>
-      <c r="D19" s="189">
+      <c r="D19" s="179">
         <v>0</v>
       </c>
-      <c r="E19" s="152">
-        <v>2</v>
-      </c>
-      <c r="F19" s="150">
+      <c r="E19" s="144">
+        <v>2</v>
+      </c>
+      <c r="F19" s="142">
         <v>6</v>
       </c>
-      <c r="G19" s="150">
+      <c r="G19" s="142">
         <v>12</v>
       </c>
-      <c r="H19" s="150"/>
-      <c r="I19" s="150"/>
-      <c r="K19" s="89">
-        <f>C19/2</f>
+      <c r="H19" s="142"/>
+      <c r="I19" s="142"/>
+      <c r="K19" s="84">
+        <f t="shared" si="0"/>
         <v>6.5</v>
       </c>
-      <c r="L19" s="144">
+      <c r="L19" s="136">
         <f>F$10+(K19-F19)/(G19-F19)*(G$10-F$10)</f>
         <v>130.16666666666666</v>
       </c>
-      <c r="M19" s="89" t="s">
+      <c r="M19" s="84" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="20" spans="2:13" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="196" t="s">
+      <c r="B20" s="186" t="s">
         <v>209</v>
       </c>
-      <c r="C20" s="91">
+      <c r="C20" s="86">
         <v>14</v>
       </c>
-      <c r="D20" s="195">
+      <c r="D20" s="185">
         <v>0</v>
       </c>
-      <c r="E20" s="147">
-        <v>2</v>
-      </c>
-      <c r="F20" s="91">
+      <c r="E20" s="139">
+        <v>2</v>
+      </c>
+      <c r="F20" s="86">
         <v>9</v>
       </c>
-      <c r="G20" s="91">
+      <c r="G20" s="86">
         <v>13</v>
       </c>
-      <c r="H20" s="91"/>
-      <c r="I20" s="91"/>
-      <c r="K20" s="89">
-        <f>C20/2</f>
+      <c r="H20" s="86"/>
+      <c r="I20" s="86"/>
+      <c r="K20" s="84">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="L20" s="144">
+      <c r="L20" s="136">
         <f>D$10+(K20-D20)/(F20-D20)*(F$10-D$10)</f>
         <v>129.33333333333334</v>
       </c>
-      <c r="M20" s="89" t="s">
+      <c r="M20" s="84" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="21" spans="2:13" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="194" t="s">
+      <c r="B21" s="184" t="s">
         <v>208</v>
       </c>
-      <c r="C21" s="160">
+      <c r="C21" s="152">
         <v>11</v>
       </c>
-      <c r="D21" s="193">
+      <c r="D21" s="183">
         <v>0</v>
       </c>
-      <c r="E21" s="192">
+      <c r="E21" s="182">
         <v>1</v>
       </c>
-      <c r="F21" s="191">
-        <v>4</v>
-      </c>
-      <c r="G21" s="191">
+      <c r="F21" s="181">
+        <v>4</v>
+      </c>
+      <c r="G21" s="181">
         <v>10</v>
       </c>
-      <c r="H21" s="191"/>
-      <c r="I21" s="191"/>
-      <c r="K21" s="89">
-        <f>C21/2</f>
+      <c r="H21" s="181"/>
+      <c r="I21" s="181"/>
+      <c r="K21" s="84">
+        <f t="shared" si="0"/>
         <v>5.5</v>
       </c>
-      <c r="L21" s="144">
+      <c r="L21" s="136">
         <f>F$10+(K21-F21)/(G21-F21)*(G$10-F$10)</f>
         <v>130.5</v>
       </c>
-      <c r="M21" s="89" t="s">
+      <c r="M21" s="84" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="22" spans="2:13" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="190" t="s">
+      <c r="B22" s="180" t="s">
         <v>207</v>
       </c>
-      <c r="C22" s="150">
+      <c r="C22" s="142">
         <v>16</v>
       </c>
-      <c r="D22" s="189">
+      <c r="D22" s="179">
         <v>0</v>
       </c>
-      <c r="E22" s="152">
-        <v>3</v>
-      </c>
-      <c r="F22" s="150">
+      <c r="E22" s="144">
+        <v>3</v>
+      </c>
+      <c r="F22" s="142">
         <v>8</v>
       </c>
-      <c r="G22" s="150">
+      <c r="G22" s="142">
         <v>12</v>
       </c>
-      <c r="H22" s="150"/>
-      <c r="I22" s="150"/>
-      <c r="K22" s="89">
-        <f>C22/2</f>
+      <c r="H22" s="142"/>
+      <c r="I22" s="142"/>
+      <c r="K22" s="84">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="L22" s="144">
+      <c r="L22" s="136">
         <f>D$10+(K22-D22)/(F22-D22)*(F$10-D$10)</f>
         <v>130</v>
       </c>
-      <c r="M22" s="89" t="s">
+      <c r="M22" s="84" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="23" spans="2:13" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="190" t="s">
+      <c r="B23" s="180" t="s">
         <v>206</v>
       </c>
-      <c r="C23" s="150">
+      <c r="C23" s="142">
         <v>8</v>
       </c>
-      <c r="D23" s="189">
+      <c r="D23" s="179">
         <v>0</v>
       </c>
-      <c r="E23" s="152">
-        <v>2</v>
-      </c>
-      <c r="F23" s="150">
+      <c r="E23" s="144">
+        <v>2</v>
+      </c>
+      <c r="F23" s="142">
         <v>7</v>
       </c>
-      <c r="G23" s="150">
+      <c r="G23" s="142">
         <v>7</v>
       </c>
-      <c r="H23" s="150"/>
-      <c r="I23" s="150"/>
-      <c r="K23" s="89">
-        <f>C23/2</f>
-        <v>4</v>
-      </c>
-      <c r="L23" s="144">
+      <c r="H23" s="142"/>
+      <c r="I23" s="142"/>
+      <c r="K23" s="84">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="L23" s="136">
         <f>D$10+(K23-D23)/(F23-D23)*(F$10-D$10)</f>
         <v>128.71428571428572</v>
       </c>
-      <c r="M23" s="89" t="s">
+      <c r="M23" s="84" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="24" spans="2:13" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="196" t="s">
+      <c r="B24" s="186" t="s">
         <v>205</v>
       </c>
-      <c r="C24" s="91">
+      <c r="C24" s="86">
         <v>8</v>
       </c>
-      <c r="D24" s="195">
+      <c r="D24" s="185">
         <v>0</v>
       </c>
-      <c r="E24" s="147">
+      <c r="E24" s="139">
         <v>0</v>
       </c>
-      <c r="F24" s="91">
-        <v>2</v>
-      </c>
-      <c r="G24" s="91">
-        <v>4</v>
-      </c>
-      <c r="H24" s="91"/>
-      <c r="I24" s="91"/>
-      <c r="K24" s="89">
-        <f>C24/2</f>
-        <v>4</v>
-      </c>
-      <c r="L24" s="144">
+      <c r="F24" s="86">
+        <v>2</v>
+      </c>
+      <c r="G24" s="86">
+        <v>4</v>
+      </c>
+      <c r="H24" s="86"/>
+      <c r="I24" s="86"/>
+      <c r="K24" s="84">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="L24" s="136">
         <f>F$10+(K24-F24)/(G24-F24)*(G$10-F$10)</f>
         <v>132</v>
       </c>
-      <c r="M24" s="89" t="s">
+      <c r="M24" s="84" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="25" spans="2:13" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="194" t="s">
+      <c r="B25" s="184" t="s">
         <v>204</v>
       </c>
-      <c r="C25" s="97">
+      <c r="C25" s="92">
         <v>15</v>
       </c>
-      <c r="D25" s="193">
-        <v>2</v>
-      </c>
-      <c r="E25" s="192">
-        <v>3</v>
-      </c>
-      <c r="F25" s="191">
+      <c r="D25" s="183">
+        <v>2</v>
+      </c>
+      <c r="E25" s="182">
+        <v>3</v>
+      </c>
+      <c r="F25" s="181">
         <v>11</v>
       </c>
-      <c r="G25" s="191">
+      <c r="G25" s="181">
         <v>13</v>
       </c>
-      <c r="H25" s="191"/>
-      <c r="I25" s="191"/>
-      <c r="K25" s="89">
-        <f>C25/2</f>
+      <c r="H25" s="181"/>
+      <c r="I25" s="181"/>
+      <c r="K25" s="84">
+        <f t="shared" si="0"/>
         <v>7.5</v>
       </c>
-      <c r="L25" s="144">
-        <f>D$10+(K25-D25)/(F25-D25)*(F$10-D$10)</f>
+      <c r="L25" s="136">
+        <f t="shared" ref="L25:L32" si="1">D$10+(K25-D25)/(F25-D25)*(F$10-D$10)</f>
         <v>128.83333333333334</v>
       </c>
-      <c r="M25" s="89" t="s">
+      <c r="M25" s="84" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="26" spans="2:13" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="190" t="s">
+      <c r="B26" s="180" t="s">
         <v>203</v>
       </c>
-      <c r="C26" s="150">
+      <c r="C26" s="142">
         <v>18</v>
       </c>
-      <c r="D26" s="189">
-        <v>2</v>
-      </c>
-      <c r="E26" s="152">
-        <v>2</v>
-      </c>
-      <c r="F26" s="150">
+      <c r="D26" s="179">
+        <v>2</v>
+      </c>
+      <c r="E26" s="144">
+        <v>2</v>
+      </c>
+      <c r="F26" s="142">
         <v>11</v>
       </c>
-      <c r="G26" s="150">
+      <c r="G26" s="142">
         <v>15</v>
       </c>
-      <c r="H26" s="150"/>
-      <c r="I26" s="150"/>
-      <c r="K26" s="89">
-        <f>C26/2</f>
+      <c r="H26" s="142"/>
+      <c r="I26" s="142"/>
+      <c r="K26" s="84">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="L26" s="144">
-        <f>D$10+(K26-D26)/(F26-D26)*(F$10-D$10)</f>
+      <c r="L26" s="136">
+        <f t="shared" si="1"/>
         <v>129.33333333333334</v>
       </c>
-      <c r="M26" s="89" t="s">
+      <c r="M26" s="84" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="27" spans="2:13" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="190" t="s">
+      <c r="B27" s="180" t="s">
         <v>202</v>
       </c>
-      <c r="C27" s="150">
+      <c r="C27" s="142">
         <v>10</v>
       </c>
-      <c r="D27" s="189">
-        <v>2</v>
-      </c>
-      <c r="E27" s="152">
-        <v>3</v>
-      </c>
-      <c r="F27" s="150">
+      <c r="D27" s="179">
+        <v>2</v>
+      </c>
+      <c r="E27" s="144">
+        <v>3</v>
+      </c>
+      <c r="F27" s="142">
         <v>8</v>
       </c>
-      <c r="G27" s="150">
+      <c r="G27" s="142">
         <v>9</v>
       </c>
-      <c r="H27" s="150"/>
-      <c r="I27" s="150"/>
-      <c r="K27" s="89">
-        <f>C27/2</f>
+      <c r="H27" s="142"/>
+      <c r="I27" s="142"/>
+      <c r="K27" s="84">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L27" s="144">
-        <f>D$10+(K27-D27)/(F27-D27)*(F$10-D$10)</f>
+      <c r="L27" s="136">
+        <f t="shared" si="1"/>
         <v>128.5</v>
       </c>
-      <c r="M27" s="89" t="s">
+      <c r="M27" s="84" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="28" spans="2:13" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="196" t="s">
+      <c r="B28" s="186" t="s">
         <v>201</v>
       </c>
-      <c r="C28" s="91">
+      <c r="C28" s="86">
         <v>9</v>
       </c>
-      <c r="D28" s="195">
+      <c r="D28" s="185">
         <v>1</v>
       </c>
-      <c r="E28" s="147">
-        <v>2</v>
-      </c>
-      <c r="F28" s="91">
+      <c r="E28" s="139">
+        <v>2</v>
+      </c>
+      <c r="F28" s="86">
         <v>6</v>
       </c>
-      <c r="G28" s="91">
+      <c r="G28" s="86">
         <v>8</v>
       </c>
-      <c r="H28" s="91"/>
-      <c r="I28" s="91"/>
-      <c r="K28" s="89">
-        <f>C28/2</f>
+      <c r="H28" s="86"/>
+      <c r="I28" s="86"/>
+      <c r="K28" s="84">
+        <f t="shared" si="0"/>
         <v>4.5</v>
       </c>
-      <c r="L28" s="144">
-        <f>D$10+(K28-D28)/(F28-D28)*(F$10-D$10)</f>
+      <c r="L28" s="136">
+        <f t="shared" si="1"/>
         <v>129.1</v>
       </c>
-      <c r="M28" s="89" t="s">
+      <c r="M28" s="84" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="29" spans="2:13" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="194" t="s">
+      <c r="B29" s="184" t="s">
         <v>200</v>
       </c>
-      <c r="C29" s="97">
+      <c r="C29" s="92">
         <v>13</v>
       </c>
-      <c r="D29" s="193">
+      <c r="D29" s="183">
         <v>1</v>
       </c>
-      <c r="E29" s="192">
-        <v>3</v>
-      </c>
-      <c r="F29" s="191">
+      <c r="E29" s="182">
+        <v>3</v>
+      </c>
+      <c r="F29" s="181">
         <v>9</v>
       </c>
-      <c r="G29" s="191">
+      <c r="G29" s="181">
         <v>12</v>
       </c>
-      <c r="H29" s="191"/>
-      <c r="I29" s="191"/>
-      <c r="K29" s="89">
-        <f>C29/2</f>
+      <c r="H29" s="181"/>
+      <c r="I29" s="181"/>
+      <c r="K29" s="84">
+        <f t="shared" si="0"/>
         <v>6.5</v>
       </c>
-      <c r="L29" s="144">
-        <f>D$10+(K29-D29)/(F29-D29)*(F$10-D$10)</f>
+      <c r="L29" s="136">
+        <f t="shared" si="1"/>
         <v>129.0625</v>
       </c>
-      <c r="M29" s="89" t="s">
+      <c r="M29" s="84" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="30" spans="2:13" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="190" t="s">
+      <c r="B30" s="180" t="s">
         <v>199</v>
       </c>
-      <c r="C30" s="150">
+      <c r="C30" s="142">
         <v>14</v>
       </c>
-      <c r="D30" s="189">
-        <v>2</v>
-      </c>
-      <c r="E30" s="152">
-        <v>2</v>
-      </c>
-      <c r="F30" s="150">
+      <c r="D30" s="179">
+        <v>2</v>
+      </c>
+      <c r="E30" s="144">
+        <v>2</v>
+      </c>
+      <c r="F30" s="142">
         <v>10</v>
       </c>
-      <c r="G30" s="150">
+      <c r="G30" s="142">
         <v>14</v>
       </c>
-      <c r="H30" s="150"/>
-      <c r="I30" s="150"/>
-      <c r="K30" s="89">
-        <f>C30/2</f>
+      <c r="H30" s="142"/>
+      <c r="I30" s="142"/>
+      <c r="K30" s="84">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="L30" s="144">
-        <f>D$10+(K30-D30)/(F30-D30)*(F$10-D$10)</f>
+      <c r="L30" s="136">
+        <f t="shared" si="1"/>
         <v>128.875</v>
       </c>
-      <c r="M30" s="89" t="s">
+      <c r="M30" s="84" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="31" spans="2:13" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="190" t="s">
+      <c r="B31" s="180" t="s">
         <v>198</v>
       </c>
-      <c r="C31" s="150">
+      <c r="C31" s="142">
         <v>11</v>
       </c>
-      <c r="D31" s="189">
+      <c r="D31" s="179">
         <v>0</v>
       </c>
-      <c r="E31" s="152">
-        <v>3</v>
-      </c>
-      <c r="F31" s="150">
+      <c r="E31" s="144">
+        <v>3</v>
+      </c>
+      <c r="F31" s="142">
         <v>8</v>
       </c>
-      <c r="G31" s="150">
+      <c r="G31" s="142">
         <v>9</v>
       </c>
-      <c r="H31" s="150"/>
-      <c r="I31" s="150"/>
-      <c r="K31" s="89">
-        <f>C31/2</f>
+      <c r="H31" s="142"/>
+      <c r="I31" s="142"/>
+      <c r="K31" s="84">
+        <f t="shared" si="0"/>
         <v>5.5</v>
       </c>
-      <c r="L31" s="144">
-        <f>D$10+(K31-D31)/(F31-D31)*(F$10-D$10)</f>
+      <c r="L31" s="136">
+        <f t="shared" si="1"/>
         <v>129.0625</v>
       </c>
-      <c r="M31" s="89" t="s">
+      <c r="M31" s="84" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="32" spans="2:13" ht="39.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="196" t="s">
+      <c r="B32" s="186" t="s">
         <v>197</v>
       </c>
-      <c r="C32" s="91">
+      <c r="C32" s="86">
         <v>11</v>
       </c>
-      <c r="D32" s="195">
+      <c r="D32" s="185">
         <v>0</v>
       </c>
-      <c r="E32" s="147">
-        <v>2</v>
-      </c>
-      <c r="F32" s="91">
+      <c r="E32" s="139">
+        <v>2</v>
+      </c>
+      <c r="F32" s="86">
         <v>8</v>
       </c>
-      <c r="G32" s="91">
+      <c r="G32" s="86">
         <v>10</v>
       </c>
-      <c r="H32" s="91"/>
-      <c r="I32" s="91"/>
-      <c r="K32" s="89">
-        <f>C32/2</f>
+      <c r="H32" s="86"/>
+      <c r="I32" s="86"/>
+      <c r="K32" s="84">
+        <f t="shared" si="0"/>
         <v>5.5</v>
       </c>
-      <c r="L32" s="144">
-        <f>D$10+(K32-D32)/(F32-D32)*(F$10-D$10)</f>
+      <c r="L32" s="136">
+        <f t="shared" si="1"/>
         <v>129.0625</v>
       </c>
-      <c r="M32" s="89" t="s">
+      <c r="M32" s="84" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="33" spans="2:13" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="194" t="s">
+      <c r="B33" s="184" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="97">
+      <c r="C33" s="92">
         <v>13</v>
       </c>
-      <c r="D33" s="193">
+      <c r="D33" s="183">
         <v>0</v>
       </c>
-      <c r="E33" s="192">
+      <c r="E33" s="182">
         <v>1</v>
       </c>
-      <c r="F33" s="191">
+      <c r="F33" s="181">
         <v>5</v>
       </c>
-      <c r="G33" s="191">
+      <c r="G33" s="181">
         <v>9</v>
       </c>
-      <c r="H33" s="191"/>
-      <c r="I33" s="191"/>
-      <c r="K33" s="89">
-        <f>C33/2</f>
+      <c r="H33" s="181"/>
+      <c r="I33" s="181"/>
+      <c r="K33" s="84">
+        <f t="shared" si="0"/>
         <v>6.5</v>
       </c>
-      <c r="L33" s="144">
+      <c r="L33" s="136">
         <f>F$10+(K33-F33)/(G33-F33)*(G$10-F$10)</f>
         <v>130.75</v>
       </c>
-      <c r="M33" s="89" t="s">
+      <c r="M33" s="84" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="34" spans="2:13" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="190" t="s">
+      <c r="B34" s="180" t="s">
         <v>195</v>
       </c>
-      <c r="C34" s="150">
+      <c r="C34" s="142">
         <v>12</v>
       </c>
-      <c r="D34" s="189">
+      <c r="D34" s="179">
         <v>1</v>
       </c>
-      <c r="E34" s="152">
+      <c r="E34" s="144">
         <v>1</v>
       </c>
-      <c r="F34" s="150">
+      <c r="F34" s="142">
         <v>5</v>
       </c>
-      <c r="G34" s="150">
+      <c r="G34" s="142">
         <v>10</v>
       </c>
-      <c r="H34" s="150"/>
-      <c r="I34" s="150"/>
-      <c r="K34" s="89">
-        <f>C34/2</f>
+      <c r="H34" s="142"/>
+      <c r="I34" s="142"/>
+      <c r="K34" s="84">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="L34" s="144">
+      <c r="L34" s="136">
         <f>F$10+(K34-F34)/(G34-F34)*(G$10-F$10)</f>
         <v>130.4</v>
       </c>
-      <c r="M34" s="89" t="s">
+      <c r="M34" s="84" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="35" spans="2:13" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="190" t="s">
+      <c r="B35" s="180" t="s">
         <v>194</v>
       </c>
-      <c r="C35" s="150">
+      <c r="C35" s="142">
         <v>12</v>
       </c>
-      <c r="D35" s="189">
+      <c r="D35" s="179">
         <v>0</v>
       </c>
-      <c r="E35" s="152">
+      <c r="E35" s="144">
         <v>1</v>
       </c>
-      <c r="F35" s="150">
-        <v>3</v>
-      </c>
-      <c r="G35" s="150">
+      <c r="F35" s="142">
+        <v>3</v>
+      </c>
+      <c r="G35" s="142">
         <v>8</v>
       </c>
-      <c r="H35" s="150"/>
-      <c r="I35" s="150"/>
-      <c r="K35" s="89">
-        <f>C35/2</f>
+      <c r="H35" s="142"/>
+      <c r="I35" s="142"/>
+      <c r="K35" s="84">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="L35" s="144">
+      <c r="L35" s="136">
         <f>F$10+(K35-F35)/(G35-F35)*(G$10-F$10)</f>
         <v>131.19999999999999</v>
       </c>
-      <c r="M35" s="89" t="s">
+      <c r="M35" s="84" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="36" spans="2:13" ht="39.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="190" t="s">
+      <c r="B36" s="180" t="s">
         <v>193</v>
       </c>
-      <c r="C36" s="91">
+      <c r="C36" s="86">
         <v>11</v>
       </c>
-      <c r="D36" s="189">
+      <c r="D36" s="179">
         <v>1</v>
       </c>
-      <c r="E36" s="152">
+      <c r="E36" s="144">
         <v>0</v>
       </c>
-      <c r="F36" s="150">
-        <v>3</v>
-      </c>
-      <c r="G36" s="150">
+      <c r="F36" s="142">
+        <v>3</v>
+      </c>
+      <c r="G36" s="142">
         <v>9</v>
       </c>
-      <c r="H36" s="150"/>
-      <c r="I36" s="150"/>
-      <c r="K36" s="89">
-        <f>C36/2</f>
+      <c r="H36" s="142"/>
+      <c r="I36" s="142"/>
+      <c r="K36" s="84">
+        <f t="shared" si="0"/>
         <v>5.5</v>
       </c>
-      <c r="L36" s="144">
+      <c r="L36" s="136">
         <f>F$10+(K36-F36)/(G36-F36)*(G$10-F$10)</f>
         <v>130.83333333333334</v>
       </c>
-      <c r="M36" s="89" t="s">
+      <c r="M36" s="84" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="D37" s="188"/>
+      <c r="D37" s="202"/>
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="D38" s="187"/>
+      <c r="D38" s="203"/>
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="D39" s="187"/>
+      <c r="D39" s="203"/>
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="D40" s="187"/>
+      <c r="D40" s="203"/>
     </row>
     <row r="41" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="D41" s="187"/>
+      <c r="D41" s="203"/>
     </row>
     <row r="42" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="D42" s="187"/>
+      <c r="D42" s="203"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -8629,8 +8629,8 @@
       <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="142"/>
-      <c r="K1" s="141">
+      <c r="J1" s="134"/>
+      <c r="K1" s="133">
         <v>43971</v>
       </c>
     </row>
@@ -8652,20 +8652,20 @@
       </c>
     </row>
     <row r="4" spans="1:14" ht="43.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="87" t="s">
+      <c r="B4" s="205" t="s">
         <v>190</v>
       </c>
-      <c r="C4" s="140"/>
-      <c r="D4" s="140"/>
-      <c r="E4" s="140"/>
-      <c r="F4" s="140"/>
-      <c r="G4" s="140"/>
-      <c r="H4" s="140"/>
-      <c r="I4" s="140"/>
-      <c r="J4" s="140"/>
-      <c r="K4" s="140"/>
-      <c r="L4" s="140"/>
-      <c r="M4" s="140"/>
+      <c r="C4" s="206"/>
+      <c r="D4" s="206"/>
+      <c r="E4" s="206"/>
+      <c r="F4" s="206"/>
+      <c r="G4" s="206"/>
+      <c r="H4" s="206"/>
+      <c r="I4" s="206"/>
+      <c r="J4" s="206"/>
+      <c r="K4" s="206"/>
+      <c r="L4" s="206"/>
+      <c r="M4" s="206"/>
     </row>
     <row r="5" spans="1:14" ht="40.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="5"/>
@@ -8693,37 +8693,37 @@
       </c>
     </row>
     <row r="6" spans="1:14" ht="22.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="137" t="s">
+      <c r="B6" s="204" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="137"/>
-      <c r="D6" s="139" t="s">
+      <c r="C6" s="204"/>
+      <c r="D6" s="132" t="s">
         <v>186</v>
       </c>
-      <c r="E6" s="139" t="s">
+      <c r="E6" s="132" t="s">
         <v>186</v>
       </c>
-      <c r="F6" s="139" t="s">
+      <c r="F6" s="132" t="s">
         <v>186</v>
       </c>
-      <c r="G6" s="139" t="s">
+      <c r="G6" s="132" t="s">
         <v>185</v>
       </c>
-      <c r="H6" s="138"/>
-      <c r="I6" s="137" t="s">
+      <c r="H6" s="131"/>
+      <c r="I6" s="204" t="s">
         <v>7</v>
       </c>
-      <c r="J6" s="137"/>
-      <c r="K6" s="136" t="s">
+      <c r="J6" s="204"/>
+      <c r="K6" s="130" t="s">
         <v>186</v>
       </c>
-      <c r="L6" s="136" t="s">
+      <c r="L6" s="130" t="s">
         <v>186</v>
       </c>
-      <c r="M6" s="136" t="s">
+      <c r="M6" s="130" t="s">
         <v>186</v>
       </c>
-      <c r="N6" s="136" t="s">
+      <c r="N6" s="130" t="s">
         <v>185</v>
       </c>
     </row>
@@ -8734,23 +8734,23 @@
       <c r="C7" s="74">
         <v>1</v>
       </c>
-      <c r="D7" s="135">
+      <c r="D7" s="129">
         <v>15</v>
       </c>
-      <c r="E7" s="135">
+      <c r="E7" s="129">
         <v>14</v>
       </c>
-      <c r="F7" s="135">
+      <c r="F7" s="129">
         <v>12</v>
       </c>
-      <c r="G7" s="134">
-        <f>(AVERAGE(D7:F7))/1.5</f>
+      <c r="G7" s="128">
+        <f t="shared" ref="G7:G18" si="0">(AVERAGE(D7:F7))/1.5</f>
         <v>9.1111111111111107</v>
       </c>
-      <c r="I7" s="133" t="s">
-        <v>3</v>
-      </c>
-      <c r="J7" s="132">
+      <c r="I7" s="127" t="s">
+        <v>3</v>
+      </c>
+      <c r="J7" s="126">
         <v>4</v>
       </c>
       <c r="K7" s="9">
@@ -8762,8 +8762,8 @@
       <c r="M7" s="9">
         <v>19</v>
       </c>
-      <c r="N7" s="131">
-        <f>(AVERAGE(K7:M7))/1.5</f>
+      <c r="N7" s="125">
+        <f t="shared" ref="N7:N18" si="1">(AVERAGE(K7:M7))/1.5</f>
         <v>12.888888888888888</v>
       </c>
     </row>
@@ -8774,17 +8774,17 @@
       <c r="C8" s="71">
         <v>2</v>
       </c>
-      <c r="D8" s="130">
+      <c r="D8" s="124">
         <v>14</v>
       </c>
-      <c r="E8" s="130">
+      <c r="E8" s="124">
         <v>16</v>
       </c>
-      <c r="F8" s="130">
+      <c r="F8" s="124">
         <v>17</v>
       </c>
-      <c r="G8" s="128">
-        <f>(AVERAGE(D8:F8))/1.5</f>
+      <c r="G8" s="122">
+        <f t="shared" si="0"/>
         <v>10.444444444444445</v>
       </c>
       <c r="I8" s="72" t="s">
@@ -8793,17 +8793,17 @@
       <c r="J8" s="71">
         <v>3</v>
       </c>
-      <c r="K8" s="130">
+      <c r="K8" s="124">
         <v>14</v>
       </c>
-      <c r="L8" s="130">
+      <c r="L8" s="124">
         <v>25</v>
       </c>
-      <c r="M8" s="130">
+      <c r="M8" s="124">
         <v>15</v>
       </c>
-      <c r="N8" s="128">
-        <f>(AVERAGE(K8:M8))/1.5</f>
+      <c r="N8" s="122">
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
     </row>
@@ -8814,17 +8814,17 @@
       <c r="C9" s="71">
         <v>3</v>
       </c>
-      <c r="D9" s="130">
+      <c r="D9" s="124">
         <v>13</v>
       </c>
-      <c r="E9" s="130">
+      <c r="E9" s="124">
         <v>14</v>
       </c>
-      <c r="F9" s="130">
+      <c r="F9" s="124">
         <v>13</v>
       </c>
-      <c r="G9" s="128">
-        <f>(AVERAGE(D9:F9))/1.5</f>
+      <c r="G9" s="122">
+        <f t="shared" si="0"/>
         <v>8.8888888888888893</v>
       </c>
       <c r="I9" s="72" t="s">
@@ -8833,17 +8833,17 @@
       <c r="J9" s="71">
         <v>2</v>
       </c>
-      <c r="K9" s="130">
+      <c r="K9" s="124">
         <v>14</v>
       </c>
-      <c r="L9" s="130">
+      <c r="L9" s="124">
         <v>16</v>
       </c>
-      <c r="M9" s="130">
+      <c r="M9" s="124">
         <v>14</v>
       </c>
-      <c r="N9" s="128">
-        <f>(AVERAGE(K9:M9))/1.5</f>
+      <c r="N9" s="122">
+        <f t="shared" si="1"/>
         <v>9.7777777777777768</v>
       </c>
     </row>
@@ -8863,8 +8863,8 @@
       <c r="F10" s="10">
         <v>18</v>
       </c>
-      <c r="G10" s="127">
-        <f>(AVERAGE(D10:F10))/1.5</f>
+      <c r="G10" s="121">
+        <f t="shared" si="0"/>
         <v>9.5555555555555554</v>
       </c>
       <c r="I10" s="69" t="s">
@@ -8882,8 +8882,8 @@
       <c r="M10" s="10">
         <v>15</v>
       </c>
-      <c r="N10" s="127">
-        <f>(AVERAGE(K10:M10))/1.5</f>
+      <c r="N10" s="121">
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
@@ -8903,8 +8903,8 @@
       <c r="F11" s="9">
         <v>12</v>
       </c>
-      <c r="G11" s="131">
-        <f>(AVERAGE(D11:F11))/1.5</f>
+      <c r="G11" s="125">
+        <f t="shared" si="0"/>
         <v>9.5555555555555554</v>
       </c>
       <c r="I11" s="11" t="s">
@@ -8922,8 +8922,8 @@
       <c r="M11" s="9">
         <v>22</v>
       </c>
-      <c r="N11" s="131">
-        <f>(AVERAGE(K11:M11))/1.5</f>
+      <c r="N11" s="125">
+        <f t="shared" si="1"/>
         <v>11.111111111111112</v>
       </c>
     </row>
@@ -8934,17 +8934,17 @@
       <c r="C12" s="71">
         <v>3</v>
       </c>
-      <c r="D12" s="130">
+      <c r="D12" s="124">
         <v>14</v>
       </c>
-      <c r="E12" s="130">
+      <c r="E12" s="124">
         <v>18</v>
       </c>
-      <c r="F12" s="130">
+      <c r="F12" s="124">
         <v>12</v>
       </c>
-      <c r="G12" s="128">
-        <f>(AVERAGE(D12:F12))/1.5</f>
+      <c r="G12" s="122">
+        <f t="shared" si="0"/>
         <v>9.7777777777777768</v>
       </c>
       <c r="I12" s="72" t="s">
@@ -8953,17 +8953,17 @@
       <c r="J12" s="71">
         <v>2</v>
       </c>
-      <c r="K12" s="130">
+      <c r="K12" s="124">
         <v>19</v>
       </c>
-      <c r="L12" s="130">
+      <c r="L12" s="124">
         <v>18</v>
       </c>
-      <c r="M12" s="130">
+      <c r="M12" s="124">
         <v>19</v>
       </c>
-      <c r="N12" s="128">
-        <f>(AVERAGE(K12:M12))/1.5</f>
+      <c r="N12" s="122">
+        <f t="shared" si="1"/>
         <v>12.444444444444445</v>
       </c>
     </row>
@@ -8974,17 +8974,17 @@
       <c r="C13" s="71">
         <v>2</v>
       </c>
-      <c r="D13" s="130">
+      <c r="D13" s="124">
         <v>12</v>
       </c>
-      <c r="E13" s="130">
+      <c r="E13" s="124">
         <v>17</v>
       </c>
-      <c r="F13" s="130">
+      <c r="F13" s="124">
         <v>16</v>
       </c>
-      <c r="G13" s="128">
-        <f>(AVERAGE(D13:F13))/1.5</f>
+      <c r="G13" s="122">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="I13" s="72" t="s">
@@ -8993,17 +8993,17 @@
       <c r="J13" s="71">
         <v>3</v>
       </c>
-      <c r="K13" s="130">
+      <c r="K13" s="124">
         <v>15</v>
       </c>
-      <c r="L13" s="130">
+      <c r="L13" s="124">
         <v>15</v>
       </c>
-      <c r="M13" s="130">
+      <c r="M13" s="124">
         <v>14</v>
       </c>
-      <c r="N13" s="128">
-        <f>(AVERAGE(K13:M13))/1.5</f>
+      <c r="N13" s="122">
+        <f t="shared" si="1"/>
         <v>9.7777777777777768</v>
       </c>
     </row>
@@ -9023,8 +9023,8 @@
       <c r="F14" s="10">
         <v>20</v>
       </c>
-      <c r="G14" s="127">
-        <f>(AVERAGE(D14:F14))/1.5</f>
+      <c r="G14" s="121">
+        <f t="shared" si="0"/>
         <v>10.888888888888888</v>
       </c>
       <c r="I14" s="69" t="s">
@@ -9042,8 +9042,8 @@
       <c r="M14" s="10">
         <v>2</v>
       </c>
-      <c r="N14" s="127">
-        <f>(AVERAGE(K14:M14))/1.5</f>
+      <c r="N14" s="121">
+        <f t="shared" si="1"/>
         <v>7.1111111111111107</v>
       </c>
     </row>
@@ -9063,8 +9063,8 @@
       <c r="F15" s="9">
         <v>16</v>
       </c>
-      <c r="G15" s="131">
-        <f>(AVERAGE(D15:F15))/1.5</f>
+      <c r="G15" s="125">
+        <f t="shared" si="0"/>
         <v>11.333333333333334</v>
       </c>
       <c r="I15" s="11" t="s">
@@ -9082,8 +9082,8 @@
       <c r="M15" s="9">
         <v>10</v>
       </c>
-      <c r="N15" s="131">
-        <f>(AVERAGE(K15:M15))/1.5</f>
+      <c r="N15" s="125">
+        <f t="shared" si="1"/>
         <v>8.6666666666666661</v>
       </c>
     </row>
@@ -9094,17 +9094,17 @@
       <c r="C16" s="71">
         <v>2</v>
       </c>
-      <c r="D16" s="130">
+      <c r="D16" s="124">
         <v>14</v>
       </c>
-      <c r="E16" s="130">
+      <c r="E16" s="124">
         <v>23</v>
       </c>
-      <c r="F16" s="130">
+      <c r="F16" s="124">
         <v>15</v>
       </c>
-      <c r="G16" s="128">
-        <f>(AVERAGE(D16:F16))/1.5</f>
+      <c r="G16" s="122">
+        <f t="shared" si="0"/>
         <v>11.555555555555555</v>
       </c>
       <c r="I16" s="72" t="s">
@@ -9113,17 +9113,17 @@
       <c r="J16" s="71">
         <v>3</v>
       </c>
-      <c r="K16" s="130">
+      <c r="K16" s="124">
         <v>12</v>
       </c>
-      <c r="L16" s="130">
+      <c r="L16" s="124">
         <v>15</v>
       </c>
-      <c r="M16" s="130">
+      <c r="M16" s="124">
         <v>15</v>
       </c>
-      <c r="N16" s="128">
-        <f>(AVERAGE(K16:M16))/1.5</f>
+      <c r="N16" s="122">
+        <f t="shared" si="1"/>
         <v>9.3333333333333339</v>
       </c>
     </row>
@@ -9134,17 +9134,17 @@
       <c r="C17" s="71">
         <v>3</v>
       </c>
-      <c r="D17" s="130">
+      <c r="D17" s="124">
         <v>23</v>
       </c>
-      <c r="E17" s="130">
+      <c r="E17" s="124">
         <v>10</v>
       </c>
-      <c r="F17" s="130">
+      <c r="F17" s="124">
         <v>17</v>
       </c>
-      <c r="G17" s="128">
-        <f>(AVERAGE(D17:F17))/1.5</f>
+      <c r="G17" s="122">
+        <f t="shared" si="0"/>
         <v>11.111111111111112</v>
       </c>
       <c r="I17" s="72" t="s">
@@ -9153,17 +9153,17 @@
       <c r="J17" s="71">
         <v>2</v>
       </c>
-      <c r="K17" s="129">
+      <c r="K17" s="123">
         <v>12</v>
       </c>
-      <c r="L17" s="129">
+      <c r="L17" s="123">
         <v>14</v>
       </c>
-      <c r="M17" s="129">
+      <c r="M17" s="123">
         <v>16</v>
       </c>
-      <c r="N17" s="128">
-        <f>(AVERAGE(K17:M17))/1.5</f>
+      <c r="N17" s="122">
+        <f t="shared" si="1"/>
         <v>9.3333333333333339</v>
       </c>
     </row>
@@ -9183,8 +9183,8 @@
       <c r="F18" s="10">
         <v>10</v>
       </c>
-      <c r="G18" s="127">
-        <f>(AVERAGE(D18:F18))/1.5</f>
+      <c r="G18" s="121">
+        <f t="shared" si="0"/>
         <v>7.7777777777777777</v>
       </c>
       <c r="I18" s="69" t="s">
@@ -9202,8 +9202,8 @@
       <c r="M18" s="10">
         <v>19</v>
       </c>
-      <c r="N18" s="127">
-        <f>(AVERAGE(K18:M18))/1.5</f>
+      <c r="N18" s="121">
+        <f t="shared" si="1"/>
         <v>11.333333333333334</v>
       </c>
     </row>
@@ -9820,1517 +9820,1517 @@
   <dimension ref="A1:K60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="5" width="9.140625" style="89"/>
-    <col min="6" max="6" width="17.5703125" style="89" customWidth="1"/>
-    <col min="7" max="7" width="16.85546875" style="89" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="89"/>
+    <col min="1" max="5" width="9.140625" style="84"/>
+    <col min="6" max="6" width="17.5703125" style="84" customWidth="1"/>
+    <col min="7" max="7" width="16.85546875" style="84" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="84"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="123"/>
-      <c r="B1" s="125">
+      <c r="A1" s="117"/>
+      <c r="B1" s="119">
         <v>2020</v>
       </c>
-      <c r="C1" s="124"/>
-      <c r="D1" s="121" t="s">
+      <c r="C1" s="118"/>
+      <c r="D1" s="115" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="107"/>
-      <c r="F1" s="121" t="s">
+      <c r="E1" s="102"/>
+      <c r="F1" s="115" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="123"/>
-      <c r="B2" s="122"/>
-      <c r="C2" s="121"/>
-      <c r="D2" s="121"/>
-      <c r="E2" s="107"/>
+      <c r="A2" s="117"/>
+      <c r="B2" s="116"/>
+      <c r="C2" s="115"/>
+      <c r="D2" s="115"/>
+      <c r="E2" s="102"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B3" s="120" t="s">
+      <c r="B3" s="114" t="s">
         <v>182</v>
       </c>
-      <c r="C3" s="116"/>
-      <c r="D3" s="116"/>
-      <c r="E3" s="114"/>
+      <c r="C3" s="110"/>
+      <c r="D3" s="110"/>
+      <c r="E3" s="108"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B4" s="117"/>
-      <c r="C4" s="116"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="114"/>
+      <c r="B4" s="111"/>
+      <c r="C4" s="110"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="108"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B5" s="116"/>
-      <c r="C5" s="116"/>
-      <c r="D5" s="116"/>
-      <c r="E5" s="114"/>
+      <c r="B5" s="110"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="108"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B6" s="116"/>
-      <c r="C6" s="116"/>
-      <c r="D6" s="116"/>
-      <c r="E6" s="114"/>
+      <c r="B6" s="110"/>
+      <c r="C6" s="110"/>
+      <c r="D6" s="110"/>
+      <c r="E6" s="108"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B7" s="116"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="116"/>
-      <c r="E7" s="114"/>
+      <c r="B7" s="110"/>
+      <c r="C7" s="110"/>
+      <c r="D7" s="110"/>
+      <c r="E7" s="108"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="119"/>
-      <c r="B8" s="119"/>
-      <c r="C8" s="119"/>
-      <c r="D8" s="115" t="s">
+      <c r="A8" s="113"/>
+      <c r="B8" s="113"/>
+      <c r="C8" s="113"/>
+      <c r="D8" s="109" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="119"/>
-      <c r="F8" s="119" t="s">
+      <c r="E8" s="113"/>
+      <c r="F8" s="113" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="119" t="s">
+      <c r="G8" s="113" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B9" s="116"/>
-      <c r="C9" s="116"/>
-      <c r="D9" s="115" t="s">
+      <c r="B9" s="110"/>
+      <c r="C9" s="110"/>
+      <c r="D9" s="109" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="114"/>
-      <c r="F9" s="118">
+      <c r="E9" s="108"/>
+      <c r="F9" s="112">
         <v>44004</v>
       </c>
-      <c r="G9" s="118" t="s">
+      <c r="G9" s="112" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B10" s="117"/>
-      <c r="C10" s="116"/>
-      <c r="D10" s="115" t="s">
+      <c r="B10" s="111"/>
+      <c r="C10" s="110"/>
+      <c r="D10" s="109" t="s">
         <v>29</v>
       </c>
-      <c r="E10" s="114"/>
-      <c r="F10" s="108">
+      <c r="E10" s="108"/>
+      <c r="F10" s="103">
         <v>174</v>
       </c>
-      <c r="G10" s="108">
+      <c r="G10" s="103">
         <v>181</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="112"/>
-      <c r="B11" s="113"/>
-      <c r="C11" s="112"/>
-      <c r="D11" s="111" t="s">
+      <c r="A11" s="106"/>
+      <c r="B11" s="107"/>
+      <c r="C11" s="106"/>
+      <c r="D11" s="105" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="111"/>
-      <c r="F11" s="110" t="s">
+      <c r="E11" s="105"/>
+      <c r="F11" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="G11" s="110" t="s">
+      <c r="G11" s="104" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="45.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="109" t="s">
+      <c r="B12" s="207" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="109"/>
-      <c r="D12" s="108" t="s">
+      <c r="C12" s="207"/>
+      <c r="D12" s="103" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="107" t="s">
+      <c r="E12" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="F12" s="106" t="s">
+      <c r="F12" s="101" t="s">
         <v>180</v>
       </c>
-      <c r="G12" s="106" t="s">
+      <c r="G12" s="101" t="s">
         <v>180</v>
       </c>
-      <c r="J12" s="89" t="s">
+      <c r="J12" s="84" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="96"/>
-      <c r="B13" s="101" t="s">
+      <c r="A13" s="91"/>
+      <c r="B13" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="100">
+      <c r="C13" s="95">
         <v>1</v>
       </c>
-      <c r="D13" s="105" t="s">
+      <c r="D13" s="100" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="98" t="s">
+      <c r="E13" s="93" t="s">
         <v>38</v>
       </c>
-      <c r="F13" s="104">
-        <v>3</v>
-      </c>
-      <c r="G13" s="104">
+      <c r="F13" s="99">
+        <v>3</v>
+      </c>
+      <c r="G13" s="99">
         <v>9</v>
       </c>
-      <c r="I13" s="89">
+      <c r="I13" s="84">
         <v>5</v>
       </c>
-      <c r="J13" s="90">
+      <c r="J13" s="85">
         <f>IF(F13&lt;=5,F$10+(I13-F13)/(G13-F13)*(G$10-F$10),"")</f>
         <v>176.33333333333334</v>
       </c>
-      <c r="K13" s="89" t="s">
+      <c r="K13" s="84" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="96"/>
-      <c r="B14" s="95"/>
-      <c r="C14" s="94"/>
-      <c r="D14" s="103" t="s">
+      <c r="A14" s="91"/>
+      <c r="B14" s="90"/>
+      <c r="C14" s="89"/>
+      <c r="D14" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="E14" s="92" t="s">
+      <c r="E14" s="87" t="s">
         <v>38</v>
       </c>
-      <c r="F14" s="102">
+      <c r="F14" s="97">
         <v>5</v>
       </c>
-      <c r="G14" s="102">
+      <c r="G14" s="97">
         <v>10</v>
       </c>
-      <c r="I14" s="89">
+      <c r="I14" s="84">
         <v>5</v>
       </c>
-      <c r="J14" s="90">
+      <c r="J14" s="85">
         <f>IF(F14&lt;=5,F$10+(I14-F14)/(G14-F14)*(G$10-F$10),"")</f>
         <v>174</v>
       </c>
-      <c r="K14" s="89" t="s">
+      <c r="K14" s="84" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="96"/>
-      <c r="B15" s="101" t="s">
+      <c r="A15" s="91"/>
+      <c r="B15" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="C15" s="100">
-        <v>2</v>
-      </c>
-      <c r="D15" s="99" t="s">
+      <c r="C15" s="95">
+        <v>2</v>
+      </c>
+      <c r="D15" s="94" t="s">
         <v>10</v>
       </c>
-      <c r="E15" s="98" t="s">
+      <c r="E15" s="93" t="s">
         <v>35</v>
       </c>
-      <c r="F15" s="97">
-        <v>3</v>
-      </c>
-      <c r="G15" s="97">
+      <c r="F15" s="92">
+        <v>3</v>
+      </c>
+      <c r="G15" s="92">
         <v>10</v>
       </c>
-      <c r="I15" s="89">
+      <c r="I15" s="84">
         <v>5</v>
       </c>
-      <c r="J15" s="90">
+      <c r="J15" s="85">
         <f>IF(F15&lt;=5,F$10+(I15-F15)/(G15-F15)*(G$10-F$10),"")</f>
         <v>176</v>
       </c>
-      <c r="K15" s="89" t="s">
+      <c r="K15" s="84" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="96"/>
-      <c r="B16" s="95"/>
-      <c r="C16" s="94"/>
-      <c r="D16" s="93" t="s">
+      <c r="A16" s="91"/>
+      <c r="B16" s="90"/>
+      <c r="C16" s="89"/>
+      <c r="D16" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="E16" s="92" t="s">
+      <c r="E16" s="87" t="s">
         <v>35</v>
       </c>
-      <c r="F16" s="91">
+      <c r="F16" s="86">
         <v>7</v>
       </c>
-      <c r="G16" s="91">
+      <c r="G16" s="86">
         <v>10</v>
       </c>
-      <c r="I16" s="89">
+      <c r="I16" s="84">
         <v>5</v>
       </c>
-      <c r="J16" s="90">
+      <c r="J16" s="85">
         <v>172</v>
       </c>
-      <c r="K16" s="89" t="s">
+      <c r="K16" s="84" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="96"/>
-      <c r="B17" s="101" t="s">
+      <c r="A17" s="91"/>
+      <c r="B17" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="C17" s="100">
-        <v>3</v>
-      </c>
-      <c r="D17" s="99" t="s">
+      <c r="C17" s="95">
+        <v>3</v>
+      </c>
+      <c r="D17" s="94" t="s">
         <v>10</v>
       </c>
-      <c r="E17" s="98" t="s">
+      <c r="E17" s="93" t="s">
         <v>35</v>
       </c>
-      <c r="F17" s="97">
+      <c r="F17" s="92">
         <v>8</v>
       </c>
-      <c r="G17" s="97">
+      <c r="G17" s="92">
         <v>10</v>
       </c>
-      <c r="I17" s="89">
+      <c r="I17" s="84">
         <v>5</v>
       </c>
-      <c r="J17" s="90">
+      <c r="J17" s="85">
         <v>171</v>
       </c>
-      <c r="K17" s="89" t="s">
+      <c r="K17" s="84" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="96"/>
-      <c r="B18" s="95"/>
-      <c r="C18" s="94"/>
-      <c r="D18" s="93" t="s">
+      <c r="A18" s="91"/>
+      <c r="B18" s="90"/>
+      <c r="C18" s="89"/>
+      <c r="D18" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="E18" s="92" t="s">
+      <c r="E18" s="87" t="s">
         <v>35</v>
       </c>
-      <c r="F18" s="91">
+      <c r="F18" s="86">
         <v>7</v>
       </c>
-      <c r="G18" s="91">
+      <c r="G18" s="86">
         <v>10</v>
       </c>
-      <c r="I18" s="89">
+      <c r="I18" s="84">
         <v>5</v>
       </c>
-      <c r="J18" s="90">
+      <c r="J18" s="85">
         <v>172</v>
       </c>
-      <c r="K18" s="89" t="s">
+      <c r="K18" s="84" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="96"/>
-      <c r="B19" s="101" t="s">
+      <c r="A19" s="91"/>
+      <c r="B19" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="C19" s="100">
-        <v>4</v>
-      </c>
-      <c r="D19" s="99" t="s">
+      <c r="C19" s="95">
+        <v>4</v>
+      </c>
+      <c r="D19" s="94" t="s">
         <v>10</v>
       </c>
-      <c r="E19" s="98" t="s">
+      <c r="E19" s="93" t="s">
         <v>38</v>
       </c>
-      <c r="F19" s="97">
+      <c r="F19" s="92">
         <v>7</v>
       </c>
-      <c r="G19" s="97">
+      <c r="G19" s="92">
         <v>10</v>
       </c>
-      <c r="I19" s="89">
+      <c r="I19" s="84">
         <v>5</v>
       </c>
-      <c r="J19" s="90">
+      <c r="J19" s="85">
         <v>172</v>
       </c>
-      <c r="K19" s="89" t="s">
+      <c r="K19" s="84" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="96"/>
-      <c r="B20" s="95"/>
-      <c r="C20" s="94"/>
-      <c r="D20" s="93" t="s">
+      <c r="A20" s="91"/>
+      <c r="B20" s="90"/>
+      <c r="C20" s="89"/>
+      <c r="D20" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="E20" s="92" t="s">
+      <c r="E20" s="87" t="s">
         <v>38</v>
       </c>
-      <c r="F20" s="91">
+      <c r="F20" s="86">
         <v>8</v>
       </c>
-      <c r="G20" s="91">
+      <c r="G20" s="86">
         <v>10</v>
       </c>
-      <c r="I20" s="89">
+      <c r="I20" s="84">
         <v>5</v>
       </c>
-      <c r="J20" s="90">
+      <c r="J20" s="85">
         <v>171</v>
       </c>
-      <c r="K20" s="89" t="s">
+      <c r="K20" s="84" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="96"/>
-      <c r="B21" s="101" t="s">
+      <c r="A21" s="91"/>
+      <c r="B21" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="C21" s="100">
-        <v>4</v>
-      </c>
-      <c r="D21" s="99" t="s">
+      <c r="C21" s="95">
+        <v>4</v>
+      </c>
+      <c r="D21" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="E21" s="98" t="s">
+      <c r="E21" s="93" t="s">
         <v>37</v>
       </c>
-      <c r="F21" s="97">
+      <c r="F21" s="92">
         <v>5</v>
       </c>
-      <c r="G21" s="97">
+      <c r="G21" s="92">
         <v>10</v>
       </c>
-      <c r="I21" s="89">
+      <c r="I21" s="84">
         <v>5</v>
       </c>
-      <c r="J21" s="90">
+      <c r="J21" s="85">
         <f>IF(F21&lt;=5,F$10+(I21-F21)/(G21-F21)*(G$10-F$10),"")</f>
         <v>174</v>
       </c>
-      <c r="K21" s="89" t="s">
+      <c r="K21" s="84" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="96"/>
-      <c r="B22" s="95"/>
-      <c r="C22" s="94"/>
-      <c r="D22" s="93" t="s">
+      <c r="A22" s="91"/>
+      <c r="B22" s="90"/>
+      <c r="C22" s="89"/>
+      <c r="D22" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="E22" s="92" t="s">
+      <c r="E22" s="87" t="s">
         <v>37</v>
       </c>
-      <c r="F22" s="91">
+      <c r="F22" s="86">
         <v>5</v>
       </c>
-      <c r="G22" s="91">
+      <c r="G22" s="86">
         <v>10</v>
       </c>
-      <c r="I22" s="89">
+      <c r="I22" s="84">
         <v>5</v>
       </c>
-      <c r="J22" s="90">
+      <c r="J22" s="85">
         <f>IF(F22&lt;=5,F$10+(I22-F22)/(G22-F22)*(G$10-F$10),"")</f>
         <v>174</v>
       </c>
-      <c r="K22" s="89" t="s">
+      <c r="K22" s="84" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="96"/>
-      <c r="B23" s="101" t="s">
+      <c r="A23" s="91"/>
+      <c r="B23" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="C23" s="100">
-        <v>3</v>
-      </c>
-      <c r="D23" s="99" t="s">
+      <c r="C23" s="95">
+        <v>3</v>
+      </c>
+      <c r="D23" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="E23" s="98" t="s">
+      <c r="E23" s="93" t="s">
         <v>38</v>
       </c>
-      <c r="F23" s="97">
+      <c r="F23" s="92">
         <v>8</v>
       </c>
-      <c r="G23" s="97">
+      <c r="G23" s="92">
         <v>10</v>
       </c>
-      <c r="I23" s="89">
+      <c r="I23" s="84">
         <v>5</v>
       </c>
-      <c r="J23" s="90">
+      <c r="J23" s="85">
         <v>171</v>
       </c>
-      <c r="K23" s="89" t="s">
+      <c r="K23" s="84" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="96"/>
-      <c r="B24" s="95"/>
-      <c r="C24" s="94"/>
-      <c r="D24" s="93" t="s">
+      <c r="A24" s="91"/>
+      <c r="B24" s="90"/>
+      <c r="C24" s="89"/>
+      <c r="D24" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="E24" s="92" t="s">
+      <c r="E24" s="87" t="s">
         <v>38</v>
       </c>
-      <c r="F24" s="91">
+      <c r="F24" s="86">
         <v>6</v>
       </c>
-      <c r="G24" s="91">
+      <c r="G24" s="86">
         <v>10</v>
       </c>
-      <c r="I24" s="89">
+      <c r="I24" s="84">
         <v>5</v>
       </c>
-      <c r="J24" s="90">
+      <c r="J24" s="85">
         <v>173</v>
       </c>
-      <c r="K24" s="89" t="s">
+      <c r="K24" s="84" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="96"/>
-      <c r="B25" s="101" t="s">
+      <c r="A25" s="91"/>
+      <c r="B25" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="C25" s="100">
-        <v>2</v>
-      </c>
-      <c r="D25" s="99" t="s">
+      <c r="C25" s="95">
+        <v>2</v>
+      </c>
+      <c r="D25" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="E25" s="98" t="s">
+      <c r="E25" s="93" t="s">
         <v>37</v>
       </c>
-      <c r="F25" s="97">
+      <c r="F25" s="92">
         <v>5</v>
       </c>
-      <c r="G25" s="97">
+      <c r="G25" s="92">
         <v>10</v>
       </c>
-      <c r="I25" s="89">
+      <c r="I25" s="84">
         <v>5</v>
       </c>
-      <c r="J25" s="90">
+      <c r="J25" s="85">
         <f>IF(F25&lt;=5,F$10+(I25-F25)/(G25-F25)*(G$10-F$10),"")</f>
         <v>174</v>
       </c>
-      <c r="K25" s="89" t="s">
+      <c r="K25" s="84" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="96"/>
-      <c r="B26" s="95"/>
-      <c r="C26" s="94"/>
-      <c r="D26" s="93" t="s">
+      <c r="A26" s="91"/>
+      <c r="B26" s="90"/>
+      <c r="C26" s="89"/>
+      <c r="D26" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="E26" s="92" t="s">
+      <c r="E26" s="87" t="s">
         <v>37</v>
       </c>
-      <c r="F26" s="91">
+      <c r="F26" s="86">
         <v>6</v>
       </c>
-      <c r="G26" s="91">
+      <c r="G26" s="86">
         <v>10</v>
       </c>
-      <c r="I26" s="89">
+      <c r="I26" s="84">
         <v>5</v>
       </c>
-      <c r="J26" s="90">
+      <c r="J26" s="85">
         <v>173</v>
       </c>
-      <c r="K26" s="89" t="s">
+      <c r="K26" s="84" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="96"/>
-      <c r="B27" s="101" t="s">
+      <c r="A27" s="91"/>
+      <c r="B27" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="C27" s="100">
+      <c r="C27" s="95">
         <v>1</v>
       </c>
-      <c r="D27" s="99" t="s">
+      <c r="D27" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="E27" s="98" t="s">
+      <c r="E27" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="F27" s="97">
-        <v>2</v>
-      </c>
-      <c r="G27" s="97">
+      <c r="F27" s="92">
+        <v>2</v>
+      </c>
+      <c r="G27" s="92">
         <v>10</v>
       </c>
-      <c r="I27" s="89">
+      <c r="I27" s="84">
         <v>5</v>
       </c>
-      <c r="J27" s="90">
-        <f>IF(F27&lt;=5,F$10+(I27-F27)/(G27-F27)*(G$10-F$10),"")</f>
+      <c r="J27" s="85">
+        <f t="shared" ref="J27:J36" si="0">IF(F27&lt;=5,F$10+(I27-F27)/(G27-F27)*(G$10-F$10),"")</f>
         <v>176.625</v>
       </c>
-      <c r="K27" s="89" t="s">
+      <c r="K27" s="84" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="96"/>
-      <c r="B28" s="95"/>
-      <c r="C28" s="94"/>
-      <c r="D28" s="93" t="s">
+      <c r="A28" s="91"/>
+      <c r="B28" s="90"/>
+      <c r="C28" s="89"/>
+      <c r="D28" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="E28" s="92" t="s">
+      <c r="E28" s="87" t="s">
         <v>36</v>
       </c>
-      <c r="F28" s="91">
-        <v>3</v>
-      </c>
-      <c r="G28" s="91">
+      <c r="F28" s="86">
+        <v>3</v>
+      </c>
+      <c r="G28" s="86">
         <v>10</v>
       </c>
-      <c r="I28" s="89">
+      <c r="I28" s="84">
         <v>5</v>
       </c>
-      <c r="J28" s="90">
-        <f>IF(F28&lt;=5,F$10+(I28-F28)/(G28-F28)*(G$10-F$10),"")</f>
+      <c r="J28" s="85">
+        <f t="shared" si="0"/>
         <v>176</v>
       </c>
-      <c r="K28" s="89" t="s">
+      <c r="K28" s="84" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="96"/>
-      <c r="B29" s="101" t="s">
-        <v>2</v>
-      </c>
-      <c r="C29" s="100">
+      <c r="A29" s="91"/>
+      <c r="B29" s="96" t="s">
+        <v>2</v>
+      </c>
+      <c r="C29" s="95">
         <v>1</v>
       </c>
-      <c r="D29" s="99" t="s">
+      <c r="D29" s="94" t="s">
         <v>10</v>
       </c>
-      <c r="E29" s="98" t="s">
+      <c r="E29" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="F29" s="97">
+      <c r="F29" s="92">
         <v>1</v>
       </c>
-      <c r="G29" s="97">
+      <c r="G29" s="92">
         <v>10</v>
       </c>
-      <c r="I29" s="89">
+      <c r="I29" s="84">
         <v>5</v>
       </c>
-      <c r="J29" s="90">
-        <f>IF(F29&lt;=5,F$10+(I29-F29)/(G29-F29)*(G$10-F$10),"")</f>
+      <c r="J29" s="85">
+        <f t="shared" si="0"/>
         <v>177.11111111111111</v>
       </c>
-      <c r="K29" s="89" t="s">
+      <c r="K29" s="84" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="96"/>
-      <c r="B30" s="95"/>
-      <c r="C30" s="94"/>
-      <c r="D30" s="93" t="s">
+      <c r="A30" s="91"/>
+      <c r="B30" s="90"/>
+      <c r="C30" s="89"/>
+      <c r="D30" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="E30" s="92" t="s">
+      <c r="E30" s="87" t="s">
         <v>36</v>
       </c>
-      <c r="F30" s="91">
-        <v>3</v>
-      </c>
-      <c r="G30" s="91">
+      <c r="F30" s="86">
+        <v>3</v>
+      </c>
+      <c r="G30" s="86">
         <v>9</v>
       </c>
-      <c r="I30" s="89">
+      <c r="I30" s="84">
         <v>5</v>
       </c>
-      <c r="J30" s="90">
-        <f>IF(F30&lt;=5,F$10+(I30-F30)/(G30-F30)*(G$10-F$10),"")</f>
+      <c r="J30" s="85">
+        <f t="shared" si="0"/>
         <v>176.33333333333334</v>
       </c>
-      <c r="K30" s="89" t="s">
+      <c r="K30" s="84" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="96"/>
-      <c r="B31" s="101" t="s">
-        <v>2</v>
-      </c>
-      <c r="C31" s="100">
-        <v>2</v>
-      </c>
-      <c r="D31" s="99" t="s">
+      <c r="A31" s="91"/>
+      <c r="B31" s="96" t="s">
+        <v>2</v>
+      </c>
+      <c r="C31" s="95">
+        <v>2</v>
+      </c>
+      <c r="D31" s="94" t="s">
         <v>10</v>
       </c>
-      <c r="E31" s="98" t="s">
+      <c r="E31" s="93" t="s">
         <v>37</v>
       </c>
-      <c r="F31" s="97">
+      <c r="F31" s="92">
         <v>1</v>
       </c>
-      <c r="G31" s="97">
+      <c r="G31" s="92">
         <v>9</v>
       </c>
-      <c r="I31" s="89">
+      <c r="I31" s="84">
         <v>5</v>
       </c>
-      <c r="J31" s="90">
-        <f>IF(F31&lt;=5,F$10+(I31-F31)/(G31-F31)*(G$10-F$10),"")</f>
+      <c r="J31" s="85">
+        <f t="shared" si="0"/>
         <v>177.5</v>
       </c>
-      <c r="K31" s="89" t="s">
+      <c r="K31" s="84" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="96"/>
-      <c r="B32" s="95"/>
-      <c r="C32" s="94"/>
-      <c r="D32" s="93" t="s">
+      <c r="A32" s="91"/>
+      <c r="B32" s="90"/>
+      <c r="C32" s="89"/>
+      <c r="D32" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="E32" s="92" t="s">
+      <c r="E32" s="87" t="s">
         <v>37</v>
       </c>
-      <c r="F32" s="91">
-        <v>2</v>
-      </c>
-      <c r="G32" s="91">
+      <c r="F32" s="86">
+        <v>2</v>
+      </c>
+      <c r="G32" s="86">
         <v>10</v>
       </c>
-      <c r="I32" s="89">
+      <c r="I32" s="84">
         <v>5</v>
       </c>
-      <c r="J32" s="90">
-        <f>IF(F32&lt;=5,F$10+(I32-F32)/(G32-F32)*(G$10-F$10),"")</f>
+      <c r="J32" s="85">
+        <f t="shared" si="0"/>
         <v>176.625</v>
       </c>
-      <c r="K32" s="89" t="s">
+      <c r="K32" s="84" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="96"/>
-      <c r="B33" s="101" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="100">
-        <v>3</v>
-      </c>
-      <c r="D33" s="99" t="s">
+      <c r="A33" s="91"/>
+      <c r="B33" s="96" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="95">
+        <v>3</v>
+      </c>
+      <c r="D33" s="94" t="s">
         <v>10</v>
       </c>
-      <c r="E33" s="98" t="s">
+      <c r="E33" s="93" t="s">
         <v>38</v>
       </c>
-      <c r="F33" s="97">
+      <c r="F33" s="92">
         <v>0</v>
       </c>
-      <c r="G33" s="97">
+      <c r="G33" s="92">
         <v>8</v>
       </c>
-      <c r="I33" s="89">
+      <c r="I33" s="84">
         <v>5</v>
       </c>
-      <c r="J33" s="90">
-        <f>IF(F33&lt;=5,F$10+(I33-F33)/(G33-F33)*(G$10-F$10),"")</f>
+      <c r="J33" s="85">
+        <f t="shared" si="0"/>
         <v>178.375</v>
       </c>
-      <c r="K33" s="89" t="s">
+      <c r="K33" s="84" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="96"/>
-      <c r="B34" s="95"/>
-      <c r="C34" s="94"/>
-      <c r="D34" s="93" t="s">
+      <c r="A34" s="91"/>
+      <c r="B34" s="90"/>
+      <c r="C34" s="89"/>
+      <c r="D34" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="E34" s="92" t="s">
+      <c r="E34" s="87" t="s">
         <v>38</v>
       </c>
-      <c r="F34" s="91">
+      <c r="F34" s="86">
         <v>5</v>
       </c>
-      <c r="G34" s="91">
+      <c r="G34" s="86">
         <v>10</v>
       </c>
-      <c r="I34" s="89">
+      <c r="I34" s="84">
         <v>5</v>
       </c>
-      <c r="J34" s="90">
-        <f>IF(F34&lt;=5,F$10+(I34-F34)/(G34-F34)*(G$10-F$10),"")</f>
+      <c r="J34" s="85">
+        <f t="shared" si="0"/>
         <v>174</v>
       </c>
-      <c r="K34" s="89" t="s">
+      <c r="K34" s="84" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="96"/>
-      <c r="B35" s="101" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="100">
-        <v>4</v>
-      </c>
-      <c r="D35" s="99" t="s">
+      <c r="A35" s="91"/>
+      <c r="B35" s="96" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="95">
+        <v>4</v>
+      </c>
+      <c r="D35" s="94" t="s">
         <v>10</v>
       </c>
-      <c r="E35" s="98" t="s">
+      <c r="E35" s="93" t="s">
         <v>37</v>
       </c>
-      <c r="F35" s="97">
-        <v>3</v>
-      </c>
-      <c r="G35" s="97">
+      <c r="F35" s="92">
+        <v>3</v>
+      </c>
+      <c r="G35" s="92">
         <v>10</v>
       </c>
-      <c r="I35" s="89">
+      <c r="I35" s="84">
         <v>5</v>
       </c>
-      <c r="J35" s="90">
-        <f>IF(F35&lt;=5,F$10+(I35-F35)/(G35-F35)*(G$10-F$10),"")</f>
+      <c r="J35" s="85">
+        <f t="shared" si="0"/>
         <v>176</v>
       </c>
-      <c r="K35" s="89" t="s">
+      <c r="K35" s="84" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="96"/>
-      <c r="B36" s="95"/>
-      <c r="C36" s="94"/>
-      <c r="D36" s="93" t="s">
+      <c r="A36" s="91"/>
+      <c r="B36" s="90"/>
+      <c r="C36" s="89"/>
+      <c r="D36" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="E36" s="92" t="s">
+      <c r="E36" s="87" t="s">
         <v>37</v>
       </c>
-      <c r="F36" s="91">
-        <v>2</v>
-      </c>
-      <c r="G36" s="91">
+      <c r="F36" s="86">
+        <v>2</v>
+      </c>
+      <c r="G36" s="86">
         <v>9</v>
       </c>
-      <c r="I36" s="89">
+      <c r="I36" s="84">
         <v>5</v>
       </c>
-      <c r="J36" s="90">
-        <f>IF(F36&lt;=5,F$10+(I36-F36)/(G36-F36)*(G$10-F$10),"")</f>
+      <c r="J36" s="85">
+        <f t="shared" si="0"/>
         <v>177</v>
       </c>
-      <c r="K36" s="89" t="s">
+      <c r="K36" s="84" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="96"/>
-      <c r="B37" s="101" t="s">
-        <v>3</v>
-      </c>
-      <c r="C37" s="100">
-        <v>4</v>
-      </c>
-      <c r="D37" s="99" t="s">
+      <c r="A37" s="91"/>
+      <c r="B37" s="96" t="s">
+        <v>3</v>
+      </c>
+      <c r="C37" s="95">
+        <v>4</v>
+      </c>
+      <c r="D37" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="E37" s="98" t="s">
+      <c r="E37" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="F37" s="97">
+      <c r="F37" s="92">
         <v>7</v>
       </c>
-      <c r="G37" s="97">
+      <c r="G37" s="92">
         <v>10</v>
       </c>
-      <c r="I37" s="89">
+      <c r="I37" s="84">
         <v>5</v>
       </c>
-      <c r="J37" s="90">
+      <c r="J37" s="85">
         <v>172</v>
       </c>
-      <c r="K37" s="89" t="s">
+      <c r="K37" s="84" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="96"/>
-      <c r="B38" s="95"/>
-      <c r="C38" s="94"/>
-      <c r="D38" s="93" t="s">
+      <c r="A38" s="91"/>
+      <c r="B38" s="90"/>
+      <c r="C38" s="89"/>
+      <c r="D38" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="E38" s="92" t="s">
+      <c r="E38" s="87" t="s">
         <v>36</v>
       </c>
-      <c r="F38" s="91">
+      <c r="F38" s="86">
         <v>6</v>
       </c>
-      <c r="G38" s="91">
+      <c r="G38" s="86">
         <v>10</v>
       </c>
-      <c r="I38" s="89">
+      <c r="I38" s="84">
         <v>5</v>
       </c>
-      <c r="J38" s="90">
+      <c r="J38" s="85">
         <v>173</v>
       </c>
-      <c r="K38" s="89" t="s">
+      <c r="K38" s="84" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="96"/>
-      <c r="B39" s="101" t="s">
-        <v>3</v>
-      </c>
-      <c r="C39" s="100">
-        <v>3</v>
-      </c>
-      <c r="D39" s="99" t="s">
+      <c r="A39" s="91"/>
+      <c r="B39" s="96" t="s">
+        <v>3</v>
+      </c>
+      <c r="C39" s="95">
+        <v>3</v>
+      </c>
+      <c r="D39" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="E39" s="98" t="s">
+      <c r="E39" s="93" t="s">
         <v>35</v>
       </c>
-      <c r="F39" s="97">
-        <v>2</v>
-      </c>
-      <c r="G39" s="97">
+      <c r="F39" s="92">
+        <v>2</v>
+      </c>
+      <c r="G39" s="92">
         <v>10</v>
       </c>
-      <c r="I39" s="89">
+      <c r="I39" s="84">
         <v>5</v>
       </c>
-      <c r="J39" s="90">
+      <c r="J39" s="85">
         <f>IF(F39&lt;=5,F$10+(I39-F39)/(G39-F39)*(G$10-F$10),"")</f>
         <v>176.625</v>
       </c>
-      <c r="K39" s="89" t="s">
+      <c r="K39" s="84" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="96"/>
-      <c r="B40" s="95"/>
-      <c r="C40" s="94"/>
-      <c r="D40" s="93" t="s">
+      <c r="A40" s="91"/>
+      <c r="B40" s="90"/>
+      <c r="C40" s="89"/>
+      <c r="D40" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="E40" s="92" t="s">
+      <c r="E40" s="87" t="s">
         <v>35</v>
       </c>
-      <c r="F40" s="91">
+      <c r="F40" s="86">
         <v>5</v>
       </c>
-      <c r="G40" s="91">
+      <c r="G40" s="86">
         <v>10</v>
       </c>
-      <c r="I40" s="89">
+      <c r="I40" s="84">
         <v>5</v>
       </c>
-      <c r="J40" s="90">
+      <c r="J40" s="85">
         <f>IF(F40&lt;=5,F$10+(I40-F40)/(G40-F40)*(G$10-F$10),"")</f>
         <v>174</v>
       </c>
-      <c r="K40" s="89" t="s">
+      <c r="K40" s="84" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="96"/>
-      <c r="B41" s="101" t="s">
-        <v>3</v>
-      </c>
-      <c r="C41" s="100">
-        <v>2</v>
-      </c>
-      <c r="D41" s="99" t="s">
+      <c r="A41" s="91"/>
+      <c r="B41" s="96" t="s">
+        <v>3</v>
+      </c>
+      <c r="C41" s="95">
+        <v>2</v>
+      </c>
+      <c r="D41" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="E41" s="98" t="s">
+      <c r="E41" s="93" t="s">
         <v>38</v>
       </c>
-      <c r="F41" s="97">
+      <c r="F41" s="92">
         <v>1</v>
       </c>
-      <c r="G41" s="97">
+      <c r="G41" s="92">
         <v>8</v>
       </c>
-      <c r="I41" s="89">
+      <c r="I41" s="84">
         <v>5</v>
       </c>
-      <c r="J41" s="90">
+      <c r="J41" s="85">
         <f>IF(F41&lt;=5,F$10+(I41-F41)/(G41-F41)*(G$10-F$10),"")</f>
         <v>178</v>
       </c>
-      <c r="K41" s="89" t="s">
+      <c r="K41" s="84" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="96"/>
-      <c r="B42" s="95"/>
-      <c r="C42" s="94"/>
-      <c r="D42" s="93" t="s">
+      <c r="A42" s="91"/>
+      <c r="B42" s="90"/>
+      <c r="C42" s="89"/>
+      <c r="D42" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="E42" s="92" t="s">
+      <c r="E42" s="87" t="s">
         <v>38</v>
       </c>
-      <c r="F42" s="91">
+      <c r="F42" s="86">
         <v>6</v>
       </c>
-      <c r="G42" s="91">
+      <c r="G42" s="86">
         <v>10</v>
       </c>
-      <c r="I42" s="89">
+      <c r="I42" s="84">
         <v>5</v>
       </c>
-      <c r="J42" s="90">
+      <c r="J42" s="85">
         <v>173</v>
       </c>
-      <c r="K42" s="89" t="s">
+      <c r="K42" s="84" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" s="96"/>
-      <c r="B43" s="101" t="s">
-        <v>3</v>
-      </c>
-      <c r="C43" s="100">
+      <c r="A43" s="91"/>
+      <c r="B43" s="96" t="s">
+        <v>3</v>
+      </c>
+      <c r="C43" s="95">
         <v>1</v>
       </c>
-      <c r="D43" s="99" t="s">
+      <c r="D43" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="E43" s="98" t="s">
+      <c r="E43" s="93" t="s">
         <v>35</v>
       </c>
-      <c r="F43" s="97">
+      <c r="F43" s="92">
         <v>8</v>
       </c>
-      <c r="G43" s="97">
+      <c r="G43" s="92">
         <v>10</v>
       </c>
-      <c r="I43" s="89">
+      <c r="I43" s="84">
         <v>5</v>
       </c>
-      <c r="J43" s="90">
+      <c r="J43" s="85">
         <v>171</v>
       </c>
-      <c r="K43" s="89" t="s">
+      <c r="K43" s="84" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="96"/>
-      <c r="B44" s="95"/>
-      <c r="C44" s="94"/>
-      <c r="D44" s="93" t="s">
+      <c r="A44" s="91"/>
+      <c r="B44" s="90"/>
+      <c r="C44" s="89"/>
+      <c r="D44" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="E44" s="92" t="s">
+      <c r="E44" s="87" t="s">
         <v>35</v>
       </c>
-      <c r="F44" s="91">
+      <c r="F44" s="86">
         <v>6</v>
       </c>
-      <c r="G44" s="91">
+      <c r="G44" s="86">
         <v>10</v>
       </c>
-      <c r="I44" s="89">
+      <c r="I44" s="84">
         <v>5</v>
       </c>
-      <c r="J44" s="90">
+      <c r="J44" s="85">
         <v>173</v>
       </c>
-      <c r="K44" s="89" t="s">
+      <c r="K44" s="84" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" s="96"/>
-      <c r="B45" s="101" t="s">
-        <v>4</v>
-      </c>
-      <c r="C45" s="100">
+      <c r="A45" s="91"/>
+      <c r="B45" s="96" t="s">
+        <v>4</v>
+      </c>
+      <c r="C45" s="95">
         <v>1</v>
       </c>
-      <c r="D45" s="99" t="s">
+      <c r="D45" s="94" t="s">
         <v>10</v>
       </c>
-      <c r="E45" s="98" t="s">
+      <c r="E45" s="93" t="s">
         <v>37</v>
       </c>
-      <c r="F45" s="97">
+      <c r="F45" s="92">
         <v>6</v>
       </c>
-      <c r="G45" s="97">
+      <c r="G45" s="92">
         <v>10</v>
       </c>
-      <c r="I45" s="89">
+      <c r="I45" s="84">
         <v>5</v>
       </c>
-      <c r="J45" s="90">
+      <c r="J45" s="85">
         <v>173</v>
       </c>
-      <c r="K45" s="89" t="s">
+      <c r="K45" s="84" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="96"/>
-      <c r="B46" s="95"/>
-      <c r="C46" s="94"/>
-      <c r="D46" s="93" t="s">
+      <c r="A46" s="91"/>
+      <c r="B46" s="90"/>
+      <c r="C46" s="89"/>
+      <c r="D46" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="E46" s="92" t="s">
+      <c r="E46" s="87" t="s">
         <v>37</v>
       </c>
-      <c r="F46" s="91">
-        <v>3</v>
-      </c>
-      <c r="G46" s="91">
+      <c r="F46" s="86">
+        <v>3</v>
+      </c>
+      <c r="G46" s="86">
         <v>9</v>
       </c>
-      <c r="I46" s="89">
+      <c r="I46" s="84">
         <v>5</v>
       </c>
-      <c r="J46" s="90">
+      <c r="J46" s="85">
         <f>IF(F46&lt;=5,F$10+(I46-F46)/(G46-F46)*(G$10-F$10),"")</f>
         <v>176.33333333333334</v>
       </c>
-      <c r="K46" s="89" t="s">
+      <c r="K46" s="84" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" s="96"/>
-      <c r="B47" s="101" t="s">
-        <v>4</v>
-      </c>
-      <c r="C47" s="100">
-        <v>2</v>
-      </c>
-      <c r="D47" s="99" t="s">
+      <c r="A47" s="91"/>
+      <c r="B47" s="96" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" s="95">
+        <v>2</v>
+      </c>
+      <c r="D47" s="94" t="s">
         <v>10</v>
       </c>
-      <c r="E47" s="98" t="s">
+      <c r="E47" s="93" t="s">
         <v>38</v>
       </c>
-      <c r="F47" s="97">
-        <v>2</v>
-      </c>
-      <c r="G47" s="97">
+      <c r="F47" s="92">
+        <v>2</v>
+      </c>
+      <c r="G47" s="92">
         <v>9</v>
       </c>
-      <c r="I47" s="89">
+      <c r="I47" s="84">
         <v>5</v>
       </c>
-      <c r="J47" s="90">
+      <c r="J47" s="85">
         <f>IF(F47&lt;=5,F$10+(I47-F47)/(G47-F47)*(G$10-F$10),"")</f>
         <v>177</v>
       </c>
-      <c r="K47" s="89" t="s">
+      <c r="K47" s="84" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="96"/>
-      <c r="B48" s="95"/>
-      <c r="C48" s="94"/>
-      <c r="D48" s="93" t="s">
+      <c r="A48" s="91"/>
+      <c r="B48" s="90"/>
+      <c r="C48" s="89"/>
+      <c r="D48" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="E48" s="92" t="s">
+      <c r="E48" s="87" t="s">
         <v>38</v>
       </c>
-      <c r="F48" s="91">
-        <v>3</v>
-      </c>
-      <c r="G48" s="91">
+      <c r="F48" s="86">
+        <v>3</v>
+      </c>
+      <c r="G48" s="86">
         <v>9</v>
       </c>
-      <c r="I48" s="89">
+      <c r="I48" s="84">
         <v>5</v>
       </c>
-      <c r="J48" s="90">
+      <c r="J48" s="85">
         <f>IF(F48&lt;=5,F$10+(I48-F48)/(G48-F48)*(G$10-F$10),"")</f>
         <v>176.33333333333334</v>
       </c>
-      <c r="K48" s="89" t="s">
+      <c r="K48" s="84" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A49" s="96"/>
-      <c r="B49" s="101" t="s">
-        <v>4</v>
-      </c>
-      <c r="C49" s="100">
-        <v>3</v>
-      </c>
-      <c r="D49" s="99" t="s">
+      <c r="A49" s="91"/>
+      <c r="B49" s="96" t="s">
+        <v>4</v>
+      </c>
+      <c r="C49" s="95">
+        <v>3</v>
+      </c>
+      <c r="D49" s="94" t="s">
         <v>10</v>
       </c>
-      <c r="E49" s="98" t="s">
+      <c r="E49" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="F49" s="97">
-        <v>2</v>
-      </c>
-      <c r="G49" s="97">
+      <c r="F49" s="92">
+        <v>2</v>
+      </c>
+      <c r="G49" s="92">
         <v>10</v>
       </c>
-      <c r="I49" s="89">
+      <c r="I49" s="84">
         <v>5</v>
       </c>
-      <c r="J49" s="90">
+      <c r="J49" s="85">
         <f>IF(F49&lt;=5,F$10+(I49-F49)/(G49-F49)*(G$10-F$10),"")</f>
         <v>176.625</v>
       </c>
-      <c r="K49" s="89" t="s">
+      <c r="K49" s="84" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="96"/>
-      <c r="B50" s="95"/>
-      <c r="C50" s="94"/>
-      <c r="D50" s="93" t="s">
+      <c r="A50" s="91"/>
+      <c r="B50" s="90"/>
+      <c r="C50" s="89"/>
+      <c r="D50" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="E50" s="92" t="s">
+      <c r="E50" s="87" t="s">
         <v>36</v>
       </c>
-      <c r="F50" s="91">
+      <c r="F50" s="86">
         <v>5</v>
       </c>
-      <c r="G50" s="91">
+      <c r="G50" s="86">
         <v>10</v>
       </c>
-      <c r="I50" s="89">
+      <c r="I50" s="84">
         <v>5</v>
       </c>
-      <c r="J50" s="90">
+      <c r="J50" s="85">
         <f>IF(F50&lt;=5,F$10+(I50-F50)/(G50-F50)*(G$10-F$10),"")</f>
         <v>174</v>
       </c>
-      <c r="K50" s="89" t="s">
+      <c r="K50" s="84" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A51" s="96"/>
-      <c r="B51" s="101" t="s">
-        <v>4</v>
-      </c>
-      <c r="C51" s="100">
-        <v>4</v>
-      </c>
-      <c r="D51" s="99" t="s">
+      <c r="A51" s="91"/>
+      <c r="B51" s="96" t="s">
+        <v>4</v>
+      </c>
+      <c r="C51" s="95">
+        <v>4</v>
+      </c>
+      <c r="D51" s="94" t="s">
         <v>10</v>
       </c>
-      <c r="E51" s="98" t="s">
+      <c r="E51" s="93" t="s">
         <v>35</v>
       </c>
-      <c r="F51" s="97">
+      <c r="F51" s="92">
         <v>6</v>
       </c>
-      <c r="G51" s="97">
+      <c r="G51" s="92">
         <v>10</v>
       </c>
-      <c r="I51" s="89">
+      <c r="I51" s="84">
         <v>5</v>
       </c>
-      <c r="J51" s="90">
+      <c r="J51" s="85">
         <v>173</v>
       </c>
-      <c r="K51" s="89" t="s">
+      <c r="K51" s="84" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="96"/>
-      <c r="B52" s="95"/>
-      <c r="C52" s="94"/>
-      <c r="D52" s="93" t="s">
+      <c r="A52" s="91"/>
+      <c r="B52" s="90"/>
+      <c r="C52" s="89"/>
+      <c r="D52" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="E52" s="92" t="s">
+      <c r="E52" s="87" t="s">
         <v>35</v>
       </c>
-      <c r="F52" s="91">
+      <c r="F52" s="86">
         <v>5</v>
       </c>
-      <c r="G52" s="91">
+      <c r="G52" s="86">
         <v>9</v>
       </c>
-      <c r="I52" s="89">
+      <c r="I52" s="84">
         <v>5</v>
       </c>
-      <c r="J52" s="90">
+      <c r="J52" s="85">
         <f>IF(F52&lt;=5,F$10+(I52-F52)/(G52-F52)*(G$10-F$10),"")</f>
         <v>174</v>
       </c>
-      <c r="K52" s="89" t="s">
+      <c r="K52" s="84" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A53" s="96"/>
-      <c r="B53" s="101" t="s">
+      <c r="A53" s="91"/>
+      <c r="B53" s="96" t="s">
         <v>5</v>
       </c>
-      <c r="C53" s="100">
-        <v>4</v>
-      </c>
-      <c r="D53" s="99" t="s">
+      <c r="C53" s="95">
+        <v>4</v>
+      </c>
+      <c r="D53" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="E53" s="98" t="s">
+      <c r="E53" s="93" t="s">
         <v>38</v>
       </c>
-      <c r="F53" s="97">
+      <c r="F53" s="92">
         <v>1</v>
       </c>
-      <c r="G53" s="97">
+      <c r="G53" s="92">
         <v>9</v>
       </c>
-      <c r="I53" s="89">
+      <c r="I53" s="84">
         <v>5</v>
       </c>
-      <c r="J53" s="90">
+      <c r="J53" s="85">
         <f>IF(F53&lt;=5,F$10+(I53-F53)/(G53-F53)*(G$10-F$10),"")</f>
         <v>177.5</v>
       </c>
-      <c r="K53" s="89" t="s">
+      <c r="K53" s="84" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="96"/>
-      <c r="B54" s="95"/>
-      <c r="C54" s="94"/>
-      <c r="D54" s="93" t="s">
+      <c r="A54" s="91"/>
+      <c r="B54" s="90"/>
+      <c r="C54" s="89"/>
+      <c r="D54" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="E54" s="92" t="s">
+      <c r="E54" s="87" t="s">
         <v>38</v>
       </c>
-      <c r="F54" s="91">
+      <c r="F54" s="86">
         <v>6</v>
       </c>
-      <c r="G54" s="91">
+      <c r="G54" s="86">
         <v>10</v>
       </c>
-      <c r="I54" s="89">
+      <c r="I54" s="84">
         <v>5</v>
       </c>
-      <c r="J54" s="90">
+      <c r="J54" s="85">
         <v>173</v>
       </c>
-      <c r="K54" s="89" t="s">
+      <c r="K54" s="84" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A55" s="96"/>
-      <c r="B55" s="101" t="s">
+      <c r="A55" s="91"/>
+      <c r="B55" s="96" t="s">
         <v>5</v>
       </c>
-      <c r="C55" s="100">
-        <v>3</v>
-      </c>
-      <c r="D55" s="99" t="s">
+      <c r="C55" s="95">
+        <v>3</v>
+      </c>
+      <c r="D55" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="E55" s="98" t="s">
+      <c r="E55" s="93" t="s">
         <v>49</v>
       </c>
-      <c r="F55" s="97">
-        <v>4</v>
-      </c>
-      <c r="G55" s="97">
+      <c r="F55" s="92">
+        <v>4</v>
+      </c>
+      <c r="G55" s="92">
         <v>10</v>
       </c>
-      <c r="I55" s="89">
+      <c r="I55" s="84">
         <v>5</v>
       </c>
-      <c r="J55" s="90">
-        <f>IF(F55&lt;=5,F$10+(I55-F55)/(G55-F55)*(G$10-F$10),"")</f>
+      <c r="J55" s="85">
+        <f t="shared" ref="J55:J60" si="1">IF(F55&lt;=5,F$10+(I55-F55)/(G55-F55)*(G$10-F$10),"")</f>
         <v>175.16666666666666</v>
       </c>
-      <c r="K55" s="89" t="s">
+      <c r="K55" s="84" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="96"/>
-      <c r="B56" s="95"/>
-      <c r="C56" s="94"/>
-      <c r="D56" s="93" t="s">
+      <c r="A56" s="91"/>
+      <c r="B56" s="90"/>
+      <c r="C56" s="89"/>
+      <c r="D56" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="E56" s="92" t="s">
+      <c r="E56" s="87" t="s">
         <v>37</v>
       </c>
-      <c r="F56" s="91">
-        <v>2</v>
-      </c>
-      <c r="G56" s="91">
+      <c r="F56" s="86">
+        <v>2</v>
+      </c>
+      <c r="G56" s="86">
         <v>8</v>
       </c>
-      <c r="I56" s="89">
+      <c r="I56" s="84">
         <v>5</v>
       </c>
-      <c r="J56" s="90">
-        <f>IF(F56&lt;=5,F$10+(I56-F56)/(G56-F56)*(G$10-F$10),"")</f>
+      <c r="J56" s="85">
+        <f t="shared" si="1"/>
         <v>177.5</v>
       </c>
-      <c r="K56" s="89" t="s">
+      <c r="K56" s="84" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A57" s="96"/>
-      <c r="B57" s="101" t="s">
+      <c r="A57" s="91"/>
+      <c r="B57" s="96" t="s">
         <v>5</v>
       </c>
-      <c r="C57" s="100">
-        <v>2</v>
-      </c>
-      <c r="D57" s="99" t="s">
+      <c r="C57" s="95">
+        <v>2</v>
+      </c>
+      <c r="D57" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="E57" s="98" t="s">
+      <c r="E57" s="93" t="s">
         <v>50</v>
       </c>
-      <c r="F57" s="97">
-        <v>3</v>
-      </c>
-      <c r="G57" s="97">
+      <c r="F57" s="92">
+        <v>3</v>
+      </c>
+      <c r="G57" s="92">
         <v>10</v>
       </c>
-      <c r="I57" s="89">
+      <c r="I57" s="84">
         <v>5</v>
       </c>
-      <c r="J57" s="90">
-        <f>IF(F57&lt;=5,F$10+(I57-F57)/(G57-F57)*(G$10-F$10),"")</f>
+      <c r="J57" s="85">
+        <f t="shared" si="1"/>
         <v>176</v>
       </c>
-      <c r="K57" s="89" t="s">
+      <c r="K57" s="84" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="96"/>
-      <c r="B58" s="95"/>
-      <c r="C58" s="94"/>
-      <c r="D58" s="93" t="s">
+      <c r="A58" s="91"/>
+      <c r="B58" s="90"/>
+      <c r="C58" s="89"/>
+      <c r="D58" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="E58" s="92" t="s">
+      <c r="E58" s="87" t="s">
         <v>50</v>
       </c>
-      <c r="F58" s="91">
+      <c r="F58" s="86">
         <v>5</v>
       </c>
-      <c r="G58" s="91">
+      <c r="G58" s="86">
         <v>9</v>
       </c>
-      <c r="I58" s="89">
+      <c r="I58" s="84">
         <v>5</v>
       </c>
-      <c r="J58" s="90">
-        <f>IF(F58&lt;=5,F$10+(I58-F58)/(G58-F58)*(G$10-F$10),"")</f>
+      <c r="J58" s="85">
+        <f t="shared" si="1"/>
         <v>174</v>
       </c>
-      <c r="K58" s="89" t="s">
+      <c r="K58" s="84" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A59" s="96"/>
-      <c r="B59" s="101" t="s">
+      <c r="A59" s="91"/>
+      <c r="B59" s="96" t="s">
         <v>5</v>
       </c>
-      <c r="C59" s="100">
+      <c r="C59" s="95">
         <v>1</v>
       </c>
-      <c r="D59" s="99" t="s">
+      <c r="D59" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="E59" s="98" t="s">
+      <c r="E59" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="F59" s="97">
+      <c r="F59" s="92">
         <v>0</v>
       </c>
-      <c r="G59" s="97">
+      <c r="G59" s="92">
         <v>8</v>
       </c>
-      <c r="I59" s="89">
+      <c r="I59" s="84">
         <v>5</v>
       </c>
-      <c r="J59" s="90">
-        <f>IF(F59&lt;=5,F$10+(I59-F59)/(G59-F59)*(G$10-F$10),"")</f>
+      <c r="J59" s="85">
+        <f t="shared" si="1"/>
         <v>178.375</v>
       </c>
-      <c r="K59" s="89" t="s">
+      <c r="K59" s="84" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="96"/>
-      <c r="B60" s="95"/>
-      <c r="C60" s="94"/>
-      <c r="D60" s="93" t="s">
+      <c r="A60" s="91"/>
+      <c r="B60" s="90"/>
+      <c r="C60" s="89"/>
+      <c r="D60" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="E60" s="92" t="s">
+      <c r="E60" s="87" t="s">
         <v>36</v>
       </c>
-      <c r="F60" s="91">
+      <c r="F60" s="86">
         <v>1</v>
       </c>
-      <c r="G60" s="91">
+      <c r="G60" s="86">
         <v>9</v>
       </c>
-      <c r="I60" s="89">
+      <c r="I60" s="84">
         <v>5</v>
       </c>
-      <c r="J60" s="90">
-        <f>IF(F60&lt;=5,F$10+(I60-F60)/(G60-F60)*(G$10-F$10),"")</f>
+      <c r="J60" s="85">
+        <f t="shared" si="1"/>
         <v>177.5</v>
       </c>
-      <c r="K60" s="89" t="s">
+      <c r="K60" s="84" t="s">
         <v>122</v>
       </c>
     </row>
@@ -11392,15 +11392,15 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="87" t="s">
+      <c r="B4" s="205" t="s">
         <v>159</v>
       </c>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
+      <c r="C4" s="208"/>
+      <c r="D4" s="208"/>
+      <c r="E4" s="208"/>
+      <c r="F4" s="208"/>
+      <c r="G4" s="208"/>
+      <c r="H4" s="208"/>
       <c r="I4" s="78"/>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -11413,10 +11413,10 @@
       <c r="I5" s="3"/>
     </row>
     <row r="6" spans="1:10" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="86" t="s">
+      <c r="B6" s="201" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="86"/>
+      <c r="C6" s="201"/>
       <c r="D6" s="76" t="s">
         <v>30</v>
       </c>
@@ -12221,15 +12221,15 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="87" t="s">
+      <c r="B4" s="205" t="s">
         <v>159</v>
       </c>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
+      <c r="C4" s="208"/>
+      <c r="D4" s="208"/>
+      <c r="E4" s="208"/>
+      <c r="F4" s="208"/>
+      <c r="G4" s="208"/>
+      <c r="H4" s="208"/>
       <c r="I4" s="78"/>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -12242,10 +12242,10 @@
       <c r="I5" s="3"/>
     </row>
     <row r="6" spans="1:10" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="86" t="s">
+      <c r="B6" s="201" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="86"/>
+      <c r="C6" s="201"/>
       <c r="D6" s="76" t="s">
         <v>30</v>
       </c>
@@ -13050,15 +13050,15 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="87" t="s">
+      <c r="B4" s="205" t="s">
         <v>159</v>
       </c>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
+      <c r="C4" s="208"/>
+      <c r="D4" s="208"/>
+      <c r="E4" s="208"/>
+      <c r="F4" s="208"/>
+      <c r="G4" s="208"/>
+      <c r="H4" s="208"/>
       <c r="I4" s="78"/>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -13073,10 +13073,10 @@
       <c r="I5" s="3"/>
     </row>
     <row r="6" spans="1:10" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="86" t="s">
+      <c r="B6" s="201" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="86"/>
+      <c r="C6" s="201"/>
       <c r="D6" s="76" t="s">
         <v>30</v>
       </c>
@@ -13881,15 +13881,15 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="87" t="s">
+      <c r="B4" s="205" t="s">
         <v>159</v>
       </c>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
+      <c r="C4" s="208"/>
+      <c r="D4" s="208"/>
+      <c r="E4" s="208"/>
+      <c r="F4" s="208"/>
+      <c r="G4" s="208"/>
+      <c r="H4" s="208"/>
       <c r="I4" s="78"/>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -13902,10 +13902,10 @@
       <c r="I5" s="3"/>
     </row>
     <row r="6" spans="1:11" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="86" t="s">
+      <c r="B6" s="201" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="86"/>
+      <c r="C6" s="201"/>
       <c r="D6" s="76" t="s">
         <v>30</v>
       </c>
@@ -17176,15 +17176,15 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="87" t="s">
+      <c r="B4" s="205" t="s">
         <v>159</v>
       </c>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
+      <c r="C4" s="208"/>
+      <c r="D4" s="208"/>
+      <c r="E4" s="208"/>
+      <c r="F4" s="208"/>
+      <c r="G4" s="208"/>
+      <c r="H4" s="208"/>
       <c r="I4" s="78"/>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -17197,10 +17197,10 @@
       <c r="I5" s="3"/>
     </row>
     <row r="6" spans="1:10" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="86" t="s">
+      <c r="B6" s="201" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="86"/>
+      <c r="C6" s="201"/>
       <c r="D6" s="76" t="s">
         <v>30</v>
       </c>
@@ -18005,15 +18005,15 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="87" t="s">
+      <c r="B4" s="205" t="s">
         <v>159</v>
       </c>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
+      <c r="C4" s="208"/>
+      <c r="D4" s="208"/>
+      <c r="E4" s="208"/>
+      <c r="F4" s="208"/>
+      <c r="G4" s="208"/>
+      <c r="H4" s="208"/>
       <c r="I4" s="78"/>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -18026,10 +18026,10 @@
       <c r="I5" s="3"/>
     </row>
     <row r="6" spans="1:10" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="86" t="s">
+      <c r="B6" s="201" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="86"/>
+      <c r="C6" s="201"/>
       <c r="D6" s="76" t="s">
         <v>30</v>
       </c>
@@ -18834,15 +18834,15 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="87" t="s">
+      <c r="B4" s="205" t="s">
         <v>159</v>
       </c>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
+      <c r="C4" s="208"/>
+      <c r="D4" s="208"/>
+      <c r="E4" s="208"/>
+      <c r="F4" s="208"/>
+      <c r="G4" s="208"/>
+      <c r="H4" s="208"/>
       <c r="I4" s="78"/>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -18855,10 +18855,10 @@
       <c r="I5" s="3"/>
     </row>
     <row r="6" spans="1:10" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="86" t="s">
+      <c r="B6" s="201" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="86"/>
+      <c r="C6" s="201"/>
       <c r="D6" s="76" t="s">
         <v>30</v>
       </c>
@@ -20775,13 +20775,13 @@
       <c r="A2" t="s">
         <v>82</v>
       </c>
-      <c r="B2" s="186"/>
-      <c r="D2" s="208"/>
-      <c r="E2" s="186"/>
-      <c r="F2" s="186">
+      <c r="B2" s="178"/>
+      <c r="D2" s="198"/>
+      <c r="E2" s="178"/>
+      <c r="F2" s="178">
         <v>44006</v>
       </c>
-      <c r="G2" s="126">
+      <c r="G2" s="120">
         <v>176.33333333333334</v>
       </c>
     </row>
@@ -20789,11 +20789,11 @@
       <c r="A3" t="s">
         <v>130</v>
       </c>
-      <c r="B3" s="186"/>
-      <c r="D3" s="208"/>
-      <c r="E3" s="186"/>
-      <c r="F3" s="186"/>
-      <c r="G3" s="126"/>
+      <c r="B3" s="178"/>
+      <c r="D3" s="198"/>
+      <c r="E3" s="178"/>
+      <c r="F3" s="178"/>
+      <c r="G3" s="120"/>
       <c r="H3" s="83">
         <v>3.5</v>
       </c>
@@ -20826,13 +20826,13 @@
       <c r="A4" t="s">
         <v>83</v>
       </c>
-      <c r="B4" s="186"/>
-      <c r="D4" s="208"/>
-      <c r="E4" s="186"/>
-      <c r="F4" s="186">
+      <c r="B4" s="178"/>
+      <c r="D4" s="198"/>
+      <c r="E4" s="178"/>
+      <c r="F4" s="178">
         <v>44004</v>
       </c>
-      <c r="G4" s="126">
+      <c r="G4" s="120">
         <v>174</v>
       </c>
       <c r="H4" s="83"/>
@@ -20849,20 +20849,20 @@
       <c r="A5" t="s">
         <v>232</v>
       </c>
-      <c r="B5" s="186">
+      <c r="B5" s="178">
         <v>43950</v>
       </c>
       <c r="C5">
         <v>2020</v>
       </c>
-      <c r="D5" s="208">
+      <c r="D5" s="198">
         <v>120.125</v>
       </c>
-      <c r="E5" s="186">
+      <c r="E5" s="178">
         <v>43959</v>
       </c>
-      <c r="F5" s="186"/>
-      <c r="G5" s="126"/>
+      <c r="F5" s="178"/>
+      <c r="G5" s="120"/>
       <c r="H5" s="83"/>
       <c r="I5" s="83"/>
       <c r="J5" s="83"/>
@@ -20877,13 +20877,13 @@
       <c r="A6" t="s">
         <v>84</v>
       </c>
-      <c r="B6" s="186"/>
-      <c r="D6" s="208"/>
-      <c r="E6" s="186"/>
-      <c r="F6" s="186">
+      <c r="B6" s="178"/>
+      <c r="D6" s="198"/>
+      <c r="E6" s="178"/>
+      <c r="F6" s="178">
         <v>44006</v>
       </c>
-      <c r="G6" s="126">
+      <c r="G6" s="120">
         <v>176</v>
       </c>
       <c r="H6" s="83"/>
@@ -20900,11 +20900,11 @@
       <c r="A7" t="s">
         <v>131</v>
       </c>
-      <c r="B7" s="186"/>
-      <c r="D7" s="208"/>
-      <c r="E7" s="186"/>
-      <c r="F7" s="186"/>
-      <c r="G7" s="126"/>
+      <c r="B7" s="178"/>
+      <c r="D7" s="198"/>
+      <c r="E7" s="178"/>
+      <c r="F7" s="178"/>
+      <c r="G7" s="120"/>
       <c r="H7" s="83">
         <v>2.5</v>
       </c>
@@ -20937,13 +20937,13 @@
       <c r="A8" t="s">
         <v>85</v>
       </c>
-      <c r="B8" s="186"/>
-      <c r="D8" s="208"/>
-      <c r="E8" s="186"/>
-      <c r="F8" s="186">
+      <c r="B8" s="178"/>
+      <c r="D8" s="198"/>
+      <c r="E8" s="178"/>
+      <c r="F8" s="178">
         <v>44002</v>
       </c>
-      <c r="G8" s="126">
+      <c r="G8" s="120">
         <v>172</v>
       </c>
       <c r="H8" s="83"/>
@@ -20960,20 +20960,20 @@
       <c r="A9" t="s">
         <v>233</v>
       </c>
-      <c r="B9" s="186">
+      <c r="B9" s="178">
         <v>43950</v>
       </c>
       <c r="C9">
         <v>2020</v>
       </c>
-      <c r="D9" s="208">
+      <c r="D9" s="198">
         <v>119.83333333333333</v>
       </c>
-      <c r="E9" s="186">
+      <c r="E9" s="178">
         <v>43959</v>
       </c>
-      <c r="F9" s="186"/>
-      <c r="G9" s="126"/>
+      <c r="F9" s="178"/>
+      <c r="G9" s="120"/>
       <c r="H9" s="83"/>
       <c r="I9" s="83"/>
       <c r="J9" s="83"/>
@@ -20988,13 +20988,13 @@
       <c r="A10" t="s">
         <v>86</v>
       </c>
-      <c r="B10" s="186"/>
-      <c r="D10" s="208"/>
-      <c r="E10" s="186"/>
-      <c r="F10" s="186">
+      <c r="B10" s="178"/>
+      <c r="D10" s="198"/>
+      <c r="E10" s="178"/>
+      <c r="F10" s="178">
         <v>44001</v>
       </c>
-      <c r="G10" s="126">
+      <c r="G10" s="120">
         <v>171</v>
       </c>
       <c r="H10" s="83"/>
@@ -21011,11 +21011,11 @@
       <c r="A11" t="s">
         <v>132</v>
       </c>
-      <c r="B11" s="186"/>
-      <c r="D11" s="208"/>
-      <c r="E11" s="186"/>
-      <c r="F11" s="186"/>
-      <c r="G11" s="126"/>
+      <c r="B11" s="178"/>
+      <c r="D11" s="198"/>
+      <c r="E11" s="178"/>
+      <c r="F11" s="178"/>
+      <c r="G11" s="120"/>
       <c r="H11" s="83">
         <v>2.6666666666666665</v>
       </c>
@@ -21048,13 +21048,13 @@
       <c r="A12" t="s">
         <v>87</v>
       </c>
-      <c r="B12" s="186"/>
-      <c r="D12" s="208"/>
-      <c r="E12" s="186"/>
-      <c r="F12" s="186">
+      <c r="B12" s="178"/>
+      <c r="D12" s="198"/>
+      <c r="E12" s="178"/>
+      <c r="F12" s="178">
         <v>44002</v>
       </c>
-      <c r="G12" s="126">
+      <c r="G12" s="120">
         <v>172</v>
       </c>
       <c r="H12" s="83"/>
@@ -21071,20 +21071,20 @@
       <c r="A13" t="s">
         <v>234</v>
       </c>
-      <c r="B13" s="186">
+      <c r="B13" s="178">
         <v>43950</v>
       </c>
       <c r="C13">
         <v>2020</v>
       </c>
-      <c r="D13" s="208">
+      <c r="D13" s="198">
         <v>120</v>
       </c>
-      <c r="E13" s="186">
+      <c r="E13" s="178">
         <v>43959</v>
       </c>
-      <c r="F13" s="186"/>
-      <c r="G13" s="126"/>
+      <c r="F13" s="178"/>
+      <c r="G13" s="120"/>
       <c r="H13" s="83"/>
       <c r="I13" s="83"/>
       <c r="J13" s="83"/>
@@ -21099,13 +21099,13 @@
       <c r="A14" t="s">
         <v>88</v>
       </c>
-      <c r="B14" s="186"/>
-      <c r="D14" s="208"/>
-      <c r="E14" s="186"/>
-      <c r="F14" s="186">
+      <c r="B14" s="178"/>
+      <c r="D14" s="198"/>
+      <c r="E14" s="178"/>
+      <c r="F14" s="178">
         <v>44002</v>
       </c>
-      <c r="G14" s="126">
+      <c r="G14" s="120">
         <v>172</v>
       </c>
       <c r="H14" s="83"/>
@@ -21122,11 +21122,11 @@
       <c r="A15" t="s">
         <v>133</v>
       </c>
-      <c r="B15" s="186"/>
-      <c r="D15" s="208"/>
-      <c r="E15" s="186"/>
-      <c r="F15" s="186"/>
-      <c r="G15" s="126"/>
+      <c r="B15" s="178"/>
+      <c r="D15" s="198"/>
+      <c r="E15" s="178"/>
+      <c r="F15" s="178"/>
+      <c r="G15" s="120"/>
       <c r="H15" s="83">
         <v>3.5</v>
       </c>
@@ -21159,13 +21159,13 @@
       <c r="A16" t="s">
         <v>89</v>
       </c>
-      <c r="B16" s="186"/>
-      <c r="D16" s="208"/>
-      <c r="E16" s="186"/>
-      <c r="F16" s="186">
+      <c r="B16" s="178"/>
+      <c r="D16" s="198"/>
+      <c r="E16" s="178"/>
+      <c r="F16" s="178">
         <v>44001</v>
       </c>
-      <c r="G16" s="126">
+      <c r="G16" s="120">
         <v>171</v>
       </c>
       <c r="H16" s="83"/>
@@ -21182,20 +21182,20 @@
       <c r="A17" t="s">
         <v>235</v>
       </c>
-      <c r="B17" s="186">
+      <c r="B17" s="178">
         <v>43950</v>
       </c>
       <c r="C17">
         <v>2020</v>
       </c>
-      <c r="D17" s="208">
+      <c r="D17" s="198">
         <v>120.16666666666667</v>
       </c>
-      <c r="E17" s="186">
+      <c r="E17" s="178">
         <v>43959</v>
       </c>
-      <c r="F17" s="186"/>
-      <c r="G17" s="126"/>
+      <c r="F17" s="178"/>
+      <c r="G17" s="120"/>
       <c r="H17" s="83"/>
       <c r="I17" s="83"/>
       <c r="J17" s="83"/>
@@ -21210,13 +21210,13 @@
       <c r="A18" t="s">
         <v>90</v>
       </c>
-      <c r="B18" s="186"/>
-      <c r="D18" s="208"/>
-      <c r="E18" s="186"/>
-      <c r="F18" s="186">
+      <c r="B18" s="178"/>
+      <c r="D18" s="198"/>
+      <c r="E18" s="178"/>
+      <c r="F18" s="178">
         <v>44006</v>
       </c>
-      <c r="G18" s="126">
+      <c r="G18" s="120">
         <v>176</v>
       </c>
       <c r="H18" s="83"/>
@@ -21233,11 +21233,11 @@
       <c r="A19" t="s">
         <v>134</v>
       </c>
-      <c r="B19" s="186"/>
-      <c r="D19" s="208"/>
-      <c r="E19" s="186"/>
-      <c r="F19" s="186"/>
-      <c r="G19" s="126"/>
+      <c r="B19" s="178"/>
+      <c r="D19" s="198"/>
+      <c r="E19" s="178"/>
+      <c r="F19" s="178"/>
+      <c r="G19" s="120"/>
       <c r="H19" s="83">
         <v>3.5</v>
       </c>
@@ -21270,13 +21270,13 @@
       <c r="A20" t="s">
         <v>91</v>
       </c>
-      <c r="B20" s="186"/>
-      <c r="D20" s="208"/>
-      <c r="E20" s="186"/>
-      <c r="F20" s="186">
+      <c r="B20" s="178"/>
+      <c r="D20" s="198"/>
+      <c r="E20" s="178"/>
+      <c r="F20" s="178">
         <v>44007</v>
       </c>
-      <c r="G20" s="126">
+      <c r="G20" s="120">
         <v>176.625</v>
       </c>
       <c r="H20" s="83"/>
@@ -21293,20 +21293,20 @@
       <c r="A21" t="s">
         <v>255</v>
       </c>
-      <c r="B21" s="186">
+      <c r="B21" s="178">
         <v>43950</v>
       </c>
       <c r="C21">
         <v>2020</v>
       </c>
-      <c r="D21" s="208">
+      <c r="D21" s="198">
         <v>120.4</v>
       </c>
-      <c r="E21" s="186">
+      <c r="E21" s="178">
         <v>43959</v>
       </c>
-      <c r="F21" s="186"/>
-      <c r="G21" s="126"/>
+      <c r="F21" s="178"/>
+      <c r="G21" s="120"/>
       <c r="H21" s="83"/>
       <c r="I21" s="83"/>
       <c r="J21" s="83"/>
@@ -21321,13 +21321,13 @@
       <c r="A22" t="s">
         <v>92</v>
       </c>
-      <c r="B22" s="186"/>
-      <c r="D22" s="208"/>
-      <c r="E22" s="186"/>
-      <c r="F22" s="186">
+      <c r="B22" s="178"/>
+      <c r="D22" s="198"/>
+      <c r="E22" s="178"/>
+      <c r="F22" s="178">
         <v>44003</v>
       </c>
-      <c r="G22" s="126">
+      <c r="G22" s="120">
         <v>173</v>
       </c>
       <c r="H22" s="83"/>
@@ -21344,11 +21344,11 @@
       <c r="A23" t="s">
         <v>135</v>
       </c>
-      <c r="B23" s="186"/>
-      <c r="D23" s="208"/>
-      <c r="E23" s="186"/>
-      <c r="F23" s="186"/>
-      <c r="G23" s="126"/>
+      <c r="B23" s="178"/>
+      <c r="D23" s="198"/>
+      <c r="E23" s="178"/>
+      <c r="F23" s="178"/>
+      <c r="G23" s="120"/>
       <c r="H23" s="83">
         <v>3.5</v>
       </c>
@@ -21381,13 +21381,13 @@
       <c r="A24" t="s">
         <v>93</v>
       </c>
-      <c r="B24" s="186"/>
-      <c r="D24" s="208"/>
-      <c r="E24" s="186"/>
-      <c r="F24" s="186">
+      <c r="B24" s="178"/>
+      <c r="D24" s="198"/>
+      <c r="E24" s="178"/>
+      <c r="F24" s="178">
         <v>44004</v>
       </c>
-      <c r="G24" s="126">
+      <c r="G24" s="120">
         <v>174</v>
       </c>
       <c r="H24" s="83"/>
@@ -21404,20 +21404,20 @@
       <c r="A25" t="s">
         <v>254</v>
       </c>
-      <c r="B25" s="186">
+      <c r="B25" s="178">
         <v>43951</v>
       </c>
       <c r="C25">
         <v>2020</v>
       </c>
-      <c r="D25" s="208">
+      <c r="D25" s="198">
         <v>120.5</v>
       </c>
-      <c r="E25" s="186">
+      <c r="E25" s="178">
         <v>43960</v>
       </c>
-      <c r="F25" s="186"/>
-      <c r="G25" s="126"/>
+      <c r="F25" s="178"/>
+      <c r="G25" s="120"/>
       <c r="H25" s="83"/>
       <c r="I25" s="83"/>
       <c r="J25" s="83"/>
@@ -21432,13 +21432,13 @@
       <c r="A26" t="s">
         <v>94</v>
       </c>
-      <c r="B26" s="186"/>
-      <c r="D26" s="208"/>
-      <c r="E26" s="186"/>
-      <c r="F26" s="186">
+      <c r="B26" s="178"/>
+      <c r="D26" s="198"/>
+      <c r="E26" s="178"/>
+      <c r="F26" s="178">
         <v>44003</v>
       </c>
-      <c r="G26" s="126">
+      <c r="G26" s="120">
         <v>173</v>
       </c>
       <c r="H26" s="83"/>
@@ -21455,11 +21455,11 @@
       <c r="A27" t="s">
         <v>136</v>
       </c>
-      <c r="B27" s="186"/>
-      <c r="D27" s="208"/>
-      <c r="E27" s="186"/>
-      <c r="F27" s="186"/>
-      <c r="G27" s="126"/>
+      <c r="B27" s="178"/>
+      <c r="D27" s="198"/>
+      <c r="E27" s="178"/>
+      <c r="F27" s="178"/>
+      <c r="G27" s="120"/>
       <c r="H27" s="83">
         <v>3</v>
       </c>
@@ -21492,13 +21492,13 @@
       <c r="A28" t="s">
         <v>95</v>
       </c>
-      <c r="B28" s="186"/>
-      <c r="D28" s="208"/>
-      <c r="E28" s="186"/>
-      <c r="F28" s="186">
+      <c r="B28" s="178"/>
+      <c r="D28" s="198"/>
+      <c r="E28" s="178"/>
+      <c r="F28" s="178">
         <v>44001</v>
       </c>
-      <c r="G28" s="126">
+      <c r="G28" s="120">
         <v>171</v>
       </c>
       <c r="H28" s="83"/>
@@ -21515,20 +21515,20 @@
       <c r="A29" t="s">
         <v>253</v>
       </c>
-      <c r="B29" s="186">
+      <c r="B29" s="178">
         <v>43951</v>
       </c>
       <c r="C29">
         <v>2020</v>
       </c>
-      <c r="D29" s="208">
+      <c r="D29" s="198">
         <v>120.5</v>
       </c>
-      <c r="E29" s="186">
+      <c r="E29" s="178">
         <v>43960</v>
       </c>
-      <c r="F29" s="186"/>
-      <c r="G29" s="126"/>
+      <c r="F29" s="178"/>
+      <c r="G29" s="120"/>
       <c r="H29" s="83"/>
       <c r="I29" s="83"/>
       <c r="J29" s="83"/>
@@ -21543,13 +21543,13 @@
       <c r="A30" t="s">
         <v>96</v>
       </c>
-      <c r="B30" s="186"/>
-      <c r="D30" s="208"/>
-      <c r="E30" s="186"/>
-      <c r="F30" s="186">
+      <c r="B30" s="178"/>
+      <c r="D30" s="198"/>
+      <c r="E30" s="178"/>
+      <c r="F30" s="178">
         <v>44004</v>
       </c>
-      <c r="G30" s="126">
+      <c r="G30" s="120">
         <v>174</v>
       </c>
       <c r="H30" s="83"/>
@@ -21566,11 +21566,11 @@
       <c r="A31" t="s">
         <v>137</v>
       </c>
-      <c r="B31" s="186"/>
-      <c r="D31" s="208"/>
-      <c r="E31" s="186"/>
-      <c r="F31" s="186"/>
-      <c r="G31" s="126"/>
+      <c r="B31" s="178"/>
+      <c r="D31" s="198"/>
+      <c r="E31" s="178"/>
+      <c r="F31" s="178"/>
+      <c r="G31" s="120"/>
       <c r="H31" s="83">
         <v>3</v>
       </c>
@@ -21603,13 +21603,13 @@
       <c r="A32" t="s">
         <v>97</v>
       </c>
-      <c r="B32" s="186"/>
-      <c r="D32" s="208"/>
-      <c r="E32" s="186"/>
-      <c r="F32" s="186">
+      <c r="B32" s="178"/>
+      <c r="D32" s="198"/>
+      <c r="E32" s="178"/>
+      <c r="F32" s="178">
         <v>44004</v>
       </c>
-      <c r="G32" s="126">
+      <c r="G32" s="120">
         <v>174</v>
       </c>
       <c r="H32" s="83"/>
@@ -21626,20 +21626,20 @@
       <c r="A33" t="s">
         <v>236</v>
       </c>
-      <c r="B33" s="186">
+      <c r="B33" s="178">
         <v>43951</v>
       </c>
       <c r="C33">
         <v>2020</v>
       </c>
-      <c r="D33" s="208">
+      <c r="D33" s="198">
         <v>120.66666666666667</v>
       </c>
-      <c r="E33" s="186">
+      <c r="E33" s="178">
         <v>43961</v>
       </c>
-      <c r="F33" s="186"/>
-      <c r="G33" s="126"/>
+      <c r="F33" s="178"/>
+      <c r="G33" s="120"/>
       <c r="H33" s="83"/>
       <c r="I33" s="83"/>
       <c r="J33" s="83"/>
@@ -21654,13 +21654,13 @@
       <c r="A34" t="s">
         <v>98</v>
       </c>
-      <c r="B34" s="186"/>
-      <c r="D34" s="208"/>
-      <c r="E34" s="186"/>
-      <c r="F34" s="186">
+      <c r="B34" s="178"/>
+      <c r="D34" s="198"/>
+      <c r="E34" s="178"/>
+      <c r="F34" s="178">
         <v>44007</v>
       </c>
-      <c r="G34" s="126">
+      <c r="G34" s="120">
         <v>177.11111111111111</v>
       </c>
       <c r="H34" s="83"/>
@@ -21677,11 +21677,11 @@
       <c r="A35" t="s">
         <v>138</v>
       </c>
-      <c r="B35" s="186"/>
-      <c r="D35" s="208"/>
-      <c r="E35" s="186"/>
-      <c r="F35" s="186"/>
-      <c r="G35" s="126"/>
+      <c r="B35" s="178"/>
+      <c r="D35" s="198"/>
+      <c r="E35" s="178"/>
+      <c r="F35" s="178"/>
+      <c r="G35" s="120"/>
       <c r="H35" s="83">
         <v>3.3333333333333335</v>
       </c>
@@ -21714,13 +21714,13 @@
       <c r="A36" t="s">
         <v>99</v>
       </c>
-      <c r="B36" s="186"/>
-      <c r="D36" s="208"/>
-      <c r="E36" s="186"/>
-      <c r="F36" s="186">
+      <c r="B36" s="178"/>
+      <c r="D36" s="198"/>
+      <c r="E36" s="178"/>
+      <c r="F36" s="178">
         <v>44006</v>
       </c>
-      <c r="G36" s="126">
+      <c r="G36" s="120">
         <v>176.33333333333334</v>
       </c>
       <c r="H36" s="83"/>
@@ -21737,20 +21737,20 @@
       <c r="A37" t="s">
         <v>237</v>
       </c>
-      <c r="B37" s="186">
+      <c r="B37" s="178">
         <v>43950</v>
       </c>
       <c r="C37">
         <v>2020</v>
       </c>
-      <c r="D37" s="208">
+      <c r="D37" s="198">
         <v>120.41666666666667</v>
       </c>
-      <c r="E37" s="186">
+      <c r="E37" s="178">
         <v>43961</v>
       </c>
-      <c r="F37" s="186"/>
-      <c r="G37" s="126"/>
+      <c r="F37" s="178"/>
+      <c r="G37" s="120"/>
       <c r="H37" s="83"/>
       <c r="I37" s="83"/>
       <c r="J37" s="83"/>
@@ -21765,13 +21765,13 @@
       <c r="A38" t="s">
         <v>100</v>
       </c>
-      <c r="B38" s="186"/>
-      <c r="D38" s="208"/>
-      <c r="E38" s="186"/>
-      <c r="F38" s="186">
+      <c r="B38" s="178"/>
+      <c r="D38" s="198"/>
+      <c r="E38" s="178"/>
+      <c r="F38" s="178">
         <v>44008</v>
       </c>
-      <c r="G38" s="126">
+      <c r="G38" s="120">
         <v>177.5</v>
       </c>
       <c r="H38" s="83"/>
@@ -21788,11 +21788,11 @@
       <c r="A39" t="s">
         <v>139</v>
       </c>
-      <c r="B39" s="186"/>
-      <c r="D39" s="208"/>
-      <c r="E39" s="186"/>
-      <c r="F39" s="186"/>
-      <c r="G39" s="126"/>
+      <c r="B39" s="178"/>
+      <c r="D39" s="198"/>
+      <c r="E39" s="178"/>
+      <c r="F39" s="178"/>
+      <c r="G39" s="120"/>
       <c r="H39" s="83">
         <v>3.5</v>
       </c>
@@ -21825,13 +21825,13 @@
       <c r="A40" t="s">
         <v>101</v>
       </c>
-      <c r="B40" s="186"/>
-      <c r="D40" s="208"/>
-      <c r="E40" s="186"/>
-      <c r="F40" s="186">
+      <c r="B40" s="178"/>
+      <c r="D40" s="198"/>
+      <c r="E40" s="178"/>
+      <c r="F40" s="178">
         <v>44007</v>
       </c>
-      <c r="G40" s="126">
+      <c r="G40" s="120">
         <v>176.625</v>
       </c>
       <c r="H40" s="83"/>
@@ -21848,20 +21848,20 @@
       <c r="A41" t="s">
         <v>238</v>
       </c>
-      <c r="B41" s="186">
+      <c r="B41" s="178">
         <v>43951</v>
       </c>
       <c r="C41">
         <v>2020</v>
       </c>
-      <c r="D41" s="208">
+      <c r="D41" s="198">
         <v>120.5</v>
       </c>
-      <c r="E41" s="186">
+      <c r="E41" s="178">
         <v>43960</v>
       </c>
-      <c r="F41" s="186"/>
-      <c r="G41" s="126"/>
+      <c r="F41" s="178"/>
+      <c r="G41" s="120"/>
       <c r="H41" s="83"/>
       <c r="I41" s="83"/>
       <c r="J41" s="83"/>
@@ -21876,13 +21876,13 @@
       <c r="A42" t="s">
         <v>102</v>
       </c>
-      <c r="B42" s="186"/>
-      <c r="D42" s="208"/>
-      <c r="E42" s="186"/>
-      <c r="F42" s="186">
+      <c r="B42" s="178"/>
+      <c r="D42" s="198"/>
+      <c r="E42" s="178"/>
+      <c r="F42" s="178">
         <v>44008</v>
       </c>
-      <c r="G42" s="126">
+      <c r="G42" s="120">
         <v>178.375</v>
       </c>
       <c r="H42" s="83"/>
@@ -21899,11 +21899,11 @@
       <c r="A43" t="s">
         <v>140</v>
       </c>
-      <c r="B43" s="186"/>
-      <c r="D43" s="208"/>
-      <c r="E43" s="186"/>
-      <c r="F43" s="186"/>
-      <c r="G43" s="126"/>
+      <c r="B43" s="178"/>
+      <c r="D43" s="198"/>
+      <c r="E43" s="178"/>
+      <c r="F43" s="178"/>
+      <c r="G43" s="120"/>
       <c r="H43" s="83">
         <v>3.6666666666666665</v>
       </c>
@@ -21936,13 +21936,13 @@
       <c r="A44" t="s">
         <v>103</v>
       </c>
-      <c r="B44" s="186"/>
-      <c r="D44" s="208"/>
-      <c r="E44" s="186"/>
-      <c r="F44" s="186">
+      <c r="B44" s="178"/>
+      <c r="D44" s="198"/>
+      <c r="E44" s="178"/>
+      <c r="F44" s="178">
         <v>44004</v>
       </c>
-      <c r="G44" s="126">
+      <c r="G44" s="120">
         <v>174</v>
       </c>
       <c r="H44" s="83"/>
@@ -21959,20 +21959,20 @@
       <c r="A45" t="s">
         <v>239</v>
       </c>
-      <c r="B45" s="186">
+      <c r="B45" s="178">
         <v>43950</v>
       </c>
       <c r="C45">
         <v>2020</v>
       </c>
-      <c r="D45" s="208">
+      <c r="D45" s="198">
         <v>120.4</v>
       </c>
-      <c r="E45" s="186">
+      <c r="E45" s="178">
         <v>43959</v>
       </c>
-      <c r="F45" s="186"/>
-      <c r="G45" s="126"/>
+      <c r="F45" s="178"/>
+      <c r="G45" s="120"/>
       <c r="H45" s="83"/>
       <c r="I45" s="83"/>
       <c r="J45" s="83"/>
@@ -21987,13 +21987,13 @@
       <c r="A46" t="s">
         <v>104</v>
       </c>
-      <c r="B46" s="186"/>
-      <c r="D46" s="208"/>
-      <c r="E46" s="186"/>
-      <c r="F46" s="186">
+      <c r="B46" s="178"/>
+      <c r="D46" s="198"/>
+      <c r="E46" s="178"/>
+      <c r="F46" s="178">
         <v>44006</v>
       </c>
-      <c r="G46" s="126">
+      <c r="G46" s="120">
         <v>176</v>
       </c>
       <c r="H46" s="83"/>
@@ -22010,11 +22010,11 @@
       <c r="A47" t="s">
         <v>141</v>
       </c>
-      <c r="B47" s="186"/>
-      <c r="D47" s="208"/>
-      <c r="E47" s="186"/>
-      <c r="F47" s="186"/>
-      <c r="G47" s="126"/>
+      <c r="B47" s="178"/>
+      <c r="D47" s="198"/>
+      <c r="E47" s="178"/>
+      <c r="F47" s="178"/>
+      <c r="G47" s="120"/>
       <c r="H47" s="83">
         <v>3.6666666666666665</v>
       </c>
@@ -22047,13 +22047,13 @@
       <c r="A48" t="s">
         <v>105</v>
       </c>
-      <c r="B48" s="186"/>
-      <c r="D48" s="208"/>
-      <c r="E48" s="186"/>
-      <c r="F48" s="186">
+      <c r="B48" s="178"/>
+      <c r="D48" s="198"/>
+      <c r="E48" s="178"/>
+      <c r="F48" s="178">
         <v>44007</v>
       </c>
-      <c r="G48" s="126">
+      <c r="G48" s="120">
         <v>177</v>
       </c>
       <c r="H48" s="83"/>
@@ -22070,20 +22070,20 @@
       <c r="A49" t="s">
         <v>240</v>
       </c>
-      <c r="B49" s="186">
+      <c r="B49" s="178">
         <v>43953</v>
       </c>
       <c r="C49">
         <v>2020</v>
       </c>
-      <c r="D49" s="208">
+      <c r="D49" s="198">
         <v>123</v>
       </c>
-      <c r="E49" s="186">
+      <c r="E49" s="178">
         <v>43962</v>
       </c>
-      <c r="F49" s="186"/>
-      <c r="G49" s="126"/>
+      <c r="F49" s="178"/>
+      <c r="G49" s="120"/>
       <c r="H49" s="83"/>
       <c r="I49" s="83"/>
       <c r="J49" s="83"/>
@@ -22098,13 +22098,13 @@
       <c r="A50" t="s">
         <v>106</v>
       </c>
-      <c r="B50" s="186"/>
-      <c r="D50" s="208"/>
-      <c r="E50" s="186"/>
-      <c r="F50" s="186">
+      <c r="B50" s="178"/>
+      <c r="D50" s="198"/>
+      <c r="E50" s="178"/>
+      <c r="F50" s="178">
         <v>44003</v>
       </c>
-      <c r="G50" s="126">
+      <c r="G50" s="120">
         <v>173</v>
       </c>
       <c r="H50" s="83"/>
@@ -22121,11 +22121,11 @@
       <c r="A51" t="s">
         <v>142</v>
       </c>
-      <c r="B51" s="186"/>
-      <c r="D51" s="208"/>
-      <c r="E51" s="186"/>
-      <c r="F51" s="186"/>
-      <c r="G51" s="126"/>
+      <c r="B51" s="178"/>
+      <c r="D51" s="198"/>
+      <c r="E51" s="178"/>
+      <c r="F51" s="178"/>
+      <c r="G51" s="120"/>
       <c r="H51" s="83">
         <v>3</v>
       </c>
@@ -22158,13 +22158,13 @@
       <c r="A52" t="s">
         <v>107</v>
       </c>
-      <c r="B52" s="186"/>
-      <c r="D52" s="208"/>
-      <c r="E52" s="186"/>
-      <c r="F52" s="186">
+      <c r="B52" s="178"/>
+      <c r="D52" s="198"/>
+      <c r="E52" s="178"/>
+      <c r="F52" s="178">
         <v>44001</v>
       </c>
-      <c r="G52" s="126">
+      <c r="G52" s="120">
         <v>171</v>
       </c>
       <c r="H52" s="83"/>
@@ -22181,20 +22181,20 @@
       <c r="A53" t="s">
         <v>244</v>
       </c>
-      <c r="B53" s="186">
+      <c r="B53" s="178">
         <v>43949</v>
       </c>
       <c r="C53">
         <v>2020</v>
       </c>
-      <c r="D53" s="208">
+      <c r="D53" s="198">
         <v>119.25</v>
       </c>
-      <c r="E53" s="186">
+      <c r="E53" s="178">
         <v>43959</v>
       </c>
-      <c r="F53" s="186"/>
-      <c r="G53" s="126"/>
+      <c r="F53" s="178"/>
+      <c r="G53" s="120"/>
       <c r="H53" s="83"/>
       <c r="I53" s="83"/>
       <c r="J53" s="83"/>
@@ -22209,13 +22209,13 @@
       <c r="A54" t="s">
         <v>108</v>
       </c>
-      <c r="B54" s="186"/>
-      <c r="D54" s="208"/>
-      <c r="E54" s="186"/>
-      <c r="F54" s="186">
+      <c r="B54" s="178"/>
+      <c r="D54" s="198"/>
+      <c r="E54" s="178"/>
+      <c r="F54" s="178">
         <v>44003</v>
       </c>
-      <c r="G54" s="126">
+      <c r="G54" s="120">
         <v>173</v>
       </c>
       <c r="H54" s="83"/>
@@ -22232,11 +22232,11 @@
       <c r="A55" t="s">
         <v>143</v>
       </c>
-      <c r="B55" s="186"/>
-      <c r="D55" s="208"/>
-      <c r="E55" s="186"/>
-      <c r="F55" s="186"/>
-      <c r="G55" s="126"/>
+      <c r="B55" s="178"/>
+      <c r="D55" s="198"/>
+      <c r="E55" s="178"/>
+      <c r="F55" s="178"/>
+      <c r="G55" s="120"/>
       <c r="H55" s="83">
         <v>4.5</v>
       </c>
@@ -22269,13 +22269,13 @@
       <c r="A56" t="s">
         <v>109</v>
       </c>
-      <c r="B56" s="186"/>
-      <c r="D56" s="208"/>
-      <c r="E56" s="186"/>
-      <c r="F56" s="186">
+      <c r="B56" s="178"/>
+      <c r="D56" s="198"/>
+      <c r="E56" s="178"/>
+      <c r="F56" s="178">
         <v>44008</v>
       </c>
-      <c r="G56" s="126">
+      <c r="G56" s="120">
         <v>178</v>
       </c>
       <c r="H56" s="83"/>
@@ -22292,20 +22292,20 @@
       <c r="A57" t="s">
         <v>243</v>
       </c>
-      <c r="B57" s="186">
+      <c r="B57" s="178">
         <v>43950</v>
       </c>
       <c r="C57">
         <v>2020</v>
       </c>
-      <c r="D57" s="208">
+      <c r="D57" s="198">
         <v>119.66666666666667</v>
       </c>
-      <c r="E57" s="186">
+      <c r="E57" s="178">
         <v>43959</v>
       </c>
-      <c r="F57" s="186"/>
-      <c r="G57" s="126"/>
+      <c r="F57" s="178"/>
+      <c r="G57" s="120"/>
       <c r="H57" s="83"/>
       <c r="I57" s="83"/>
       <c r="J57" s="83"/>
@@ -22320,13 +22320,13 @@
       <c r="A58" t="s">
         <v>110</v>
       </c>
-      <c r="B58" s="186"/>
-      <c r="D58" s="208"/>
-      <c r="E58" s="186"/>
-      <c r="F58" s="186">
+      <c r="B58" s="178"/>
+      <c r="D58" s="198"/>
+      <c r="E58" s="178"/>
+      <c r="F58" s="178">
         <v>44004</v>
       </c>
-      <c r="G58" s="126">
+      <c r="G58" s="120">
         <v>174</v>
       </c>
       <c r="H58" s="83"/>
@@ -22343,11 +22343,11 @@
       <c r="A59" t="s">
         <v>144</v>
       </c>
-      <c r="B59" s="186"/>
-      <c r="D59" s="208"/>
-      <c r="E59" s="186"/>
-      <c r="F59" s="186"/>
-      <c r="G59" s="126"/>
+      <c r="B59" s="178"/>
+      <c r="D59" s="198"/>
+      <c r="E59" s="178"/>
+      <c r="F59" s="178"/>
+      <c r="G59" s="120"/>
       <c r="H59" s="83">
         <v>2.6666666666666665</v>
       </c>
@@ -22380,13 +22380,13 @@
       <c r="A60" t="s">
         <v>111</v>
       </c>
-      <c r="B60" s="186"/>
-      <c r="D60" s="208"/>
-      <c r="E60" s="186"/>
-      <c r="F60" s="186">
+      <c r="B60" s="178"/>
+      <c r="D60" s="198"/>
+      <c r="E60" s="178"/>
+      <c r="F60" s="178">
         <v>44007</v>
       </c>
-      <c r="G60" s="126">
+      <c r="G60" s="120">
         <v>176.625</v>
       </c>
       <c r="H60" s="83"/>
@@ -22403,20 +22403,20 @@
       <c r="A61" t="s">
         <v>242</v>
       </c>
-      <c r="B61" s="186">
+      <c r="B61" s="178">
         <v>43950</v>
       </c>
       <c r="C61">
         <v>2020</v>
       </c>
-      <c r="D61" s="208">
+      <c r="D61" s="198">
         <v>120</v>
       </c>
-      <c r="E61" s="186">
+      <c r="E61" s="178">
         <v>43959</v>
       </c>
-      <c r="F61" s="186"/>
-      <c r="G61" s="126"/>
+      <c r="F61" s="178"/>
+      <c r="G61" s="120"/>
       <c r="H61" s="83"/>
       <c r="I61" s="83"/>
       <c r="J61" s="83"/>
@@ -22431,13 +22431,13 @@
       <c r="A62" t="s">
         <v>112</v>
       </c>
-      <c r="B62" s="186"/>
-      <c r="D62" s="208"/>
-      <c r="E62" s="186"/>
-      <c r="F62" s="186">
+      <c r="B62" s="178"/>
+      <c r="D62" s="198"/>
+      <c r="E62" s="178"/>
+      <c r="F62" s="178">
         <v>44003</v>
       </c>
-      <c r="G62" s="126">
+      <c r="G62" s="120">
         <v>173</v>
       </c>
       <c r="H62" s="83"/>
@@ -22454,11 +22454,11 @@
       <c r="A63" t="s">
         <v>145</v>
       </c>
-      <c r="B63" s="186"/>
-      <c r="D63" s="208"/>
-      <c r="E63" s="186"/>
-      <c r="F63" s="186"/>
-      <c r="G63" s="126"/>
+      <c r="B63" s="178"/>
+      <c r="D63" s="198"/>
+      <c r="E63" s="178"/>
+      <c r="F63" s="178"/>
+      <c r="G63" s="120"/>
       <c r="H63" s="83">
         <v>2.3333333333333335</v>
       </c>
@@ -22491,13 +22491,13 @@
       <c r="A64" t="s">
         <v>113</v>
       </c>
-      <c r="B64" s="186"/>
-      <c r="D64" s="208"/>
-      <c r="E64" s="186"/>
-      <c r="F64" s="186">
+      <c r="B64" s="178"/>
+      <c r="D64" s="198"/>
+      <c r="E64" s="178"/>
+      <c r="F64" s="178">
         <v>44002</v>
       </c>
-      <c r="G64" s="126">
+      <c r="G64" s="120">
         <v>172</v>
       </c>
       <c r="H64" s="83"/>
@@ -22514,20 +22514,20 @@
       <c r="A65" t="s">
         <v>241</v>
       </c>
-      <c r="B65" s="186">
+      <c r="B65" s="178">
         <v>43950</v>
       </c>
       <c r="C65">
         <v>2020</v>
       </c>
-      <c r="D65" s="208">
+      <c r="D65" s="198">
         <v>120.08333333333333</v>
       </c>
-      <c r="E65" s="186">
+      <c r="E65" s="178">
         <v>43959</v>
       </c>
-      <c r="F65" s="186"/>
-      <c r="G65" s="126"/>
+      <c r="F65" s="178"/>
+      <c r="G65" s="120"/>
       <c r="H65" s="83"/>
       <c r="I65" s="83"/>
       <c r="J65" s="83"/>
@@ -22542,13 +22542,13 @@
       <c r="A66" t="s">
         <v>114</v>
       </c>
-      <c r="B66" s="186"/>
-      <c r="D66" s="208"/>
-      <c r="E66" s="186"/>
-      <c r="F66" s="186">
+      <c r="B66" s="178"/>
+      <c r="D66" s="198"/>
+      <c r="E66" s="178"/>
+      <c r="F66" s="178">
         <v>44003</v>
       </c>
-      <c r="G66" s="126">
+      <c r="G66" s="120">
         <v>173</v>
       </c>
       <c r="H66" s="83"/>
@@ -22565,11 +22565,11 @@
       <c r="A67" t="s">
         <v>146</v>
       </c>
-      <c r="B67" s="186"/>
-      <c r="D67" s="208"/>
-      <c r="E67" s="186"/>
-      <c r="F67" s="186"/>
-      <c r="G67" s="126"/>
+      <c r="B67" s="178"/>
+      <c r="D67" s="198"/>
+      <c r="E67" s="178"/>
+      <c r="F67" s="178"/>
+      <c r="G67" s="120"/>
       <c r="H67" s="83">
         <v>4</v>
       </c>
@@ -22602,13 +22602,13 @@
       <c r="A68" t="s">
         <v>115</v>
       </c>
-      <c r="B68" s="186"/>
-      <c r="D68" s="208"/>
-      <c r="E68" s="186"/>
-      <c r="F68" s="186">
+      <c r="B68" s="178"/>
+      <c r="D68" s="198"/>
+      <c r="E68" s="178"/>
+      <c r="F68" s="178">
         <v>44006</v>
       </c>
-      <c r="G68" s="126">
+      <c r="G68" s="120">
         <v>176.33333333333334</v>
       </c>
       <c r="H68" s="83"/>
@@ -22625,20 +22625,20 @@
       <c r="A69" t="s">
         <v>245</v>
       </c>
-      <c r="B69" s="186">
+      <c r="B69" s="178">
         <v>43951</v>
       </c>
       <c r="C69">
         <v>2020</v>
       </c>
-      <c r="D69" s="208">
+      <c r="D69" s="198">
         <v>120.5</v>
       </c>
-      <c r="E69" s="186">
+      <c r="E69" s="178">
         <v>43959</v>
       </c>
-      <c r="F69" s="186"/>
-      <c r="G69" s="126"/>
+      <c r="F69" s="178"/>
+      <c r="G69" s="120"/>
       <c r="H69" s="83"/>
       <c r="I69" s="83"/>
       <c r="J69" s="83"/>
@@ -22653,13 +22653,13 @@
       <c r="A70" t="s">
         <v>116</v>
       </c>
-      <c r="B70" s="186"/>
-      <c r="D70" s="208"/>
-      <c r="E70" s="186"/>
-      <c r="F70" s="186">
+      <c r="B70" s="178"/>
+      <c r="D70" s="198"/>
+      <c r="E70" s="178"/>
+      <c r="F70" s="178">
         <v>44007</v>
       </c>
-      <c r="G70" s="126">
+      <c r="G70" s="120">
         <v>177</v>
       </c>
       <c r="H70" s="83"/>
@@ -22676,11 +22676,11 @@
       <c r="A71" t="s">
         <v>147</v>
       </c>
-      <c r="B71" s="186"/>
-      <c r="D71" s="208"/>
-      <c r="E71" s="186"/>
-      <c r="F71" s="186"/>
-      <c r="G71" s="126"/>
+      <c r="B71" s="178"/>
+      <c r="D71" s="198"/>
+      <c r="E71" s="178"/>
+      <c r="F71" s="178"/>
+      <c r="G71" s="120"/>
       <c r="H71" s="83">
         <v>4</v>
       </c>
@@ -22713,13 +22713,13 @@
       <c r="A72" t="s">
         <v>117</v>
       </c>
-      <c r="B72" s="186"/>
-      <c r="D72" s="208"/>
-      <c r="E72" s="186"/>
-      <c r="F72" s="186">
+      <c r="B72" s="178"/>
+      <c r="D72" s="198"/>
+      <c r="E72" s="178"/>
+      <c r="F72" s="178">
         <v>44006</v>
       </c>
-      <c r="G72" s="126">
+      <c r="G72" s="120">
         <v>176.33333333333334</v>
       </c>
       <c r="H72" s="83"/>
@@ -22736,20 +22736,20 @@
       <c r="A73" t="s">
         <v>246</v>
       </c>
-      <c r="B73" s="186">
+      <c r="B73" s="178">
         <v>43949</v>
       </c>
       <c r="C73">
         <v>2020</v>
       </c>
-      <c r="D73" s="208">
+      <c r="D73" s="198">
         <v>119</v>
       </c>
-      <c r="E73" s="186">
+      <c r="E73" s="178">
         <v>43959</v>
       </c>
-      <c r="F73" s="186"/>
-      <c r="G73" s="126"/>
+      <c r="F73" s="178"/>
+      <c r="G73" s="120"/>
       <c r="H73" s="83"/>
       <c r="I73" s="83"/>
       <c r="J73" s="83"/>
@@ -22764,13 +22764,13 @@
       <c r="A74" t="s">
         <v>118</v>
       </c>
-      <c r="B74" s="186"/>
-      <c r="D74" s="208"/>
-      <c r="E74" s="186"/>
-      <c r="F74" s="186">
+      <c r="B74" s="178"/>
+      <c r="D74" s="198"/>
+      <c r="E74" s="178"/>
+      <c r="F74" s="178">
         <v>44007</v>
       </c>
-      <c r="G74" s="126">
+      <c r="G74" s="120">
         <v>176.625</v>
       </c>
       <c r="H74" s="83"/>
@@ -22787,11 +22787,11 @@
       <c r="A75" t="s">
         <v>148</v>
       </c>
-      <c r="B75" s="186"/>
-      <c r="D75" s="208"/>
-      <c r="E75" s="186"/>
-      <c r="F75" s="186"/>
-      <c r="G75" s="126"/>
+      <c r="B75" s="178"/>
+      <c r="D75" s="198"/>
+      <c r="E75" s="178"/>
+      <c r="F75" s="178"/>
+      <c r="G75" s="120"/>
       <c r="H75" s="83">
         <v>3.3333333333333335</v>
       </c>
@@ -22824,13 +22824,13 @@
       <c r="A76" t="s">
         <v>119</v>
       </c>
-      <c r="B76" s="186"/>
-      <c r="D76" s="208"/>
-      <c r="E76" s="186"/>
-      <c r="F76" s="186">
+      <c r="B76" s="178"/>
+      <c r="D76" s="198"/>
+      <c r="E76" s="178"/>
+      <c r="F76" s="178">
         <v>44004</v>
       </c>
-      <c r="G76" s="126">
+      <c r="G76" s="120">
         <v>174</v>
       </c>
       <c r="H76" s="83"/>
@@ -22847,20 +22847,20 @@
       <c r="A77" t="s">
         <v>247</v>
       </c>
-      <c r="B77" s="186">
+      <c r="B77" s="178">
         <v>43950</v>
       </c>
       <c r="C77">
         <v>2020</v>
       </c>
-      <c r="D77" s="208">
+      <c r="D77" s="198">
         <v>119.91666666666667</v>
       </c>
-      <c r="E77" s="186">
+      <c r="E77" s="178">
         <v>43959</v>
       </c>
-      <c r="F77" s="186"/>
-      <c r="G77" s="126"/>
+      <c r="F77" s="178"/>
+      <c r="G77" s="120"/>
       <c r="H77" s="83"/>
       <c r="I77" s="83"/>
       <c r="J77" s="83"/>
@@ -22875,13 +22875,13 @@
       <c r="A78" t="s">
         <v>120</v>
       </c>
-      <c r="B78" s="186"/>
-      <c r="D78" s="208"/>
-      <c r="E78" s="186"/>
-      <c r="F78" s="186">
+      <c r="B78" s="178"/>
+      <c r="D78" s="198"/>
+      <c r="E78" s="178"/>
+      <c r="F78" s="178">
         <v>44003</v>
       </c>
-      <c r="G78" s="126">
+      <c r="G78" s="120">
         <v>173</v>
       </c>
       <c r="H78" s="83"/>
@@ -22898,11 +22898,11 @@
       <c r="A79" t="s">
         <v>149</v>
       </c>
-      <c r="B79" s="186"/>
-      <c r="D79" s="208"/>
-      <c r="E79" s="186"/>
-      <c r="F79" s="186"/>
-      <c r="G79" s="126"/>
+      <c r="B79" s="178"/>
+      <c r="D79" s="198"/>
+      <c r="E79" s="178"/>
+      <c r="F79" s="178"/>
+      <c r="G79" s="120"/>
       <c r="H79" s="83">
         <v>2.8333333333333335</v>
       </c>
@@ -22935,13 +22935,13 @@
       <c r="A80" t="s">
         <v>121</v>
       </c>
-      <c r="B80" s="186"/>
-      <c r="D80" s="208"/>
-      <c r="E80" s="186"/>
-      <c r="F80" s="186">
+      <c r="B80" s="178"/>
+      <c r="D80" s="198"/>
+      <c r="E80" s="178"/>
+      <c r="F80" s="178">
         <v>44004</v>
       </c>
-      <c r="G80" s="126">
+      <c r="G80" s="120">
         <v>174</v>
       </c>
       <c r="H80" s="83"/>
@@ -22958,20 +22958,20 @@
       <c r="A81" t="s">
         <v>248</v>
       </c>
-      <c r="B81" s="186">
+      <c r="B81" s="178">
         <v>43949</v>
       </c>
       <c r="C81">
         <v>2020</v>
       </c>
-      <c r="D81" s="208">
+      <c r="D81" s="198">
         <v>119.16666666666667</v>
       </c>
-      <c r="E81" s="186">
+      <c r="E81" s="178">
         <v>43959</v>
       </c>
-      <c r="F81" s="186"/>
-      <c r="G81" s="126"/>
+      <c r="F81" s="178"/>
+      <c r="G81" s="120"/>
       <c r="H81" s="83"/>
       <c r="I81" s="83"/>
       <c r="J81" s="83"/>
@@ -22986,13 +22986,13 @@
       <c r="A82" t="s">
         <v>122</v>
       </c>
-      <c r="B82" s="186"/>
-      <c r="D82" s="208"/>
-      <c r="E82" s="186"/>
-      <c r="F82" s="186">
+      <c r="B82" s="178"/>
+      <c r="D82" s="198"/>
+      <c r="E82" s="178"/>
+      <c r="F82" s="178">
         <v>44008</v>
       </c>
-      <c r="G82" s="126">
+      <c r="G82" s="120">
         <v>177.5</v>
       </c>
       <c r="H82" s="83"/>
@@ -23009,11 +23009,11 @@
       <c r="A83" t="s">
         <v>150</v>
       </c>
-      <c r="B83" s="186"/>
-      <c r="D83" s="208"/>
-      <c r="E83" s="186"/>
-      <c r="F83" s="186"/>
-      <c r="G83" s="126"/>
+      <c r="B83" s="178"/>
+      <c r="D83" s="198"/>
+      <c r="E83" s="178"/>
+      <c r="F83" s="178"/>
+      <c r="G83" s="120"/>
       <c r="H83" s="83">
         <v>3.5</v>
       </c>
@@ -23046,13 +23046,13 @@
       <c r="A84" t="s">
         <v>123</v>
       </c>
-      <c r="B84" s="186"/>
-      <c r="D84" s="208"/>
-      <c r="E84" s="186"/>
-      <c r="F84" s="186">
+      <c r="B84" s="178"/>
+      <c r="D84" s="198"/>
+      <c r="E84" s="178"/>
+      <c r="F84" s="178">
         <v>44008</v>
       </c>
-      <c r="G84" s="126">
+      <c r="G84" s="120">
         <v>178.375</v>
       </c>
       <c r="H84" s="83"/>
@@ -23069,20 +23069,20 @@
       <c r="A85" t="s">
         <v>252</v>
       </c>
-      <c r="B85" s="186">
+      <c r="B85" s="178">
         <v>43950</v>
       </c>
       <c r="C85">
         <v>2020</v>
       </c>
-      <c r="D85" s="208">
+      <c r="D85" s="198">
         <v>119.5</v>
       </c>
-      <c r="E85" s="186">
+      <c r="E85" s="178">
         <v>43961</v>
       </c>
-      <c r="F85" s="186"/>
-      <c r="G85" s="126"/>
+      <c r="F85" s="178"/>
+      <c r="G85" s="120"/>
       <c r="H85" s="83"/>
       <c r="I85" s="83"/>
       <c r="J85" s="83"/>
@@ -23097,13 +23097,13 @@
       <c r="A86" t="s">
         <v>124</v>
       </c>
-      <c r="B86" s="186"/>
-      <c r="D86" s="208"/>
-      <c r="E86" s="186"/>
-      <c r="F86" s="186">
+      <c r="B86" s="178"/>
+      <c r="D86" s="198"/>
+      <c r="E86" s="178"/>
+      <c r="F86" s="178">
         <v>44004</v>
       </c>
-      <c r="G86" s="126">
+      <c r="G86" s="120">
         <v>174</v>
       </c>
       <c r="H86" s="83"/>
@@ -23120,11 +23120,11 @@
       <c r="A87" t="s">
         <v>151</v>
       </c>
-      <c r="B87" s="186"/>
-      <c r="D87" s="208"/>
-      <c r="E87" s="186"/>
-      <c r="F87" s="186"/>
-      <c r="G87" s="126"/>
+      <c r="B87" s="178"/>
+      <c r="D87" s="198"/>
+      <c r="E87" s="178"/>
+      <c r="F87" s="178"/>
+      <c r="G87" s="120"/>
       <c r="H87" s="83">
         <v>3.3333333333333335</v>
       </c>
@@ -23157,13 +23157,13 @@
       <c r="A88" t="s">
         <v>125</v>
       </c>
-      <c r="B88" s="186"/>
-      <c r="D88" s="208"/>
-      <c r="E88" s="186"/>
-      <c r="F88" s="186">
+      <c r="B88" s="178"/>
+      <c r="D88" s="198"/>
+      <c r="E88" s="178"/>
+      <c r="F88" s="178">
         <v>44006</v>
       </c>
-      <c r="G88" s="126">
+      <c r="G88" s="120">
         <v>176</v>
       </c>
       <c r="H88" s="83"/>
@@ -23180,20 +23180,20 @@
       <c r="A89" t="s">
         <v>251</v>
       </c>
-      <c r="B89" s="186">
+      <c r="B89" s="178">
         <v>43951</v>
       </c>
       <c r="C89">
         <v>2020</v>
       </c>
-      <c r="D89" s="208">
+      <c r="D89" s="198">
         <v>120.5</v>
       </c>
-      <c r="E89" s="186">
+      <c r="E89" s="178">
         <v>43961</v>
       </c>
-      <c r="F89" s="186"/>
-      <c r="G89" s="126"/>
+      <c r="F89" s="178"/>
+      <c r="G89" s="120"/>
       <c r="H89" s="83"/>
       <c r="I89" s="83"/>
       <c r="J89" s="83"/>
@@ -23208,13 +23208,13 @@
       <c r="A90" t="s">
         <v>126</v>
       </c>
-      <c r="B90" s="186"/>
-      <c r="D90" s="208"/>
-      <c r="E90" s="186"/>
-      <c r="F90" s="186">
+      <c r="B90" s="178"/>
+      <c r="D90" s="198"/>
+      <c r="E90" s="178"/>
+      <c r="F90" s="178">
         <v>44008</v>
       </c>
-      <c r="G90" s="126">
+      <c r="G90" s="120">
         <v>177.5</v>
       </c>
       <c r="H90" s="83"/>
@@ -23231,11 +23231,11 @@
       <c r="A91" t="s">
         <v>152</v>
       </c>
-      <c r="B91" s="186"/>
-      <c r="D91" s="208"/>
-      <c r="E91" s="186"/>
-      <c r="F91" s="186"/>
-      <c r="G91" s="126"/>
+      <c r="B91" s="178"/>
+      <c r="D91" s="198"/>
+      <c r="E91" s="178"/>
+      <c r="F91" s="178"/>
+      <c r="G91" s="120"/>
       <c r="H91" s="83">
         <v>3.6666666666666665</v>
       </c>
@@ -23268,13 +23268,13 @@
       <c r="A92" t="s">
         <v>127</v>
       </c>
-      <c r="B92" s="186"/>
-      <c r="D92" s="208"/>
-      <c r="E92" s="186"/>
-      <c r="F92" s="186">
+      <c r="B92" s="178"/>
+      <c r="D92" s="198"/>
+      <c r="E92" s="178"/>
+      <c r="F92" s="178">
         <v>44005</v>
       </c>
-      <c r="G92" s="126">
+      <c r="G92" s="120">
         <v>175.16666666666666</v>
       </c>
       <c r="H92" s="83"/>
@@ -23291,20 +23291,20 @@
       <c r="A93" t="s">
         <v>250</v>
       </c>
-      <c r="B93" s="186">
+      <c r="B93" s="178">
         <v>43950</v>
       </c>
       <c r="C93">
         <v>2020</v>
       </c>
-      <c r="D93" s="208">
+      <c r="D93" s="198">
         <v>120.25</v>
       </c>
-      <c r="E93" s="186">
+      <c r="E93" s="178">
         <v>43960</v>
       </c>
-      <c r="F93" s="186"/>
-      <c r="G93" s="126"/>
+      <c r="F93" s="178"/>
+      <c r="G93" s="120"/>
       <c r="H93" s="83"/>
       <c r="I93" s="83"/>
       <c r="J93" s="83"/>
@@ -23319,13 +23319,13 @@
       <c r="A94" t="s">
         <v>128</v>
       </c>
-      <c r="B94" s="186"/>
-      <c r="D94" s="208"/>
-      <c r="E94" s="186"/>
-      <c r="F94" s="186">
+      <c r="B94" s="178"/>
+      <c r="D94" s="198"/>
+      <c r="E94" s="178"/>
+      <c r="F94" s="178">
         <v>44003</v>
       </c>
-      <c r="G94" s="126">
+      <c r="G94" s="120">
         <v>173</v>
       </c>
       <c r="H94" s="83"/>
@@ -23342,11 +23342,11 @@
       <c r="A95" t="s">
         <v>153</v>
       </c>
-      <c r="B95" s="186"/>
-      <c r="D95" s="208"/>
-      <c r="E95" s="186"/>
-      <c r="F95" s="186"/>
-      <c r="G95" s="126"/>
+      <c r="B95" s="178"/>
+      <c r="D95" s="198"/>
+      <c r="E95" s="178"/>
+      <c r="F95" s="178"/>
+      <c r="G95" s="120"/>
       <c r="H95" s="83">
         <v>3</v>
       </c>
@@ -23379,13 +23379,13 @@
       <c r="A96" t="s">
         <v>129</v>
       </c>
-      <c r="B96" s="186"/>
-      <c r="D96" s="208"/>
-      <c r="E96" s="186"/>
-      <c r="F96" s="186">
+      <c r="B96" s="178"/>
+      <c r="D96" s="198"/>
+      <c r="E96" s="178"/>
+      <c r="F96" s="178">
         <v>44008</v>
       </c>
-      <c r="G96" s="126">
+      <c r="G96" s="120">
         <v>177.5</v>
       </c>
     </row>
@@ -23393,21 +23393,21 @@
       <c r="A97" t="s">
         <v>249</v>
       </c>
-      <c r="B97" s="186">
+      <c r="B97" s="178">
         <v>43950</v>
       </c>
       <c r="C97">
         <v>2020</v>
       </c>
-      <c r="D97" s="208">
+      <c r="D97" s="198">
         <v>120.25</v>
       </c>
-      <c r="E97" s="186">
+      <c r="E97" s="178">
         <v>43961</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D98" s="208"/>
+      <c r="D98" s="198"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -24218,21 +24218,21 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="84" t="s">
+      <c r="B7" s="199" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="85"/>
-      <c r="D7" s="85"/>
-      <c r="E7" s="85"/>
-      <c r="F7" s="85"/>
-      <c r="G7" s="85"/>
-      <c r="H7" s="85"/>
+      <c r="C7" s="200"/>
+      <c r="D7" s="200"/>
+      <c r="E7" s="200"/>
+      <c r="F7" s="200"/>
+      <c r="G7" s="200"/>
+      <c r="H7" s="200"/>
     </row>
     <row r="8" spans="1:11" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="86" t="s">
+      <c r="B8" s="201" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="86"/>
+      <c r="C8" s="201"/>
       <c r="D8" s="18" t="s">
         <v>12</v>
       </c>
@@ -25282,10 +25282,10 @@
       <c r="AD11" s="57"/>
     </row>
     <row r="12" spans="1:30" ht="20.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="86" t="s">
+      <c r="B12" s="201" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="86"/>
+      <c r="C12" s="201"/>
       <c r="D12" s="18" t="s">
         <v>12</v>
       </c>
@@ -29273,10 +29273,10 @@
       <c r="AC11" s="57"/>
     </row>
     <row r="12" spans="1:29" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="86" t="s">
+      <c r="B12" s="201" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="86"/>
+      <c r="C12" s="201"/>
       <c r="D12" s="18" t="s">
         <v>12</v>
       </c>
